--- a/Colombia/Resultados electorales.xlsx
+++ b/Colombia/Resultados electorales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juansoag\Downloads\Github\Avances tesis\Avances tesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juans\Downloads\Avances tesis\Colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41327905-2522-41EB-B8DC-84D6EA17EC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE74403F-CA1C-483F-AAC9-3CD263DB4392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="1245" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="1170" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidatos E-26 ALC" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4857" uniqueCount="1242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4926" uniqueCount="1311">
   <si>
     <t>ID Candidato</t>
   </si>
@@ -3768,6 +3768,213 @@
   </si>
   <si>
     <t>https://www.facebook.com/Robertojimenezdosquebradas</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/jorgenavasgranados/?locale=es_LA</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@jorge_navas</t>
+  </si>
+  <si>
+    <t>https://x.com/JorgeANavasG</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jorgenavasgranados/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/joseluisosoriogalviis/mentions/</t>
+  </si>
+  <si>
+    <t>https://x.com/JoseOsorioG</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/joseosoriog/</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@joseosoriogalvis</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/horaciojserpa/</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@horaciojserpa</t>
+  </si>
+  <si>
+    <t>https://x.com/horaciojserpa</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/horaciojserpa</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tatianalopezsaldarriaga/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/libiamosqueraviveros/</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@tatianalopezsaldarriaga</t>
+  </si>
+  <si>
+    <t>https://x.com/TatianaLopSal</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/TatianaLopezSaldarriagaA</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/consueloberraca</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@consueloberraca</t>
+  </si>
+  <si>
+    <t>https://x.com/consuelordonez</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ConsueloBerraca</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pautorosantana/</t>
+  </si>
+  <si>
+    <t>https://x.com/pautorosantana</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@pautorosantana</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/pautorosantana</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/adolforomerolider/</t>
+  </si>
+  <si>
+    <t>https://x.com/AdolfoRomeroB</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/adolforomerob</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/camiloquirozh/</t>
+  </si>
+  <si>
+    <t>https://x.com/camiloquirozh</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@camiloquirozh</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/CamiloQuirozHinojosa/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/eribertoibarrac/</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@eribertoibarrac</t>
+  </si>
+  <si>
+    <t>https://x.com/betoibarra2020</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eribertoibarrac/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oscarmauriciotoro/</t>
+  </si>
+  <si>
+    <t>https://x.com/omauriciotoro</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@omaurotoro</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/omaurotoro</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/marcohincapie</t>
+  </si>
+  <si>
+    <t>https://x.com/marcoemiliohr</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@marco_hincapie</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/MarcoHincapieR/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/libia.mosqueraviveros/</t>
+  </si>
+  <si>
+    <t>https://x.com/libiamosquerav</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@libiamosquerav</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/heinergaitan_/</t>
+  </si>
+  <si>
+    <t>https://x.com/HeinerGaitan</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@heinergaitan_</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/GaitanParraHeiner/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/miguelmorales_lavoz/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/MiguelMoralesOficial/</t>
+  </si>
+  <si>
+    <t>https://x.com/mmoraleslavoz</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@miguelmoraleslavoz</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/PadreHuerfano1/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hassanfares1970/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/RenzoGarciaP/?locale=es_LA</t>
+  </si>
+  <si>
+    <t>https://x.com/renzogarciap</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/renzo.garcia1</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@renzo.garcia1</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lavallecaucana</t>
+  </si>
+  <si>
+    <t>https://x.com/LaVallecaucana</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@lavallecaucana</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LaVallecaucana</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/Osoriobotelloconcejal</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/OsorioBotelloAlcalde</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/john.carrerov/</t>
+  </si>
+  <si>
+    <t>https://x.com/John_Carrero</t>
   </si>
 </sst>
 </file>
@@ -3895,7 +4102,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3967,10 +4174,13 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4276,7 +4486,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I353"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -4288,7 +4498,7 @@
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4317,7 +4527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -4346,7 +4556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
@@ -4375,7 +4585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -4404,7 +4614,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>22</v>
       </c>
@@ -4433,7 +4643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -4462,7 +4672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
@@ -4491,7 +4701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -4520,7 +4730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
@@ -4549,7 +4759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -4578,7 +4788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
@@ -4607,7 +4817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -4636,7 +4846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
@@ -4665,7 +4875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -4694,7 +4904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>55</v>
       </c>
@@ -4723,7 +4933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>58</v>
       </c>
@@ -4752,7 +4962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>61</v>
       </c>
@@ -4781,7 +4991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
@@ -4810,7 +5020,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>67</v>
       </c>
@@ -4839,7 +5049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>69</v>
       </c>
@@ -4868,7 +5078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>72</v>
       </c>
@@ -4897,7 +5107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>75</v>
       </c>
@@ -4926,7 +5136,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>78</v>
       </c>
@@ -4955,7 +5165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>81</v>
       </c>
@@ -4984,7 +5194,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>83</v>
       </c>
@@ -5013,7 +5223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>86</v>
       </c>
@@ -5042,7 +5252,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>89</v>
       </c>
@@ -5071,7 +5281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -5100,7 +5310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>97</v>
       </c>
@@ -5129,7 +5339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>100</v>
       </c>
@@ -5158,7 +5368,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>102</v>
       </c>
@@ -5187,7 +5397,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>105</v>
       </c>
@@ -5216,7 +5426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>108</v>
       </c>
@@ -5245,7 +5455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>110</v>
       </c>
@@ -5274,7 +5484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>113</v>
       </c>
@@ -5303,7 +5513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
@@ -5332,7 +5542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>117</v>
       </c>
@@ -5361,7 +5571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>119</v>
       </c>
@@ -5390,7 +5600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>121</v>
       </c>
@@ -5419,7 +5629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>127</v>
       </c>
@@ -5448,7 +5658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>130</v>
       </c>
@@ -5477,7 +5687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>133</v>
       </c>
@@ -5506,7 +5716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>135</v>
       </c>
@@ -5535,7 +5745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>138</v>
       </c>
@@ -5564,7 +5774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>140</v>
       </c>
@@ -5593,7 +5803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>145</v>
       </c>
@@ -5622,7 +5832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>147</v>
       </c>
@@ -5651,7 +5861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>150</v>
       </c>
@@ -5680,7 +5890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>152</v>
       </c>
@@ -5709,7 +5919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>155</v>
       </c>
@@ -5738,7 +5948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>158</v>
       </c>
@@ -5767,7 +5977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>161</v>
       </c>
@@ -5796,7 +6006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>164</v>
       </c>
@@ -5825,7 +6035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>167</v>
       </c>
@@ -5854,7 +6064,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>171</v>
       </c>
@@ -5883,7 +6093,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>174</v>
       </c>
@@ -5912,7 +6122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>177</v>
       </c>
@@ -5941,7 +6151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>180</v>
       </c>
@@ -5970,7 +6180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>183</v>
       </c>
@@ -5999,7 +6209,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>186</v>
       </c>
@@ -6028,7 +6238,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>188</v>
       </c>
@@ -6057,7 +6267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>191</v>
       </c>
@@ -6086,7 +6296,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
         <v>193</v>
       </c>
@@ -6115,7 +6325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -6144,7 +6354,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>201</v>
       </c>
@@ -6173,7 +6383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>204</v>
       </c>
@@ -6202,7 +6412,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>206</v>
       </c>
@@ -6231,7 +6441,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>208</v>
       </c>
@@ -6260,7 +6470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>210</v>
       </c>
@@ -6289,7 +6499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>212</v>
       </c>
@@ -6318,7 +6528,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>215</v>
       </c>
@@ -6347,7 +6557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>217</v>
       </c>
@@ -6376,7 +6586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>219</v>
       </c>
@@ -6405,7 +6615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>222</v>
       </c>
@@ -6434,7 +6644,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>225</v>
       </c>
@@ -6463,7 +6673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>228</v>
       </c>
@@ -6492,7 +6702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>231</v>
       </c>
@@ -6521,7 +6731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>234</v>
       </c>
@@ -6550,7 +6760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>239</v>
       </c>
@@ -6579,7 +6789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>241</v>
       </c>
@@ -6608,7 +6818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>244</v>
       </c>
@@ -6637,7 +6847,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>247</v>
       </c>
@@ -6666,7 +6876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>250</v>
       </c>
@@ -6695,7 +6905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>253</v>
       </c>
@@ -6724,7 +6934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>255</v>
       </c>
@@ -6753,7 +6963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>257</v>
       </c>
@@ -6782,7 +6992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>259</v>
       </c>
@@ -6811,7 +7021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>261</v>
       </c>
@@ -6840,7 +7050,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>263</v>
       </c>
@@ -6869,7 +7079,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>265</v>
       </c>
@@ -6898,7 +7108,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>268</v>
       </c>
@@ -6927,7 +7137,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
         <v>270</v>
       </c>
@@ -6956,7 +7166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>273</v>
       </c>
@@ -6985,7 +7195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>276</v>
       </c>
@@ -7014,7 +7224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
         <v>280</v>
       </c>
@@ -7043,7 +7253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>283</v>
       </c>
@@ -7072,7 +7282,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>286</v>
       </c>
@@ -7101,7 +7311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>289</v>
       </c>
@@ -7130,7 +7340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>292</v>
       </c>
@@ -7159,7 +7369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>294</v>
       </c>
@@ -7188,7 +7398,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>297</v>
       </c>
@@ -7217,7 +7427,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>299</v>
       </c>
@@ -7246,7 +7456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>302</v>
       </c>
@@ -7275,7 +7485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>304</v>
       </c>
@@ -7304,7 +7514,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>309</v>
       </c>
@@ -7333,7 +7543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>312</v>
       </c>
@@ -7362,7 +7572,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>314</v>
       </c>
@@ -7391,7 +7601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>316</v>
       </c>
@@ -7420,7 +7630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>318</v>
       </c>
@@ -7449,7 +7659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>321</v>
       </c>
@@ -7478,7 +7688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>323</v>
       </c>
@@ -7507,7 +7717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>325</v>
       </c>
@@ -7536,7 +7746,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>327</v>
       </c>
@@ -7565,7 +7775,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>329</v>
       </c>
@@ -7594,7 +7804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="8" t="s">
         <v>332</v>
       </c>
@@ -7623,7 +7833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>335</v>
       </c>
@@ -7652,7 +7862,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>340</v>
       </c>
@@ -7681,7 +7891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>342</v>
       </c>
@@ -7710,7 +7920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
         <v>344</v>
       </c>
@@ -7739,7 +7949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>346</v>
       </c>
@@ -7768,7 +7978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>349</v>
       </c>
@@ -7797,7 +8007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>351</v>
       </c>
@@ -7826,7 +8036,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>353</v>
       </c>
@@ -7855,7 +8065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>355</v>
       </c>
@@ -7884,7 +8094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>357</v>
       </c>
@@ -7913,7 +8123,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>360</v>
       </c>
@@ -7942,7 +8152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>363</v>
       </c>
@@ -7971,7 +8181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>366</v>
       </c>
@@ -8000,7 +8210,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
         <v>369</v>
       </c>
@@ -8029,7 +8239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>371</v>
       </c>
@@ -8058,7 +8268,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>377</v>
       </c>
@@ -8087,7 +8297,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="8" t="s">
         <v>379</v>
       </c>
@@ -8116,7 +8326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>382</v>
       </c>
@@ -8145,7 +8355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>385</v>
       </c>
@@ -8174,7 +8384,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="8" t="s">
         <v>387</v>
       </c>
@@ -8203,7 +8413,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>392</v>
       </c>
@@ -8232,7 +8442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>394</v>
       </c>
@@ -8261,7 +8471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>396</v>
       </c>
@@ -8290,7 +8500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
         <v>399</v>
       </c>
@@ -8319,7 +8529,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>403</v>
       </c>
@@ -8348,7 +8558,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
         <v>406</v>
       </c>
@@ -8377,7 +8587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
         <v>408</v>
       </c>
@@ -8406,7 +8616,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
         <v>411</v>
       </c>
@@ -8435,7 +8645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>413</v>
       </c>
@@ -8464,7 +8674,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
         <v>415</v>
       </c>
@@ -8493,7 +8703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>418</v>
       </c>
@@ -8522,7 +8732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
         <v>420</v>
       </c>
@@ -8551,7 +8761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>422</v>
       </c>
@@ -8580,7 +8790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
         <v>425</v>
       </c>
@@ -8609,7 +8819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>430</v>
       </c>
@@ -8638,7 +8848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
         <v>433</v>
       </c>
@@ -8667,7 +8877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>435</v>
       </c>
@@ -8696,7 +8906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
         <v>438</v>
       </c>
@@ -8725,7 +8935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>441</v>
       </c>
@@ -8754,7 +8964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
         <v>443</v>
       </c>
@@ -8783,7 +8993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>446</v>
       </c>
@@ -8812,7 +9022,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
         <v>448</v>
       </c>
@@ -8841,7 +9051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>451</v>
       </c>
@@ -8870,7 +9080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>455</v>
       </c>
@@ -8899,7 +9109,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="8" t="s">
         <v>458</v>
       </c>
@@ -8928,7 +9138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
         <v>461</v>
       </c>
@@ -8957,7 +9167,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>464</v>
       </c>
@@ -8986,7 +9196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
         <v>466</v>
       </c>
@@ -9015,7 +9225,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>468</v>
       </c>
@@ -9044,7 +9254,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
         <v>470</v>
       </c>
@@ -9073,7 +9283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="8" t="s">
         <v>472</v>
       </c>
@@ -9102,7 +9312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
         <v>478</v>
       </c>
@@ -9131,7 +9341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>480</v>
       </c>
@@ -9160,7 +9370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
         <v>482</v>
       </c>
@@ -9189,7 +9399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>484</v>
       </c>
@@ -9218,7 +9428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
         <v>486</v>
       </c>
@@ -9247,7 +9457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>488</v>
       </c>
@@ -9276,7 +9486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
         <v>491</v>
       </c>
@@ -9305,7 +9515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>493</v>
       </c>
@@ -9334,7 +9544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
         <v>495</v>
       </c>
@@ -9363,7 +9573,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="8" t="s">
         <v>498</v>
       </c>
@@ -9392,7 +9602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
         <v>502</v>
       </c>
@@ -9421,7 +9631,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>505</v>
       </c>
@@ -9450,7 +9660,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
         <v>508</v>
       </c>
@@ -9479,7 +9689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>510</v>
       </c>
@@ -9508,7 +9718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
         <v>513</v>
       </c>
@@ -9537,7 +9747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>515</v>
       </c>
@@ -9566,7 +9776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>517</v>
       </c>
@@ -9595,7 +9805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>519</v>
       </c>
@@ -9624,7 +9834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
         <v>522</v>
       </c>
@@ -9653,7 +9863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>525</v>
       </c>
@@ -9682,7 +9892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
         <v>528</v>
       </c>
@@ -9711,7 +9921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>530</v>
       </c>
@@ -9740,7 +9950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
         <v>532</v>
       </c>
@@ -9769,7 +9979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>534</v>
       </c>
@@ -9798,7 +10008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="5" t="s">
         <v>539</v>
       </c>
@@ -9827,7 +10037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>541</v>
       </c>
@@ -9856,7 +10066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
         <v>543</v>
       </c>
@@ -9885,7 +10095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>546</v>
       </c>
@@ -9914,7 +10124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
         <v>548</v>
       </c>
@@ -9943,7 +10153,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>551</v>
       </c>
@@ -9972,7 +10182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="8" t="s">
         <v>553</v>
       </c>
@@ -10001,7 +10211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>556</v>
       </c>
@@ -10030,7 +10240,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
         <v>561</v>
       </c>
@@ -10059,7 +10269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>563</v>
       </c>
@@ -10088,7 +10298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
         <v>565</v>
       </c>
@@ -10117,7 +10327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>568</v>
       </c>
@@ -10146,7 +10356,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="5" t="s">
         <v>570</v>
       </c>
@@ -10175,7 +10385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="8" t="s">
         <v>573</v>
       </c>
@@ -10204,7 +10414,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>576</v>
       </c>
@@ -10233,7 +10443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>579</v>
       </c>
@@ -10262,7 +10472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="5" t="s">
         <v>582</v>
       </c>
@@ -10291,7 +10501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>586</v>
       </c>
@@ -10320,7 +10530,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
         <v>588</v>
       </c>
@@ -10349,7 +10559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>591</v>
       </c>
@@ -10378,7 +10588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
         <v>593</v>
       </c>
@@ -10407,7 +10617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>595</v>
       </c>
@@ -10436,7 +10646,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="8" t="s">
         <v>597</v>
       </c>
@@ -10465,7 +10675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>600</v>
       </c>
@@ -10494,7 +10704,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
         <v>602</v>
       </c>
@@ -10523,7 +10733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>605</v>
       </c>
@@ -10552,7 +10762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="5" t="s">
         <v>607</v>
       </c>
@@ -10581,7 +10791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>612</v>
       </c>
@@ -10610,7 +10820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="5" t="s">
         <v>614</v>
       </c>
@@ -10639,7 +10849,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>617</v>
       </c>
@@ -10668,7 +10878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="5" t="s">
         <v>620</v>
       </c>
@@ -10697,7 +10907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="8" t="s">
         <v>622</v>
       </c>
@@ -10726,7 +10936,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="5" t="s">
         <v>625</v>
       </c>
@@ -10755,7 +10965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>627</v>
       </c>
@@ -10784,7 +10994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="5" t="s">
         <v>629</v>
       </c>
@@ -10813,7 +11023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>631</v>
       </c>
@@ -10842,7 +11052,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
         <v>636</v>
       </c>
@@ -10871,7 +11081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>638</v>
       </c>
@@ -10900,7 +11110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="5" t="s">
         <v>640</v>
       </c>
@@ -10929,7 +11139,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>642</v>
       </c>
@@ -10958,7 +11168,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="8" t="s">
         <v>644</v>
       </c>
@@ -10987,7 +11197,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>647</v>
       </c>
@@ -11016,7 +11226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="5" t="s">
         <v>649</v>
       </c>
@@ -11045,7 +11255,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>654</v>
       </c>
@@ -11074,7 +11284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="5" t="s">
         <v>656</v>
       </c>
@@ -11103,7 +11313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>658</v>
       </c>
@@ -11132,7 +11342,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="5" t="s">
         <v>660</v>
       </c>
@@ -11161,7 +11371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>662</v>
       </c>
@@ -11190,7 +11400,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="5" t="s">
         <v>664</v>
       </c>
@@ -11219,7 +11429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>666</v>
       </c>
@@ -11248,7 +11458,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="5" t="s">
         <v>668</v>
       </c>
@@ -11277,7 +11487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="8" t="s">
         <v>670</v>
       </c>
@@ -11306,7 +11516,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="5" t="s">
         <v>673</v>
       </c>
@@ -11335,7 +11545,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>675</v>
       </c>
@@ -11364,7 +11574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="5" t="s">
         <v>677</v>
       </c>
@@ -11393,7 +11603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>680</v>
       </c>
@@ -11422,7 +11632,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="5" t="s">
         <v>685</v>
       </c>
@@ -11451,7 +11661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>687</v>
       </c>
@@ -11480,7 +11690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="5" t="s">
         <v>689</v>
       </c>
@@ -11509,7 +11719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>691</v>
       </c>
@@ -11538,7 +11748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="5" t="s">
         <v>693</v>
       </c>
@@ -11567,7 +11777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>695</v>
       </c>
@@ -11596,7 +11806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="5" t="s">
         <v>698</v>
       </c>
@@ -11625,7 +11835,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>700</v>
       </c>
@@ -11654,7 +11864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="5" t="s">
         <v>702</v>
       </c>
@@ -11683,7 +11893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>705</v>
       </c>
@@ -11712,7 +11922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" s="5" t="s">
         <v>707</v>
       </c>
@@ -11741,7 +11951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>709</v>
       </c>
@@ -11770,7 +11980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="5" t="s">
         <v>711</v>
       </c>
@@ -11799,7 +12009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>713</v>
       </c>
@@ -11828,7 +12038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
         <v>718</v>
       </c>
@@ -11857,7 +12067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="8" t="s">
         <v>720</v>
       </c>
@@ -11886,7 +12096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" s="5" t="s">
         <v>723</v>
       </c>
@@ -11915,7 +12125,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>726</v>
       </c>
@@ -11944,7 +12154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" s="5" t="s">
         <v>728</v>
       </c>
@@ -11973,7 +12183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>731</v>
       </c>
@@ -12002,7 +12212,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="5" t="s">
         <v>731</v>
       </c>
@@ -12031,7 +12241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="8" t="s">
         <v>736</v>
       </c>
@@ -12060,7 +12270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" s="8" t="s">
         <v>736</v>
       </c>
@@ -12089,7 +12299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>739</v>
       </c>
@@ -12118,7 +12328,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" s="5" t="s">
         <v>739</v>
       </c>
@@ -12147,7 +12357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>742</v>
       </c>
@@ -12176,7 +12386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" s="5" t="s">
         <v>742</v>
       </c>
@@ -12205,7 +12415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>744</v>
       </c>
@@ -12234,7 +12444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="5" t="s">
         <v>744</v>
       </c>
@@ -12263,7 +12473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>746</v>
       </c>
@@ -12292,7 +12502,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="5" t="s">
         <v>746</v>
       </c>
@@ -12321,7 +12531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>749</v>
       </c>
@@ -12350,7 +12560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="5" t="s">
         <v>749</v>
       </c>
@@ -12379,7 +12589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>751</v>
       </c>
@@ -12408,7 +12618,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="5" t="s">
         <v>751</v>
       </c>
@@ -12437,7 +12647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>753</v>
       </c>
@@ -12466,7 +12676,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" s="5" t="s">
         <v>753</v>
       </c>
@@ -12495,7 +12705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>755</v>
       </c>
@@ -12524,7 +12734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" s="5" t="s">
         <v>760</v>
       </c>
@@ -12553,7 +12763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>762</v>
       </c>
@@ -12582,7 +12792,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="5" t="s">
         <v>764</v>
       </c>
@@ -12611,7 +12821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>766</v>
       </c>
@@ -12640,7 +12850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
         <v>769</v>
       </c>
@@ -12669,7 +12879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>771</v>
       </c>
@@ -12698,7 +12908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" s="5" t="s">
         <v>774</v>
       </c>
@@ -12727,7 +12937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>776</v>
       </c>
@@ -12756,7 +12966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="5" t="s">
         <v>778</v>
       </c>
@@ -12785,7 +12995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>781</v>
       </c>
@@ -12814,7 +13024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" s="5" t="s">
         <v>783</v>
       </c>
@@ -12843,7 +13053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>785</v>
       </c>
@@ -12872,7 +13082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="8" t="s">
         <v>787</v>
       </c>
@@ -12901,7 +13111,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>789</v>
       </c>
@@ -12930,7 +13140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="5" t="s">
         <v>794</v>
       </c>
@@ -12959,7 +13169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>797</v>
       </c>
@@ -12988,7 +13198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="5" t="s">
         <v>799</v>
       </c>
@@ -13017,7 +13227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>802</v>
       </c>
@@ -13046,7 +13256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" s="8" t="s">
         <v>804</v>
       </c>
@@ -13075,7 +13285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>807</v>
       </c>
@@ -13104,7 +13314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="5" t="s">
         <v>810</v>
       </c>
@@ -13133,7 +13343,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>813</v>
       </c>
@@ -13162,7 +13372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="5" t="s">
         <v>816</v>
       </c>
@@ -13191,7 +13401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>818</v>
       </c>
@@ -13220,7 +13430,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" s="5" t="s">
         <v>822</v>
       </c>
@@ -13249,7 +13459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>824</v>
       </c>
@@ -13278,7 +13488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" s="5" t="s">
         <v>826</v>
       </c>
@@ -13307,7 +13517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>828</v>
       </c>
@@ -13336,7 +13546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" s="5" t="s">
         <v>830</v>
       </c>
@@ -13365,7 +13575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="8" t="s">
         <v>832</v>
       </c>
@@ -13394,7 +13604,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" s="5" t="s">
         <v>835</v>
       </c>
@@ -13423,7 +13633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
         <v>837</v>
       </c>
@@ -13452,7 +13662,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="5" t="s">
         <v>839</v>
       </c>
@@ -13481,7 +13691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
         <v>841</v>
       </c>
@@ -13510,7 +13720,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="5" t="s">
         <v>843</v>
       </c>
@@ -13539,7 +13749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>849</v>
       </c>
@@ -13568,7 +13778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="5" t="s">
         <v>851</v>
       </c>
@@ -13597,7 +13807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>853</v>
       </c>
@@ -13626,7 +13836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="5" t="s">
         <v>855</v>
       </c>
@@ -13655,7 +13865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>857</v>
       </c>
@@ -13684,7 +13894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="5" t="s">
         <v>860</v>
       </c>
@@ -13713,7 +13923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>862</v>
       </c>
@@ -13742,7 +13952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="8" t="s">
         <v>865</v>
       </c>
@@ -13771,7 +13981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>867</v>
       </c>
@@ -13800,7 +14010,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="5" t="s">
         <v>872</v>
       </c>
@@ -13829,7 +14039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>874</v>
       </c>
@@ -13858,7 +14068,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" s="5" t="s">
         <v>876</v>
       </c>
@@ -13887,7 +14097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>878</v>
       </c>
@@ -13916,7 +14126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" s="5" t="s">
         <v>880</v>
       </c>
@@ -13945,7 +14155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" s="8" t="s">
         <v>882</v>
       </c>
@@ -13974,7 +14184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" s="5" t="s">
         <v>885</v>
       </c>
@@ -14003,7 +14213,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>888</v>
       </c>
@@ -14032,7 +14242,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" s="5" t="s">
         <v>890</v>
       </c>
@@ -14061,7 +14271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>893</v>
       </c>
@@ -14090,7 +14300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" s="5" t="s">
         <v>898</v>
       </c>
@@ -14119,7 +14329,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>900</v>
       </c>
@@ -14148,7 +14358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="5" t="s">
         <v>903</v>
       </c>
@@ -14177,7 +14387,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="8" t="s">
         <v>906</v>
       </c>
@@ -14206,7 +14416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="5" t="s">
         <v>909</v>
       </c>
@@ -14235,7 +14445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>911</v>
       </c>
@@ -14264,7 +14474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345" s="5" t="s">
         <v>914</v>
       </c>
@@ -14293,7 +14503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>916</v>
       </c>
@@ -14322,7 +14532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A347" s="5" t="s">
         <v>918</v>
       </c>
@@ -14351,7 +14561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>920</v>
       </c>
@@ -14380,7 +14590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" s="5" t="s">
         <v>923</v>
       </c>
@@ -14409,7 +14619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>925</v>
       </c>
@@ -14438,7 +14648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" s="5" t="s">
         <v>927</v>
       </c>
@@ -14467,7 +14677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>929</v>
       </c>
@@ -14496,7 +14706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="5" t="s">
         <v>931</v>
       </c>
@@ -14534,18 +14744,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K355"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" customWidth="1"/>
+    <col min="4" max="4" width="24.1796875" customWidth="1"/>
     <col min="5" max="5" width="27" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="9" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="11" width="15.7109375" style="21" customWidth="1"/>
+    <col min="8" max="11" width="15.7265625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14580,7 +14790,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>180</v>
       </c>
@@ -14616,7 +14826,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>498</v>
       </c>
@@ -14652,7 +14862,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>188</v>
       </c>
@@ -14688,7 +14898,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>183</v>
       </c>
@@ -14724,7 +14934,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>127</v>
       </c>
@@ -14760,7 +14970,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>280</v>
       </c>
@@ -14796,7 +15006,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>294</v>
       </c>
@@ -14832,7 +15042,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>332</v>
       </c>
@@ -14868,7 +15078,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>472</v>
       </c>
@@ -14904,7 +15114,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>553</v>
       </c>
@@ -14940,7 +15150,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>528</v>
       </c>
@@ -14976,7 +15186,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>193</v>
       </c>
@@ -15012,7 +15222,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>360</v>
       </c>
@@ -15048,7 +15258,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>548</v>
       </c>
@@ -15084,7 +15294,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>366</v>
       </c>
@@ -15120,7 +15330,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>299</v>
       </c>
@@ -15156,7 +15366,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>731</v>
       </c>
@@ -15192,7 +15402,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>731</v>
       </c>
@@ -15228,7 +15438,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>736</v>
       </c>
@@ -15264,7 +15474,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>736</v>
       </c>
@@ -15300,7 +15510,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>832</v>
       </c>
@@ -15336,7 +15546,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>644</v>
       </c>
@@ -15372,7 +15582,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>787</v>
       </c>
@@ -15408,7 +15618,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>443</v>
       </c>
@@ -15444,7 +15654,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>622</v>
       </c>
@@ -15480,7 +15690,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>102</v>
       </c>
@@ -15516,7 +15726,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>882</v>
       </c>
@@ -15552,7 +15762,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>906</v>
       </c>
@@ -15588,7 +15798,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>425</v>
       </c>
@@ -15624,7 +15834,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>174</v>
       </c>
@@ -15660,7 +15870,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>171</v>
       </c>
@@ -15696,7 +15906,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>147</v>
       </c>
@@ -15732,7 +15942,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>631</v>
       </c>
@@ -15768,7 +15978,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>900</v>
       </c>
@@ -15804,7 +16014,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>804</v>
       </c>
@@ -15840,7 +16050,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>597</v>
       </c>
@@ -15876,7 +16086,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>573</v>
       </c>
@@ -15912,7 +16122,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>327</v>
       </c>
@@ -15948,7 +16158,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>161</v>
       </c>
@@ -15984,7 +16194,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>408</v>
       </c>
@@ -16020,7 +16230,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>818</v>
       </c>
@@ -16056,7 +16266,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>813</v>
       </c>
@@ -16092,7 +16302,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>135</v>
       </c>
@@ -16128,7 +16338,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>387</v>
       </c>
@@ -16164,7 +16374,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>458</v>
       </c>
@@ -16200,7 +16410,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>617</v>
       </c>
@@ -16236,7 +16446,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>357</v>
       </c>
@@ -16272,7 +16482,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>270</v>
       </c>
@@ -16308,7 +16518,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>931</v>
       </c>
@@ -16344,7 +16554,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -16380,7 +16590,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>762</v>
       </c>
@@ -16412,7 +16622,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>329</v>
       </c>
@@ -16448,7 +16658,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>588</v>
       </c>
@@ -16484,43 +16694,43 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
         <v>702</v>
       </c>
       <c r="B55" s="2">
         <f>VLOOKUP(A55,'Candidatos E-26 ALC'!A255:I606,8,FALSE)</f>
         <v>36917</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" s="5">
-        <v>0</v>
-      </c>
-      <c r="H55" s="23" t="s">
+      <c r="F55" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="24" t="s">
         <v>1151</v>
       </c>
-      <c r="I55" s="23" t="s">
+      <c r="I55" s="24" t="s">
         <v>1152</v>
       </c>
-      <c r="J55" s="23" t="s">
+      <c r="J55" s="24" t="s">
         <v>1153</v>
       </c>
-      <c r="K55" s="23" t="s">
+      <c r="K55" s="24" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>700</v>
       </c>
@@ -16554,7 +16764,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>309</v>
       </c>
@@ -16590,7 +16800,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>83</v>
       </c>
@@ -16626,7 +16836,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>289</v>
       </c>
@@ -16662,7 +16872,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>191</v>
       </c>
@@ -16698,7 +16908,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>198</v>
       </c>
@@ -16734,7 +16944,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>464</v>
       </c>
@@ -16770,7 +16980,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>455</v>
       </c>
@@ -16806,7 +17016,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>422</v>
       </c>
@@ -16842,7 +17052,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>647</v>
       </c>
@@ -16878,7 +17088,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>167</v>
       </c>
@@ -16914,7 +17124,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>680</v>
       </c>
@@ -16948,7 +17158,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
         <v>720</v>
       </c>
@@ -16984,7 +17194,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>22</v>
       </c>
@@ -17020,7 +17230,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>105</v>
       </c>
@@ -17056,7 +17266,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="8" t="s">
         <v>670</v>
       </c>
@@ -17084,7 +17294,7 @@
       <c r="J71" s="18"/>
       <c r="K71" s="24"/>
     </row>
-    <row r="72" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>392</v>
       </c>
@@ -17116,7 +17326,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>865</v>
       </c>
@@ -17152,7 +17362,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>522</v>
       </c>
@@ -17188,7 +17398,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>728</v>
       </c>
@@ -17222,7 +17432,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>86</v>
       </c>
@@ -17256,7 +17466,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>835</v>
       </c>
@@ -17292,7 +17502,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>878</v>
       </c>
@@ -17328,7 +17538,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="8" t="s">
         <v>379</v>
       </c>
@@ -17364,7 +17574,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>677</v>
       </c>
@@ -17387,12 +17597,20 @@
       <c r="G80" s="5">
         <v>0</v>
       </c>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-    </row>
-    <row r="81" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H80" s="23" t="s">
+        <v>1245</v>
+      </c>
+      <c r="I80" s="23" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J80" s="23" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K80" s="23" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>325</v>
       </c>
@@ -17415,12 +17633,20 @@
       <c r="G81" s="2">
         <v>0</v>
       </c>
-      <c r="H81" s="16"/>
-      <c r="I81" s="16"/>
-      <c r="J81" s="16"/>
-      <c r="K81" s="16"/>
-    </row>
-    <row r="82" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H81" s="22" t="s">
+        <v>1248</v>
+      </c>
+      <c r="I81" s="22" t="s">
+        <v>1247</v>
+      </c>
+      <c r="J81" s="22" t="s">
+        <v>1249</v>
+      </c>
+      <c r="K81" s="22" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>231</v>
       </c>
@@ -17443,12 +17669,20 @@
       <c r="G82" s="5">
         <v>0</v>
       </c>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
-      <c r="J82" s="17"/>
-      <c r="K82" s="20"/>
-    </row>
-    <row r="83" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H82" s="23" t="s">
+        <v>1250</v>
+      </c>
+      <c r="I82" s="23" t="s">
+        <v>1252</v>
+      </c>
+      <c r="J82" s="23" t="s">
+        <v>1251</v>
+      </c>
+      <c r="K82" s="23" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>385</v>
       </c>
@@ -17471,12 +17705,20 @@
       <c r="G83" s="2">
         <v>0</v>
       </c>
-      <c r="H83" s="16"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="16"/>
-      <c r="K83" s="16"/>
-    </row>
-    <row r="84" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H83" s="22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="I83" s="22" t="s">
+        <v>1257</v>
+      </c>
+      <c r="J83" s="22" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K83" s="22" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>201</v>
       </c>
@@ -17499,12 +17741,20 @@
       <c r="G84" s="5">
         <v>0</v>
       </c>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="17"/>
-      <c r="K84" s="17"/>
-    </row>
-    <row r="85" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H84" s="23" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I84" s="23" t="s">
+        <v>1261</v>
+      </c>
+      <c r="J84" s="23" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K84" s="23" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>495</v>
       </c>
@@ -17527,12 +17777,20 @@
       <c r="G85" s="5">
         <v>0</v>
       </c>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-      <c r="J85" s="17"/>
-      <c r="K85" s="17"/>
-    </row>
-    <row r="86" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H85" s="23" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I85" s="23" t="s">
+        <v>1264</v>
+      </c>
+      <c r="J85" s="23" t="s">
+        <v>1265</v>
+      </c>
+      <c r="K85" s="23" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>26</v>
       </c>
@@ -17555,12 +17813,18 @@
       <c r="G86" s="2">
         <v>0</v>
       </c>
-      <c r="H86" s="22"/>
-      <c r="I86" s="16"/>
+      <c r="H86" s="22" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I86" s="22" t="s">
+        <v>1268</v>
+      </c>
       <c r="J86" s="16"/>
-      <c r="K86" s="22"/>
-    </row>
-    <row r="87" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K86" s="22" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>885</v>
       </c>
@@ -17583,12 +17847,20 @@
       <c r="G87" s="5">
         <v>0</v>
       </c>
-      <c r="H87" s="17"/>
-      <c r="I87" s="17"/>
-      <c r="J87" s="17"/>
-      <c r="K87" s="17"/>
-    </row>
-    <row r="88" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H87" s="23" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I87" s="23" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J87" s="23" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K87" s="23" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>723</v>
       </c>
@@ -17611,12 +17883,20 @@
       <c r="G88" s="5">
         <v>0</v>
       </c>
-      <c r="H88" s="17"/>
-      <c r="I88" s="17"/>
-      <c r="J88" s="17"/>
-      <c r="K88" s="17"/>
-    </row>
-    <row r="89" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H88" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I88" s="28" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J88" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="K88" s="23" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>382</v>
       </c>
@@ -17639,12 +17919,20 @@
       <c r="G89" s="5">
         <v>0</v>
       </c>
-      <c r="H89" s="17"/>
-      <c r="I89" s="17"/>
-      <c r="J89" s="17"/>
-      <c r="K89" s="17"/>
-    </row>
-    <row r="90" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H89" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I89" s="23" t="s">
+        <v>1279</v>
+      </c>
+      <c r="J89" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="K89" s="23" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>441</v>
       </c>
@@ -17667,12 +17955,20 @@
       <c r="G90" s="2">
         <v>0</v>
       </c>
-      <c r="H90" s="16"/>
-      <c r="I90" s="16"/>
-      <c r="J90" s="16"/>
-      <c r="K90" s="16"/>
-    </row>
-    <row r="91" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H90" s="22" t="s">
+        <v>1282</v>
+      </c>
+      <c r="I90" s="22" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J90" s="22" t="s">
+        <v>1284</v>
+      </c>
+      <c r="K90" s="22" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>259</v>
       </c>
@@ -17695,12 +17991,20 @@
       <c r="G91" s="5">
         <v>0</v>
       </c>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
-      <c r="J91" s="17"/>
-      <c r="K91" s="17"/>
-    </row>
-    <row r="92" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H91" s="23" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I91" s="23" t="s">
+        <v>1287</v>
+      </c>
+      <c r="J91" s="23" t="s">
+        <v>1288</v>
+      </c>
+      <c r="K91" s="23" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>807</v>
       </c>
@@ -17723,12 +18027,20 @@
       <c r="G92" s="2">
         <v>0</v>
       </c>
-      <c r="H92" s="16"/>
-      <c r="I92" s="16"/>
-      <c r="J92" s="16"/>
-      <c r="K92" s="16"/>
-    </row>
-    <row r="93" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H92" s="22" t="s">
+        <v>1289</v>
+      </c>
+      <c r="I92" s="22" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J92" s="22" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K92" s="22" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>880</v>
       </c>
@@ -17751,12 +18063,20 @@
       <c r="G93" s="5">
         <v>0</v>
       </c>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
-      <c r="J93" s="17"/>
-      <c r="K93" s="17"/>
-    </row>
-    <row r="94" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H93" s="23" t="s">
+        <v>1293</v>
+      </c>
+      <c r="I93" s="23" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J93" s="23" t="s">
+        <v>1296</v>
+      </c>
+      <c r="K93" s="23" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>292</v>
       </c>
@@ -17782,9 +18102,11 @@
       <c r="H94" s="17"/>
       <c r="I94" s="17"/>
       <c r="J94" s="17"/>
-      <c r="K94" s="17"/>
-    </row>
-    <row r="95" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K94" s="23" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>138</v>
       </c>
@@ -17807,12 +18129,14 @@
       <c r="G95" s="2">
         <v>0</v>
       </c>
-      <c r="H95" s="16"/>
+      <c r="H95" s="22" t="s">
+        <v>1298</v>
+      </c>
       <c r="I95" s="16"/>
       <c r="J95" s="16"/>
       <c r="K95" s="16"/>
     </row>
-    <row r="96" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>862</v>
       </c>
@@ -17835,12 +18159,16 @@
       <c r="G96" s="2">
         <v>0</v>
       </c>
-      <c r="H96" s="16"/>
-      <c r="I96" s="16"/>
+      <c r="H96" s="22" t="s">
+        <v>1309</v>
+      </c>
+      <c r="I96" s="22" t="s">
+        <v>1310</v>
+      </c>
       <c r="J96" s="16"/>
       <c r="K96" s="16"/>
     </row>
-    <row r="97" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>556</v>
       </c>
@@ -17863,12 +18191,16 @@
       <c r="G97" s="2">
         <v>0</v>
       </c>
-      <c r="H97" s="16"/>
+      <c r="H97" s="22" t="s">
+        <v>1307</v>
+      </c>
       <c r="I97" s="16"/>
       <c r="J97" s="16"/>
-      <c r="K97" s="16"/>
-    </row>
-    <row r="98" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K97" s="22" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>273</v>
       </c>
@@ -17896,7 +18228,7 @@
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
     </row>
-    <row r="99" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>602</v>
       </c>
@@ -17919,12 +18251,20 @@
       <c r="G99" s="5">
         <v>0</v>
       </c>
-      <c r="H99" s="17"/>
-      <c r="I99" s="17"/>
-      <c r="J99" s="17"/>
-      <c r="K99" s="17"/>
-    </row>
-    <row r="100" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H99" s="23" t="s">
+        <v>1303</v>
+      </c>
+      <c r="I99" s="23" t="s">
+        <v>1304</v>
+      </c>
+      <c r="J99" s="23" t="s">
+        <v>1305</v>
+      </c>
+      <c r="K99" s="23" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>433</v>
       </c>
@@ -17947,12 +18287,20 @@
       <c r="G100" s="5">
         <v>0</v>
       </c>
-      <c r="H100" s="17"/>
-      <c r="I100" s="17"/>
-      <c r="J100" s="17"/>
-      <c r="K100" s="17"/>
-    </row>
-    <row r="101" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H100" s="23" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I100" s="23" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J100" s="23" t="s">
+        <v>1302</v>
+      </c>
+      <c r="K100" s="23" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>739</v>
       </c>
@@ -17980,7 +18328,7 @@
       <c r="J101" s="16"/>
       <c r="K101" s="16"/>
     </row>
-    <row r="102" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
         <v>739</v>
       </c>
@@ -18008,7 +18356,7 @@
       <c r="J102" s="17"/>
       <c r="K102" s="17"/>
     </row>
-    <row r="103" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>351</v>
       </c>
@@ -18036,7 +18384,7 @@
       <c r="J103" s="16"/>
       <c r="K103" s="16"/>
     </row>
-    <row r="104" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>97</v>
       </c>
@@ -18064,7 +18412,7 @@
       <c r="J104" s="17"/>
       <c r="K104" s="17"/>
     </row>
-    <row r="105" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>448</v>
       </c>
@@ -18092,7 +18440,7 @@
       <c r="J105" s="17"/>
       <c r="K105" s="17"/>
     </row>
-    <row r="106" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>394</v>
       </c>
@@ -18120,7 +18468,7 @@
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
     </row>
-    <row r="107" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>914</v>
       </c>
@@ -18148,7 +18496,7 @@
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
     </row>
-    <row r="108" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>614</v>
       </c>
@@ -18176,7 +18524,7 @@
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
     </row>
-    <row r="109" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>810</v>
       </c>
@@ -18204,7 +18552,7 @@
       <c r="J109" s="17"/>
       <c r="K109" s="17"/>
     </row>
-    <row r="110" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
         <v>177</v>
       </c>
@@ -18232,7 +18580,7 @@
       <c r="J110" s="17"/>
       <c r="K110" s="17"/>
     </row>
-    <row r="111" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
         <v>576</v>
       </c>
@@ -18260,7 +18608,7 @@
       <c r="J111" s="17"/>
       <c r="K111" s="17"/>
     </row>
-    <row r="112" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>638</v>
       </c>
@@ -18288,7 +18636,7 @@
       <c r="J112" s="16"/>
       <c r="K112" s="16"/>
     </row>
-    <row r="113" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>570</v>
       </c>
@@ -18316,7 +18664,7 @@
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
     </row>
-    <row r="114" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
         <v>415</v>
       </c>
@@ -18344,7 +18692,7 @@
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
     </row>
-    <row r="115" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>525</v>
       </c>
@@ -18372,7 +18720,7 @@
       <c r="J115" s="16"/>
       <c r="K115" s="16"/>
     </row>
-    <row r="116" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
         <v>369</v>
       </c>
@@ -18400,7 +18748,7 @@
       <c r="J116" s="17"/>
       <c r="K116" s="17"/>
     </row>
-    <row r="117" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>565</v>
       </c>
@@ -18428,7 +18776,7 @@
       <c r="J117" s="17"/>
       <c r="K117" s="17"/>
     </row>
-    <row r="118" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>755</v>
       </c>
@@ -18456,7 +18804,7 @@
       <c r="J118" s="16"/>
       <c r="K118" s="16"/>
     </row>
-    <row r="119" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
         <v>561</v>
       </c>
@@ -18484,7 +18832,7 @@
       <c r="J119" s="17"/>
       <c r="K119" s="17"/>
     </row>
-    <row r="120" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>579</v>
       </c>
@@ -18512,7 +18860,7 @@
       <c r="J120" s="16"/>
       <c r="K120" s="16"/>
     </row>
-    <row r="121" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>396</v>
       </c>
@@ -18540,7 +18888,7 @@
       <c r="J121" s="16"/>
       <c r="K121" s="16"/>
     </row>
-    <row r="122" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>363</v>
       </c>
@@ -18568,7 +18916,7 @@
       <c r="J122" s="17"/>
       <c r="K122" s="17"/>
     </row>
-    <row r="123" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>532</v>
       </c>
@@ -18596,7 +18944,7 @@
       <c r="J123" s="17"/>
       <c r="K123" s="17"/>
     </row>
-    <row r="124" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>55</v>
       </c>
@@ -18624,7 +18972,7 @@
       <c r="J124" s="17"/>
       <c r="K124" s="17"/>
     </row>
-    <row r="125" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>843</v>
       </c>
@@ -18652,7 +19000,7 @@
       <c r="J125" s="17"/>
       <c r="K125" s="17"/>
     </row>
-    <row r="126" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>140</v>
       </c>
@@ -18680,7 +19028,7 @@
       <c r="J126" s="17"/>
       <c r="K126" s="17"/>
     </row>
-    <row r="127" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>302</v>
       </c>
@@ -18708,7 +19056,7 @@
       <c r="J127" s="17"/>
       <c r="K127" s="17"/>
     </row>
-    <row r="128" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
         <v>438</v>
       </c>
@@ -18736,7 +19084,7 @@
       <c r="J128" s="17"/>
       <c r="K128" s="17"/>
     </row>
-    <row r="129" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
         <v>872</v>
       </c>
@@ -18764,7 +19112,7 @@
       <c r="J129" s="17"/>
       <c r="K129" s="17"/>
     </row>
-    <row r="130" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>75</v>
       </c>
@@ -18792,7 +19140,7 @@
       <c r="J130" s="16"/>
       <c r="K130" s="16"/>
     </row>
-    <row r="131" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>654</v>
       </c>
@@ -18820,7 +19168,7 @@
       <c r="J131" s="16"/>
       <c r="K131" s="16"/>
     </row>
-    <row r="132" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>508</v>
       </c>
@@ -18848,7 +19196,7 @@
       <c r="J132" s="17"/>
       <c r="K132" s="17"/>
     </row>
-    <row r="133" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>225</v>
       </c>
@@ -18876,7 +19224,7 @@
       <c r="J133" s="17"/>
       <c r="K133" s="17"/>
     </row>
-    <row r="134" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>222</v>
       </c>
@@ -18904,7 +19252,7 @@
       <c r="J134" s="16"/>
       <c r="K134" s="16"/>
     </row>
-    <row r="135" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>867</v>
       </c>
@@ -18932,7 +19280,7 @@
       <c r="J135" s="16"/>
       <c r="K135" s="16"/>
     </row>
-    <row r="136" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>58</v>
       </c>
@@ -18960,7 +19308,7 @@
       <c r="J136" s="16"/>
       <c r="K136" s="16"/>
     </row>
-    <row r="137" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
         <v>349</v>
       </c>
@@ -18988,7 +19336,7 @@
       <c r="J137" s="17"/>
       <c r="K137" s="17"/>
     </row>
-    <row r="138" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
         <v>860</v>
       </c>
@@ -19016,7 +19364,7 @@
       <c r="J138" s="17"/>
       <c r="K138" s="17"/>
     </row>
-    <row r="139" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>484</v>
       </c>
@@ -19044,7 +19392,7 @@
       <c r="J139" s="16"/>
       <c r="K139" s="16"/>
     </row>
-    <row r="140" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
         <v>219</v>
       </c>
@@ -19072,7 +19420,7 @@
       <c r="J140" s="17"/>
       <c r="K140" s="17"/>
     </row>
-    <row r="141" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>709</v>
       </c>
@@ -19100,7 +19448,7 @@
       <c r="J141" s="16"/>
       <c r="K141" s="16"/>
     </row>
-    <row r="142" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
         <v>121</v>
       </c>
@@ -19128,7 +19476,7 @@
       <c r="J142" s="17"/>
       <c r="K142" s="17"/>
     </row>
-    <row r="143" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>627</v>
       </c>
@@ -19156,7 +19504,7 @@
       <c r="J143" s="16"/>
       <c r="K143" s="16"/>
     </row>
-    <row r="144" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>130</v>
       </c>
@@ -19184,7 +19532,7 @@
       <c r="J144" s="17"/>
       <c r="K144" s="17"/>
     </row>
-    <row r="145" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>371</v>
       </c>
@@ -19212,7 +19560,7 @@
       <c r="J145" s="16"/>
       <c r="K145" s="16"/>
     </row>
-    <row r="146" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
         <v>67</v>
       </c>
@@ -19240,7 +19588,7 @@
       <c r="J146" s="17"/>
       <c r="K146" s="17"/>
     </row>
-    <row r="147" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
         <v>152</v>
       </c>
@@ -19268,7 +19616,7 @@
       <c r="J147" s="17"/>
       <c r="K147" s="17"/>
     </row>
-    <row r="148" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>446</v>
       </c>
@@ -19296,7 +19644,7 @@
       <c r="J148" s="16"/>
       <c r="K148" s="16"/>
     </row>
-    <row r="149" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>857</v>
       </c>
@@ -19324,7 +19672,7 @@
       <c r="J149" s="16"/>
       <c r="K149" s="16"/>
     </row>
-    <row r="150" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
         <v>250</v>
       </c>
@@ -19352,7 +19700,7 @@
       <c r="J150" s="17"/>
       <c r="K150" s="17"/>
     </row>
-    <row r="151" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>893</v>
       </c>
@@ -19380,7 +19728,7 @@
       <c r="J151" s="16"/>
       <c r="K151" s="16"/>
     </row>
-    <row r="152" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
         <v>420</v>
       </c>
@@ -19408,7 +19756,7 @@
       <c r="J152" s="17"/>
       <c r="K152" s="17"/>
     </row>
-    <row r="153" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>510</v>
       </c>
@@ -19436,7 +19784,7 @@
       <c r="J153" s="16"/>
       <c r="K153" s="16"/>
     </row>
-    <row r="154" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>403</v>
       </c>
@@ -19464,7 +19812,7 @@
       <c r="J154" s="16"/>
       <c r="K154" s="16"/>
     </row>
-    <row r="155" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>355</v>
       </c>
@@ -19492,7 +19840,7 @@
       <c r="J155" s="16"/>
       <c r="K155" s="16"/>
     </row>
-    <row r="156" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
         <v>855</v>
       </c>
@@ -19520,7 +19868,7 @@
       <c r="J156" s="17"/>
       <c r="K156" s="17"/>
     </row>
-    <row r="157" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
         <v>673</v>
       </c>
@@ -19548,7 +19896,7 @@
       <c r="J157" s="17"/>
       <c r="K157" s="17"/>
     </row>
-    <row r="158" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>430</v>
       </c>
@@ -19576,7 +19924,7 @@
       <c r="J158" s="16"/>
       <c r="K158" s="16"/>
     </row>
-    <row r="159" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>642</v>
       </c>
@@ -19604,7 +19952,7 @@
       <c r="J159" s="16"/>
       <c r="K159" s="16"/>
     </row>
-    <row r="160" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>925</v>
       </c>
@@ -19632,7 +19980,7 @@
       <c r="J160" s="16"/>
       <c r="K160" s="16"/>
     </row>
-    <row r="161" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
         <v>890</v>
       </c>
@@ -19660,7 +20008,7 @@
       <c r="J161" s="17"/>
       <c r="K161" s="17"/>
     </row>
-    <row r="162" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>346</v>
       </c>
@@ -19688,7 +20036,7 @@
       <c r="J162" s="16"/>
       <c r="K162" s="16"/>
     </row>
-    <row r="163" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>312</v>
       </c>
@@ -19716,7 +20064,7 @@
       <c r="J163" s="16"/>
       <c r="K163" s="16"/>
     </row>
-    <row r="164" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>742</v>
       </c>
@@ -19744,7 +20092,7 @@
       <c r="J164" s="16"/>
       <c r="K164" s="16"/>
     </row>
-    <row r="165" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
         <v>742</v>
       </c>
@@ -19772,7 +20120,7 @@
       <c r="J165" s="17"/>
       <c r="K165" s="17"/>
     </row>
-    <row r="166" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>478</v>
       </c>
@@ -19800,7 +20148,7 @@
       <c r="J166" s="17"/>
       <c r="K166" s="17"/>
     </row>
-    <row r="167" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>541</v>
       </c>
@@ -19828,7 +20176,7 @@
       <c r="J167" s="16"/>
       <c r="K167" s="16"/>
     </row>
-    <row r="168" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
         <v>340</v>
       </c>
@@ -19856,7 +20204,7 @@
       <c r="J168" s="17"/>
       <c r="K168" s="17"/>
     </row>
-    <row r="169" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
         <v>286</v>
       </c>
@@ -19884,7 +20232,7 @@
       <c r="J169" s="17"/>
       <c r="K169" s="17"/>
     </row>
-    <row r="170" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>625</v>
       </c>
@@ -19912,7 +20260,7 @@
       <c r="J170" s="17"/>
       <c r="K170" s="17"/>
     </row>
-    <row r="171" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
         <v>636</v>
       </c>
@@ -19940,7 +20288,7 @@
       <c r="J171" s="17"/>
       <c r="K171" s="17"/>
     </row>
-    <row r="172" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
         <v>830</v>
       </c>
@@ -19968,7 +20316,7 @@
       <c r="J172" s="17"/>
       <c r="K172" s="17"/>
     </row>
-    <row r="173" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>64</v>
       </c>
@@ -19996,7 +20344,7 @@
       <c r="J173" s="16"/>
       <c r="K173" s="16"/>
     </row>
-    <row r="174" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
         <v>593</v>
       </c>
@@ -20024,7 +20372,7 @@
       <c r="J174" s="17"/>
       <c r="K174" s="17"/>
     </row>
-    <row r="175" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
         <v>903</v>
       </c>
@@ -20052,7 +20400,7 @@
       <c r="J175" s="17"/>
       <c r="K175" s="17"/>
     </row>
-    <row r="176" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>133</v>
       </c>
@@ -20080,7 +20428,7 @@
       <c r="J176" s="16"/>
       <c r="K176" s="16"/>
     </row>
-    <row r="177" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
         <v>461</v>
       </c>
@@ -20108,7 +20456,7 @@
       <c r="J177" s="17"/>
       <c r="K177" s="17"/>
     </row>
-    <row r="178" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>321</v>
       </c>
@@ -20136,7 +20484,7 @@
       <c r="J178" s="16"/>
       <c r="K178" s="16"/>
     </row>
-    <row r="179" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>612</v>
       </c>
@@ -20164,7 +20512,7 @@
       <c r="J179" s="16"/>
       <c r="K179" s="16"/>
     </row>
-    <row r="180" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>145</v>
       </c>
@@ -20192,7 +20540,7 @@
       <c r="J180" s="16"/>
       <c r="K180" s="16"/>
     </row>
-    <row r="181" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
         <v>707</v>
       </c>
@@ -20220,7 +20568,7 @@
       <c r="J181" s="17"/>
       <c r="K181" s="17"/>
     </row>
-    <row r="182" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>551</v>
       </c>
@@ -20248,7 +20596,7 @@
       <c r="J182" s="16"/>
       <c r="K182" s="16"/>
     </row>
-    <row r="183" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>778</v>
       </c>
@@ -20276,7 +20624,7 @@
       <c r="J183" s="17"/>
       <c r="K183" s="17"/>
     </row>
-    <row r="184" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>418</v>
       </c>
@@ -20304,7 +20652,7 @@
       <c r="J184" s="16"/>
       <c r="K184" s="16"/>
     </row>
-    <row r="185" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>515</v>
       </c>
@@ -20332,7 +20680,7 @@
       <c r="J185" s="16"/>
       <c r="K185" s="16"/>
     </row>
-    <row r="186" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="5" t="s">
         <v>297</v>
       </c>
@@ -20360,7 +20708,7 @@
       <c r="J186" s="17"/>
       <c r="K186" s="17"/>
     </row>
-    <row r="187" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>586</v>
       </c>
@@ -20388,7 +20736,7 @@
       <c r="J187" s="16"/>
       <c r="K187" s="16"/>
     </row>
-    <row r="188" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>705</v>
       </c>
@@ -20416,7 +20764,7 @@
       <c r="J188" s="16"/>
       <c r="K188" s="16"/>
     </row>
-    <row r="189" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
         <v>513</v>
       </c>
@@ -20444,7 +20792,7 @@
       <c r="J189" s="17"/>
       <c r="K189" s="17"/>
     </row>
-    <row r="190" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5" t="s">
         <v>486</v>
       </c>
@@ -20472,7 +20820,7 @@
       <c r="J190" s="17"/>
       <c r="K190" s="17"/>
     </row>
-    <row r="191" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>695</v>
       </c>
@@ -20500,7 +20848,7 @@
       <c r="J191" s="16"/>
       <c r="K191" s="16"/>
     </row>
-    <row r="192" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="5" t="s">
         <v>344</v>
       </c>
@@ -20528,7 +20876,7 @@
       <c r="J192" s="17"/>
       <c r="K192" s="17"/>
     </row>
-    <row r="193" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>413</v>
       </c>
@@ -20556,7 +20904,7 @@
       <c r="J193" s="16"/>
       <c r="K193" s="16"/>
     </row>
-    <row r="194" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="5" t="s">
         <v>502</v>
       </c>
@@ -20584,7 +20932,7 @@
       <c r="J194" s="17"/>
       <c r="K194" s="17"/>
     </row>
-    <row r="195" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>316</v>
       </c>
@@ -20612,7 +20960,7 @@
       <c r="J195" s="16"/>
       <c r="K195" s="16"/>
     </row>
-    <row r="196" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="5" t="s">
         <v>649</v>
       </c>
@@ -20640,7 +20988,7 @@
       <c r="J196" s="17"/>
       <c r="K196" s="17"/>
     </row>
-    <row r="197" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>493</v>
       </c>
@@ -20668,7 +21016,7 @@
       <c r="J197" s="16"/>
       <c r="K197" s="16"/>
     </row>
-    <row r="198" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>468</v>
       </c>
@@ -20696,7 +21044,7 @@
       <c r="J198" s="16"/>
       <c r="K198" s="16"/>
     </row>
-    <row r="199" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>261</v>
       </c>
@@ -20724,7 +21072,7 @@
       <c r="J199" s="16"/>
       <c r="K199" s="16"/>
     </row>
-    <row r="200" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>488</v>
       </c>
@@ -20752,7 +21100,7 @@
       <c r="J200" s="16"/>
       <c r="K200" s="16"/>
     </row>
-    <row r="201" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
         <v>314</v>
       </c>
@@ -20780,7 +21128,7 @@
       <c r="J201" s="17"/>
       <c r="K201" s="17"/>
     </row>
-    <row r="202" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>519</v>
       </c>
@@ -20808,7 +21156,7 @@
       <c r="J202" s="16"/>
       <c r="K202" s="16"/>
     </row>
-    <row r="203" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>115</v>
       </c>
@@ -20836,7 +21184,7 @@
       <c r="J203" s="16"/>
       <c r="K203" s="16"/>
     </row>
-    <row r="204" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>186</v>
       </c>
@@ -20864,7 +21212,7 @@
       <c r="J204" s="16"/>
       <c r="K204" s="16"/>
     </row>
-    <row r="205" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>530</v>
       </c>
@@ -20892,7 +21240,7 @@
       <c r="J205" s="16"/>
       <c r="K205" s="16"/>
     </row>
-    <row r="206" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>480</v>
       </c>
@@ -20920,7 +21268,7 @@
       <c r="J206" s="16"/>
       <c r="K206" s="16"/>
     </row>
-    <row r="207" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="5" t="s">
         <v>582</v>
       </c>
@@ -20948,7 +21296,7 @@
       <c r="J207" s="17"/>
       <c r="K207" s="17"/>
     </row>
-    <row r="208" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="5" t="s">
         <v>215</v>
       </c>
@@ -20976,7 +21324,7 @@
       <c r="J208" s="17"/>
       <c r="K208" s="17"/>
     </row>
-    <row r="209" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
         <v>72</v>
       </c>
@@ -21004,7 +21352,7 @@
       <c r="J209" s="17"/>
       <c r="K209" s="17"/>
     </row>
-    <row r="210" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="5" t="s">
         <v>718</v>
       </c>
@@ -21032,7 +21380,7 @@
       <c r="J210" s="17"/>
       <c r="K210" s="17"/>
     </row>
-    <row r="211" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
         <v>629</v>
       </c>
@@ -21060,7 +21408,7 @@
       <c r="J211" s="17"/>
       <c r="K211" s="17"/>
     </row>
-    <row r="212" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>353</v>
       </c>
@@ -21088,7 +21436,7 @@
       <c r="J212" s="17"/>
       <c r="K212" s="17"/>
     </row>
-    <row r="213" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>595</v>
       </c>
@@ -21116,7 +21464,7 @@
       <c r="J213" s="16"/>
       <c r="K213" s="16"/>
     </row>
-    <row r="214" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>253</v>
       </c>
@@ -21144,7 +21492,7 @@
       <c r="J214" s="16"/>
       <c r="K214" s="16"/>
     </row>
-    <row r="215" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>691</v>
       </c>
@@ -21172,7 +21520,7 @@
       <c r="J215" s="16"/>
       <c r="K215" s="16"/>
     </row>
-    <row r="216" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="5" t="s">
         <v>158</v>
       </c>
@@ -21200,7 +21548,7 @@
       <c r="J216" s="17"/>
       <c r="K216" s="17"/>
     </row>
-    <row r="217" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>888</v>
       </c>
@@ -21228,7 +21576,7 @@
       <c r="J217" s="16"/>
       <c r="K217" s="16"/>
     </row>
-    <row r="218" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>283</v>
       </c>
@@ -21256,7 +21604,7 @@
       <c r="J218" s="16"/>
       <c r="K218" s="16"/>
     </row>
-    <row r="219" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="5" t="s">
         <v>61</v>
       </c>
@@ -21284,7 +21632,7 @@
       <c r="J219" s="17"/>
       <c r="K219" s="17"/>
     </row>
-    <row r="220" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="5" t="s">
         <v>78</v>
       </c>
@@ -21312,7 +21660,7 @@
       <c r="J220" s="17"/>
       <c r="K220" s="17"/>
     </row>
-    <row r="221" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="5" t="s">
         <v>323</v>
       </c>
@@ -21340,7 +21688,7 @@
       <c r="J221" s="17"/>
       <c r="K221" s="17"/>
     </row>
-    <row r="222" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>744</v>
       </c>
@@ -21368,7 +21716,7 @@
       <c r="J222" s="16"/>
       <c r="K222" s="16"/>
     </row>
-    <row r="223" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="5" t="s">
         <v>744</v>
       </c>
@@ -21396,7 +21744,7 @@
       <c r="J223" s="17"/>
       <c r="K223" s="17"/>
     </row>
-    <row r="224" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>228</v>
       </c>
@@ -21424,7 +21772,7 @@
       <c r="J224" s="16"/>
       <c r="K224" s="16"/>
     </row>
-    <row r="225" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>766</v>
       </c>
@@ -21452,7 +21800,7 @@
       <c r="J225" s="16"/>
       <c r="K225" s="16"/>
     </row>
-    <row r="226" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="5" t="s">
         <v>244</v>
       </c>
@@ -21480,7 +21828,7 @@
       <c r="J226" s="17"/>
       <c r="K226" s="17"/>
     </row>
-    <row r="227" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
         <v>517</v>
       </c>
@@ -21508,7 +21856,7 @@
       <c r="J227" s="17"/>
       <c r="K227" s="17"/>
     </row>
-    <row r="228" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="5" t="s">
         <v>470</v>
       </c>
@@ -21536,7 +21884,7 @@
       <c r="J228" s="17"/>
       <c r="K228" s="17"/>
     </row>
-    <row r="229" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="5" t="s">
         <v>263</v>
       </c>
@@ -21564,7 +21912,7 @@
       <c r="J229" s="17"/>
       <c r="K229" s="17"/>
     </row>
-    <row r="230" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>662</v>
       </c>
@@ -21592,7 +21940,7 @@
       <c r="J230" s="16"/>
       <c r="K230" s="16"/>
     </row>
-    <row r="231" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="5" t="s">
         <v>318</v>
       </c>
@@ -21620,7 +21968,7 @@
       <c r="J231" s="17"/>
       <c r="K231" s="17"/>
     </row>
-    <row r="232" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>150</v>
       </c>
@@ -21648,7 +21996,7 @@
       <c r="J232" s="16"/>
       <c r="K232" s="16"/>
     </row>
-    <row r="233" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>335</v>
       </c>
@@ -21676,7 +22024,7 @@
       <c r="J233" s="16"/>
       <c r="K233" s="16"/>
     </row>
-    <row r="234" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>53</v>
       </c>
@@ -21704,7 +22052,7 @@
       <c r="J234" s="16"/>
       <c r="K234" s="16"/>
     </row>
-    <row r="235" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="5" t="s">
         <v>826</v>
       </c>
@@ -21732,7 +22080,7 @@
       <c r="J235" s="17"/>
       <c r="K235" s="17"/>
     </row>
-    <row r="236" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="5" t="s">
         <v>816</v>
       </c>
@@ -21760,7 +22108,7 @@
       <c r="J236" s="17"/>
       <c r="K236" s="17"/>
     </row>
-    <row r="237" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>435</v>
       </c>
@@ -21788,7 +22136,7 @@
       <c r="J237" s="16"/>
       <c r="K237" s="16"/>
     </row>
-    <row r="238" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="5" t="s">
         <v>764</v>
       </c>
@@ -21816,7 +22164,7 @@
       <c r="J238" s="17"/>
       <c r="K238" s="17"/>
     </row>
-    <row r="239" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>746</v>
       </c>
@@ -21844,7 +22192,7 @@
       <c r="J239" s="16"/>
       <c r="K239" s="16"/>
     </row>
-    <row r="240" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="5" t="s">
         <v>746</v>
       </c>
@@ -21872,7 +22220,7 @@
       <c r="J240" s="17"/>
       <c r="K240" s="17"/>
     </row>
-    <row r="241" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="5" t="s">
         <v>822</v>
       </c>
@@ -21900,7 +22248,7 @@
       <c r="J241" s="17"/>
       <c r="K241" s="17"/>
     </row>
-    <row r="242" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>342</v>
       </c>
@@ -21928,7 +22276,7 @@
       <c r="J242" s="16"/>
       <c r="K242" s="16"/>
     </row>
-    <row r="243" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>749</v>
       </c>
@@ -21956,7 +22304,7 @@
       <c r="J243" s="16"/>
       <c r="K243" s="16"/>
     </row>
-    <row r="244" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="5" t="s">
         <v>749</v>
       </c>
@@ -21984,7 +22332,7 @@
       <c r="J244" s="17"/>
       <c r="K244" s="17"/>
     </row>
-    <row r="245" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>916</v>
       </c>
@@ -22012,7 +22360,7 @@
       <c r="J245" s="16"/>
       <c r="K245" s="16"/>
     </row>
-    <row r="246" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>776</v>
       </c>
@@ -22040,7 +22388,7 @@
       <c r="J246" s="16"/>
       <c r="K246" s="16"/>
     </row>
-    <row r="247" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>276</v>
       </c>
@@ -22068,7 +22416,7 @@
       <c r="J247" s="16"/>
       <c r="K247" s="16"/>
     </row>
-    <row r="248" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>9</v>
       </c>
@@ -22096,7 +22444,7 @@
       <c r="J248" s="22"/>
       <c r="K248" s="22"/>
     </row>
-    <row r="249" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>605</v>
       </c>
@@ -22124,7 +22472,7 @@
       <c r="J249" s="16"/>
       <c r="K249" s="16"/>
     </row>
-    <row r="250" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>837</v>
       </c>
@@ -22152,7 +22500,7 @@
       <c r="J250" s="16"/>
       <c r="K250" s="16"/>
     </row>
-    <row r="251" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>841</v>
       </c>
@@ -22180,7 +22528,7 @@
       <c r="J251" s="16"/>
       <c r="K251" s="16"/>
     </row>
-    <row r="252" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>546</v>
       </c>
@@ -22208,7 +22556,7 @@
       <c r="J252" s="16"/>
       <c r="K252" s="16"/>
     </row>
-    <row r="253" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="5" t="s">
         <v>482</v>
       </c>
@@ -22236,7 +22584,7 @@
       <c r="J253" s="17"/>
       <c r="K253" s="17"/>
     </row>
-    <row r="254" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>751</v>
       </c>
@@ -22264,7 +22612,7 @@
       <c r="J254" s="16"/>
       <c r="K254" s="16"/>
     </row>
-    <row r="255" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="5" t="s">
         <v>751</v>
       </c>
@@ -22292,7 +22640,7 @@
       <c r="J255" s="17"/>
       <c r="K255" s="17"/>
     </row>
-    <row r="256" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="5" t="s">
         <v>656</v>
       </c>
@@ -22320,7 +22668,7 @@
       <c r="J256" s="17"/>
       <c r="K256" s="17"/>
     </row>
-    <row r="257" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>771</v>
       </c>
@@ -22348,7 +22696,7 @@
       <c r="J257" s="16"/>
       <c r="K257" s="16"/>
     </row>
-    <row r="258" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>304</v>
       </c>
@@ -22376,7 +22724,7 @@
       <c r="J258" s="16"/>
       <c r="K258" s="16"/>
     </row>
-    <row r="259" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>666</v>
       </c>
@@ -22404,7 +22752,7 @@
       <c r="J259" s="16"/>
       <c r="K259" s="16"/>
     </row>
-    <row r="260" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>505</v>
       </c>
@@ -22432,7 +22780,7 @@
       <c r="J260" s="16"/>
       <c r="K260" s="16"/>
     </row>
-    <row r="261" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
         <v>794</v>
       </c>
@@ -22460,7 +22808,7 @@
       <c r="J261" s="17"/>
       <c r="K261" s="17"/>
     </row>
-    <row r="262" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>204</v>
       </c>
@@ -22488,7 +22836,7 @@
       <c r="J262" s="16"/>
       <c r="K262" s="16"/>
     </row>
-    <row r="263" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="5" t="s">
         <v>239</v>
       </c>
@@ -22516,7 +22864,7 @@
       <c r="J263" s="17"/>
       <c r="K263" s="17"/>
     </row>
-    <row r="264" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>100</v>
       </c>
@@ -22544,7 +22892,7 @@
       <c r="J264" s="16"/>
       <c r="K264" s="16"/>
     </row>
-    <row r="265" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>208</v>
       </c>
@@ -22572,7 +22920,7 @@
       <c r="J265" s="16"/>
       <c r="K265" s="16"/>
     </row>
-    <row r="266" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>94</v>
       </c>
@@ -22600,7 +22948,7 @@
       <c r="J266" s="16"/>
       <c r="K266" s="16"/>
     </row>
-    <row r="267" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>853</v>
       </c>
@@ -22628,7 +22976,7 @@
       <c r="J267" s="16"/>
       <c r="K267" s="16"/>
     </row>
-    <row r="268" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>69</v>
       </c>
@@ -22656,7 +23004,7 @@
       <c r="J268" s="16"/>
       <c r="K268" s="16"/>
     </row>
-    <row r="269" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="5" t="s">
         <v>689</v>
       </c>
@@ -22684,7 +23032,7 @@
       <c r="J269" s="17"/>
       <c r="K269" s="17"/>
     </row>
-    <row r="270" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="5" t="s">
         <v>491</v>
       </c>
@@ -22712,7 +23060,7 @@
       <c r="J270" s="17"/>
       <c r="K270" s="17"/>
     </row>
-    <row r="271" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>451</v>
       </c>
@@ -22740,7 +23088,7 @@
       <c r="J271" s="16"/>
       <c r="K271" s="16"/>
     </row>
-    <row r="272" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>911</v>
       </c>
@@ -22768,7 +23116,7 @@
       <c r="J272" s="16"/>
       <c r="K272" s="16"/>
     </row>
-    <row r="273" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>563</v>
       </c>
@@ -22796,7 +23144,7 @@
       <c r="J273" s="16"/>
       <c r="K273" s="16"/>
     </row>
-    <row r="274" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>591</v>
       </c>
@@ -22824,7 +23172,7 @@
       <c r="J274" s="16"/>
       <c r="K274" s="16"/>
     </row>
-    <row r="275" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>675</v>
       </c>
@@ -22852,7 +23200,7 @@
       <c r="J275" s="16"/>
       <c r="K275" s="16"/>
     </row>
-    <row r="276" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="5" t="s">
         <v>660</v>
       </c>
@@ -22880,7 +23228,7 @@
       <c r="J276" s="17"/>
       <c r="K276" s="17"/>
     </row>
-    <row r="277" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="5" t="s">
         <v>377</v>
       </c>
@@ -22908,7 +23256,7 @@
       <c r="J277" s="17"/>
       <c r="K277" s="17"/>
     </row>
-    <row r="278" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>920</v>
       </c>
@@ -22936,7 +23284,7 @@
       <c r="J278" s="16"/>
       <c r="K278" s="16"/>
     </row>
-    <row r="279" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="5" t="s">
         <v>620</v>
       </c>
@@ -22964,7 +23312,7 @@
       <c r="J279" s="17"/>
       <c r="K279" s="17"/>
     </row>
-    <row r="280" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="5" t="s">
         <v>29</v>
       </c>
@@ -22992,7 +23340,7 @@
       <c r="J280" s="17"/>
       <c r="K280" s="23"/>
     </row>
-    <row r="281" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="5" t="s">
         <v>539</v>
       </c>
@@ -23020,7 +23368,7 @@
       <c r="J281" s="17"/>
       <c r="K281" s="17"/>
     </row>
-    <row r="282" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="5" t="s">
         <v>607</v>
       </c>
@@ -23048,7 +23396,7 @@
       <c r="J282" s="17"/>
       <c r="K282" s="17"/>
     </row>
-    <row r="283" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>753</v>
       </c>
@@ -23076,7 +23424,7 @@
       <c r="J283" s="16"/>
       <c r="K283" s="16"/>
     </row>
-    <row r="284" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="5" t="s">
         <v>753</v>
       </c>
@@ -23104,7 +23452,7 @@
       <c r="J284" s="17"/>
       <c r="K284" s="17"/>
     </row>
-    <row r="285" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="5" t="s">
         <v>783</v>
       </c>
@@ -23132,7 +23480,7 @@
       <c r="J285" s="17"/>
       <c r="K285" s="17"/>
     </row>
-    <row r="286" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>81</v>
       </c>
@@ -23160,7 +23508,7 @@
       <c r="J286" s="16"/>
       <c r="K286" s="16"/>
     </row>
-    <row r="287" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>155</v>
       </c>
@@ -23188,7 +23536,7 @@
       <c r="J287" s="16"/>
       <c r="K287" s="16"/>
     </row>
-    <row r="288" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="5" t="s">
         <v>927</v>
       </c>
@@ -23216,7 +23564,7 @@
       <c r="J288" s="17"/>
       <c r="K288" s="17"/>
     </row>
-    <row r="289" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
         <v>769</v>
       </c>
@@ -23244,7 +23592,7 @@
       <c r="J289" s="17"/>
       <c r="K289" s="17"/>
     </row>
-    <row r="290" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="5" t="s">
         <v>206</v>
       </c>
@@ -23272,7 +23620,7 @@
       <c r="J290" s="17"/>
       <c r="K290" s="17"/>
     </row>
-    <row r="291" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>568</v>
       </c>
@@ -23300,7 +23648,7 @@
       <c r="J291" s="16"/>
       <c r="K291" s="16"/>
     </row>
-    <row r="292" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>600</v>
       </c>
@@ -23328,7 +23676,7 @@
       <c r="J292" s="16"/>
       <c r="K292" s="16"/>
     </row>
-    <row r="293" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="5" t="s">
         <v>108</v>
       </c>
@@ -23356,7 +23704,7 @@
       <c r="J293" s="17"/>
       <c r="K293" s="17"/>
     </row>
-    <row r="294" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>257</v>
       </c>
@@ -23384,7 +23732,7 @@
       <c r="J294" s="16"/>
       <c r="K294" s="16"/>
     </row>
-    <row r="295" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="5" t="s">
         <v>760</v>
       </c>
@@ -23412,7 +23760,7 @@
       <c r="J295" s="17"/>
       <c r="K295" s="17"/>
     </row>
-    <row r="296" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="5" t="s">
         <v>113</v>
       </c>
@@ -23440,7 +23788,7 @@
       <c r="J296" s="17"/>
       <c r="K296" s="17"/>
     </row>
-    <row r="297" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>828</v>
       </c>
@@ -23468,7 +23816,7 @@
       <c r="J297" s="16"/>
       <c r="K297" s="16"/>
     </row>
-    <row r="298" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="5" t="s">
         <v>685</v>
       </c>
@@ -23496,7 +23844,7 @@
       <c r="J298" s="17"/>
       <c r="K298" s="17"/>
     </row>
-    <row r="299" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="5" t="s">
         <v>41</v>
       </c>
@@ -23524,7 +23872,7 @@
       <c r="J299" s="17"/>
       <c r="K299" s="17"/>
     </row>
-    <row r="300" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="5" t="s">
         <v>923</v>
       </c>
@@ -23552,7 +23900,7 @@
       <c r="J300" s="17"/>
       <c r="K300" s="17"/>
     </row>
-    <row r="301" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>658</v>
       </c>
@@ -23580,7 +23928,7 @@
       <c r="J301" s="16"/>
       <c r="K301" s="16"/>
     </row>
-    <row r="302" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>19</v>
       </c>
@@ -23608,7 +23956,7 @@
       <c r="J302" s="16"/>
       <c r="K302" s="22"/>
     </row>
-    <row r="303" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="5" t="s">
         <v>255</v>
       </c>
@@ -23636,7 +23984,7 @@
       <c r="J303" s="17"/>
       <c r="K303" s="17"/>
     </row>
-    <row r="304" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="5" t="s">
         <v>698</v>
       </c>
@@ -23664,7 +24012,7 @@
       <c r="J304" s="17"/>
       <c r="K304" s="17"/>
     </row>
-    <row r="305" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="5" t="s">
         <v>543</v>
       </c>
@@ -23692,7 +24040,7 @@
       <c r="J305" s="17"/>
       <c r="K305" s="17"/>
     </row>
-    <row r="306" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>824</v>
       </c>
@@ -23720,7 +24068,7 @@
       <c r="J306" s="16"/>
       <c r="K306" s="16"/>
     </row>
-    <row r="307" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="5" t="s">
         <v>268</v>
       </c>
@@ -23748,7 +24096,7 @@
       <c r="J307" s="17"/>
       <c r="K307" s="17"/>
     </row>
-    <row r="308" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="5" t="s">
         <v>898</v>
       </c>
@@ -23776,7 +24124,7 @@
       <c r="J308" s="17"/>
       <c r="K308" s="17"/>
     </row>
-    <row r="309" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="5" t="s">
         <v>693</v>
       </c>
@@ -23804,7 +24152,7 @@
       <c r="J309" s="17"/>
       <c r="K309" s="17"/>
     </row>
-    <row r="310" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>785</v>
       </c>
@@ -23832,7 +24180,7 @@
       <c r="J310" s="16"/>
       <c r="K310" s="16"/>
     </row>
-    <row r="311" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="5" t="s">
         <v>466</v>
       </c>
@@ -23860,7 +24208,7 @@
       <c r="J311" s="17"/>
       <c r="K311" s="17"/>
     </row>
-    <row r="312" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="5" t="s">
         <v>89</v>
       </c>
@@ -23888,7 +24236,7 @@
       <c r="J312" s="17"/>
       <c r="K312" s="17"/>
     </row>
-    <row r="313" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="5" t="s">
         <v>640</v>
       </c>
@@ -23916,7 +24264,7 @@
       <c r="J313" s="17"/>
       <c r="K313" s="17"/>
     </row>
-    <row r="314" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="5" t="s">
         <v>47</v>
       </c>
@@ -23944,7 +24292,7 @@
       <c r="J314" s="17"/>
       <c r="K314" s="17"/>
     </row>
-    <row r="315" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>110</v>
       </c>
@@ -23972,7 +24320,7 @@
       <c r="J315" s="16"/>
       <c r="K315" s="16"/>
     </row>
-    <row r="316" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="5" t="s">
         <v>210</v>
       </c>
@@ -24000,7 +24348,7 @@
       <c r="J316" s="17"/>
       <c r="K316" s="17"/>
     </row>
-    <row r="317" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>32</v>
       </c>
@@ -24026,7 +24374,7 @@
       <c r="J317" s="16"/>
       <c r="K317" s="16"/>
     </row>
-    <row r="318" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="5" t="s">
         <v>164</v>
       </c>
@@ -24054,7 +24402,7 @@
       <c r="J318" s="17"/>
       <c r="K318" s="17"/>
     </row>
-    <row r="319" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>713</v>
       </c>
@@ -24082,7 +24430,7 @@
       <c r="J319" s="16"/>
       <c r="K319" s="16"/>
     </row>
-    <row r="320" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>241</v>
       </c>
@@ -24110,7 +24458,7 @@
       <c r="J320" s="16"/>
       <c r="K320" s="16"/>
     </row>
-    <row r="321" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="5" t="s">
         <v>909</v>
       </c>
@@ -24138,7 +24486,7 @@
       <c r="J321" s="17"/>
       <c r="K321" s="17"/>
     </row>
-    <row r="322" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>217</v>
       </c>
@@ -24166,7 +24514,7 @@
       <c r="J322" s="16"/>
       <c r="K322" s="16"/>
     </row>
-    <row r="323" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="5" t="s">
         <v>839</v>
       </c>
@@ -24194,7 +24542,7 @@
       <c r="J323" s="17"/>
       <c r="K323" s="17"/>
     </row>
-    <row r="324" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="5" t="s">
         <v>664</v>
       </c>
@@ -24222,7 +24570,7 @@
       <c r="J324" s="17"/>
       <c r="K324" s="17"/>
     </row>
-    <row r="325" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>265</v>
       </c>
@@ -24250,7 +24598,7 @@
       <c r="J325" s="16"/>
       <c r="K325" s="16"/>
     </row>
-    <row r="326" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>534</v>
       </c>
@@ -24278,7 +24626,7 @@
       <c r="J326" s="16"/>
       <c r="K326" s="16"/>
     </row>
-    <row r="327" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="5" t="s">
         <v>711</v>
       </c>
@@ -24306,7 +24654,7 @@
       <c r="J327" s="17"/>
       <c r="K327" s="17"/>
     </row>
-    <row r="328" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>929</v>
       </c>
@@ -24334,7 +24682,7 @@
       <c r="J328" s="16"/>
       <c r="K328" s="16"/>
     </row>
-    <row r="329" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="5" t="s">
         <v>918</v>
       </c>
@@ -24362,7 +24710,7 @@
       <c r="J329" s="17"/>
       <c r="K329" s="17"/>
     </row>
-    <row r="330" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>726</v>
       </c>
@@ -24390,7 +24738,7 @@
       <c r="J330" s="16"/>
       <c r="K330" s="16"/>
     </row>
-    <row r="331" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>849</v>
       </c>
@@ -24418,7 +24766,7 @@
       <c r="J331" s="16"/>
       <c r="K331" s="16"/>
     </row>
-    <row r="332" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>234</v>
       </c>
@@ -24446,7 +24794,7 @@
       <c r="J332" s="16"/>
       <c r="K332" s="16"/>
     </row>
-    <row r="333" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>781</v>
       </c>
@@ -24474,7 +24822,7 @@
       <c r="J333" s="16"/>
       <c r="K333" s="16"/>
     </row>
-    <row r="334" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="5" t="s">
         <v>668</v>
       </c>
@@ -24502,7 +24850,7 @@
       <c r="J334" s="17"/>
       <c r="K334" s="17"/>
     </row>
-    <row r="335" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="5" t="s">
         <v>876</v>
       </c>
@@ -24530,7 +24878,7 @@
       <c r="J335" s="17"/>
       <c r="K335" s="17"/>
     </row>
-    <row r="336" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="5" t="s">
         <v>774</v>
       </c>
@@ -24558,7 +24906,7 @@
       <c r="J336" s="17"/>
       <c r="K336" s="17"/>
     </row>
-    <row r="337" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>687</v>
       </c>
@@ -24586,7 +24934,7 @@
       <c r="J337" s="16"/>
       <c r="K337" s="16"/>
     </row>
-    <row r="338" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="5" t="s">
         <v>16</v>
       </c>
@@ -24614,7 +24962,7 @@
       <c r="J338" s="23"/>
       <c r="K338" s="23"/>
     </row>
-    <row r="339" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>119</v>
       </c>
@@ -24642,7 +24990,7 @@
       <c r="J339" s="16"/>
       <c r="K339" s="16"/>
     </row>
-    <row r="340" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>247</v>
       </c>
@@ -24670,7 +25018,7 @@
       <c r="J340" s="16"/>
       <c r="K340" s="16"/>
     </row>
-    <row r="341" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="5" t="s">
         <v>117</v>
       </c>
@@ -24698,7 +25046,7 @@
       <c r="J341" s="17"/>
       <c r="K341" s="17"/>
     </row>
-    <row r="342" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>874</v>
       </c>
@@ -24726,7 +25074,7 @@
       <c r="J342" s="16"/>
       <c r="K342" s="16"/>
     </row>
-    <row r="343" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="5" t="s">
         <v>411</v>
       </c>
@@ -24754,7 +25102,7 @@
       <c r="J343" s="17"/>
       <c r="K343" s="17"/>
     </row>
-    <row r="344" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="5" t="s">
         <v>399</v>
       </c>
@@ -24782,7 +25130,7 @@
       <c r="J344" s="17"/>
       <c r="K344" s="17"/>
     </row>
-    <row r="345" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="5" t="s">
         <v>406</v>
       </c>
@@ -24810,7 +25158,7 @@
       <c r="J345" s="17"/>
       <c r="K345" s="17"/>
     </row>
-    <row r="346" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="5" t="s">
         <v>35</v>
       </c>
@@ -24838,7 +25186,7 @@
       <c r="J346" s="17"/>
       <c r="K346" s="17"/>
     </row>
-    <row r="347" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>38</v>
       </c>
@@ -24866,7 +25214,7 @@
       <c r="J347" s="16"/>
       <c r="K347" s="16"/>
     </row>
-    <row r="348" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>44</v>
       </c>
@@ -24894,7 +25242,7 @@
       <c r="J348" s="16"/>
       <c r="K348" s="16"/>
     </row>
-    <row r="349" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
         <v>789</v>
       </c>
@@ -24922,7 +25270,7 @@
       <c r="J349" s="16"/>
       <c r="K349" s="16"/>
     </row>
-    <row r="350" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>797</v>
       </c>
@@ -24950,7 +25298,7 @@
       <c r="J350" s="16"/>
       <c r="K350" s="16"/>
     </row>
-    <row r="351" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="5" t="s">
         <v>799</v>
       </c>
@@ -24978,7 +25326,7 @@
       <c r="J351" s="17"/>
       <c r="K351" s="17"/>
     </row>
-    <row r="352" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>802</v>
       </c>
@@ -25006,7 +25354,7 @@
       <c r="J352" s="16"/>
       <c r="K352" s="16"/>
     </row>
-    <row r="353" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="5" t="s">
         <v>851</v>
       </c>
@@ -25034,23 +25382,23 @@
       <c r="J353" s="17"/>
       <c r="K353" s="17"/>
     </row>
-    <row r="354" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G354" s="27"/>
-    </row>
-    <row r="355" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="25">
-        <v>0</v>
-      </c>
-      <c r="B355" s="25"/>
-      <c r="C355" s="26"/>
-      <c r="D355" s="26"/>
-      <c r="E355" s="26"/>
-      <c r="F355" s="26"/>
-      <c r="G355" s="26"/>
-      <c r="H355" s="26"/>
-      <c r="I355" s="26"/>
-      <c r="J355" s="26"/>
-      <c r="K355" s="26"/>
+    <row r="354" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G354" s="25"/>
+    </row>
+    <row r="355" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A355" s="26">
+        <v>0</v>
+      </c>
+      <c r="B355" s="26"/>
+      <c r="C355" s="27"/>
+      <c r="D355" s="27"/>
+      <c r="E355" s="27"/>
+      <c r="F355" s="27"/>
+      <c r="G355" s="27"/>
+      <c r="H355" s="27"/>
+      <c r="I355" s="27"/>
+      <c r="J355" s="27"/>
+      <c r="K355" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K353" xr:uid="{00000000-0009-0000-0000-000001000000}">
@@ -25330,6 +25678,74 @@
     <hyperlink ref="J79" r:id="rId266" xr:uid="{25C0EC99-4084-4EEF-8D04-23E9DCB95415}"/>
     <hyperlink ref="I79" r:id="rId267" xr:uid="{C82AC3D4-9CFE-4DA0-A994-F2D832EFBE22}"/>
     <hyperlink ref="K79" r:id="rId268" xr:uid="{8EE95FD2-85B2-4D89-80C3-FE66F6A15996}"/>
+    <hyperlink ref="K80" r:id="rId269" xr:uid="{AE0A8815-AA89-4A5B-8032-A049602C807E}"/>
+    <hyperlink ref="J80" r:id="rId270" xr:uid="{F037A08E-7B3F-4B50-BB9C-CB755168BA57}"/>
+    <hyperlink ref="I80" r:id="rId271" xr:uid="{837CD94E-C3C4-47A7-B684-840E6448562B}"/>
+    <hyperlink ref="H80" r:id="rId272" xr:uid="{992C4E59-CBBB-4B12-929A-5427D18F893E}"/>
+    <hyperlink ref="K81" r:id="rId273" xr:uid="{ED74A614-5EBD-4739-B94F-EB20107FB2D6}"/>
+    <hyperlink ref="I81" r:id="rId274" xr:uid="{C6F59F61-A257-45AF-877F-39BC3306D4EA}"/>
+    <hyperlink ref="H81" r:id="rId275" xr:uid="{7464499A-5BA1-4D8C-A229-42B61D70F2C5}"/>
+    <hyperlink ref="J81" r:id="rId276" xr:uid="{FF331B10-ACB3-4E9D-B260-1C7BB046E4F6}"/>
+    <hyperlink ref="H82" r:id="rId277" xr:uid="{9227A9C3-9E81-43B2-A038-1B69A37A90B8}"/>
+    <hyperlink ref="J82" r:id="rId278" xr:uid="{5A822F7D-B80A-4946-ABEE-846FCD2D1760}"/>
+    <hyperlink ref="I82" r:id="rId279" xr:uid="{0EE2CB08-A09A-4451-B516-966038CF27FD}"/>
+    <hyperlink ref="K82" r:id="rId280" xr:uid="{BE651F56-FABD-41BF-8A50-59B08D48CF9C}"/>
+    <hyperlink ref="H83" r:id="rId281" xr:uid="{D2418C1C-EF4A-4036-8AF3-89D91FDD787B}"/>
+    <hyperlink ref="J83" r:id="rId282" xr:uid="{C99311E7-1188-4AF4-8A2C-D3661410CC6F}"/>
+    <hyperlink ref="I83" r:id="rId283" xr:uid="{E522DBF5-F59E-4635-B411-BBFEC0FFD3CB}"/>
+    <hyperlink ref="K83" r:id="rId284" xr:uid="{A7083C05-0F97-4C39-ADE9-A068F47B6F9C}"/>
+    <hyperlink ref="H84" r:id="rId285" xr:uid="{30BEDCE5-C818-49EA-8DC0-3FA7851BC49D}"/>
+    <hyperlink ref="J84" r:id="rId286" xr:uid="{C05CACFF-DC02-4C34-8C7D-D154B5D2EC99}"/>
+    <hyperlink ref="I84" r:id="rId287" xr:uid="{9CD9860A-9DDE-4A80-A43E-CC3BEA61881E}"/>
+    <hyperlink ref="K84" r:id="rId288" xr:uid="{4B66A3B2-9EED-4A1E-B926-B8025B5799C3}"/>
+    <hyperlink ref="H85" r:id="rId289" xr:uid="{04D82AC4-9373-4495-B029-1B0E35B56C71}"/>
+    <hyperlink ref="I85" r:id="rId290" xr:uid="{9DE0D6F8-DAC5-43DA-B52E-4E4494B7C5F6}"/>
+    <hyperlink ref="J85" r:id="rId291" xr:uid="{E9AF79E0-2AA2-4687-BEFE-0F7ED15059AE}"/>
+    <hyperlink ref="K85" r:id="rId292" xr:uid="{90FA869D-615C-4490-9D54-21A639C95D57}"/>
+    <hyperlink ref="H86" r:id="rId293" xr:uid="{186189FC-B189-48B5-9141-CCF3794EB2B3}"/>
+    <hyperlink ref="I86" r:id="rId294" xr:uid="{7A34B5FE-017C-4B67-BBA7-3D01A773A960}"/>
+    <hyperlink ref="K86" r:id="rId295" xr:uid="{89B1D8F3-87FA-4554-BA8E-5ABFFA8FE0DB}"/>
+    <hyperlink ref="H87" r:id="rId296" xr:uid="{8E5153DE-9C00-4689-9D84-6F1CC94C83C8}"/>
+    <hyperlink ref="I87" r:id="rId297" xr:uid="{1C6295FC-CBEE-4117-B836-EB66FABBF5F8}"/>
+    <hyperlink ref="J87" r:id="rId298" xr:uid="{973BFCFF-5877-4D0C-B83E-51120FFF284B}"/>
+    <hyperlink ref="K87" r:id="rId299" xr:uid="{2EE8AFEC-9394-4014-90EF-EFCBC4F87F67}"/>
+    <hyperlink ref="J88" r:id="rId300" xr:uid="{EA571617-EAAF-4298-A444-1686ADD1D3D5}"/>
+    <hyperlink ref="I88" r:id="rId301" xr:uid="{AC84840B-F3D1-480B-BB39-024179B2F2FE}"/>
+    <hyperlink ref="H88" r:id="rId302" xr:uid="{E8B9E159-E076-416B-B54D-E3B95F01ED75}"/>
+    <hyperlink ref="H89" r:id="rId303" xr:uid="{B450D7E7-5FFA-413C-8E43-1B6EB18697DE}"/>
+    <hyperlink ref="I89" r:id="rId304" xr:uid="{33DA5BD8-3FDC-4BEE-AD0F-56CC1D26927A}"/>
+    <hyperlink ref="J89" r:id="rId305" xr:uid="{692DD2B8-162E-41D4-B102-9E744EBF34FC}"/>
+    <hyperlink ref="K89" r:id="rId306" xr:uid="{374B1D5B-6330-4DD9-AC3A-273CC12CB3CA}"/>
+    <hyperlink ref="H90" r:id="rId307" xr:uid="{461E7030-4225-4F51-830A-F0A914765891}"/>
+    <hyperlink ref="I90" r:id="rId308" xr:uid="{63D4F047-34D7-4DB3-A863-D338E082518F}"/>
+    <hyperlink ref="J90" r:id="rId309" xr:uid="{3E2E93AE-B986-4030-A5A4-DCF3E38CCAFC}"/>
+    <hyperlink ref="K90" r:id="rId310" xr:uid="{89DBB7D9-B012-4778-86BA-B88448122C6F}"/>
+    <hyperlink ref="I91" r:id="rId311" xr:uid="{1CC3B30D-55E3-48C4-958E-2194300E7D16}"/>
+    <hyperlink ref="K91" r:id="rId312" xr:uid="{250A8EE6-9C28-4FB2-9D35-73B8CC2B4E00}"/>
+    <hyperlink ref="K88" r:id="rId313" xr:uid="{09E505D1-5E14-4B56-9CB8-B521B3B81A60}"/>
+    <hyperlink ref="J91" r:id="rId314" xr:uid="{A98CD08F-B3A3-4243-AC18-4D36F4536165}"/>
+    <hyperlink ref="H92" r:id="rId315" xr:uid="{6D66CEBB-CAFA-43E6-AE15-E5FD81162B6E}"/>
+    <hyperlink ref="I92" r:id="rId316" xr:uid="{6F7C2771-FFE8-4F6A-9417-3F9278D90766}"/>
+    <hyperlink ref="J92" r:id="rId317" xr:uid="{1FEE7F89-264D-46C0-90B0-BE6603006F15}"/>
+    <hyperlink ref="K92" r:id="rId318" xr:uid="{13258245-AED3-4740-868D-25D308564107}"/>
+    <hyperlink ref="H93" r:id="rId319" xr:uid="{C25F4DDE-DEF0-48B2-B142-958599703B6B}"/>
+    <hyperlink ref="K93" r:id="rId320" xr:uid="{64D94DEC-FDCB-4B47-8ED0-CFAE81F35579}"/>
+    <hyperlink ref="I93" r:id="rId321" xr:uid="{74EF847F-3849-4C10-A31E-2A821F251DC3}"/>
+    <hyperlink ref="J93" r:id="rId322" xr:uid="{43E6FB73-BFB5-4757-BB0D-7665CD644538}"/>
+    <hyperlink ref="K94" r:id="rId323" xr:uid="{995E09AF-C1E8-46E9-A2F2-E51BB4C8802E}"/>
+    <hyperlink ref="H95" r:id="rId324" xr:uid="{84B8E2A8-8EF7-47F0-9A21-ABC7086C904B}"/>
+    <hyperlink ref="K100" r:id="rId325" xr:uid="{7355F602-54A8-4514-A6D3-E00D8F73A9EC}"/>
+    <hyperlink ref="I100" r:id="rId326" xr:uid="{AA64C7A4-22C4-4714-8118-7E4E11736E0D}"/>
+    <hyperlink ref="H100" r:id="rId327" xr:uid="{66D5E096-C1AA-4813-8367-8813F33D8F7B}"/>
+    <hyperlink ref="J100" r:id="rId328" xr:uid="{088F396F-DDB0-4E9C-9EFA-93CF44B5CF21}"/>
+    <hyperlink ref="H99" r:id="rId329" xr:uid="{A476BAFF-FC7D-4364-8C47-B546C0FAEE1A}"/>
+    <hyperlink ref="I99" r:id="rId330" xr:uid="{121D0C05-91A0-40FA-81D2-DE84701C9D4A}"/>
+    <hyperlink ref="J99" r:id="rId331" xr:uid="{74F955A8-D058-4F2F-B305-775CAF52E311}"/>
+    <hyperlink ref="K99" r:id="rId332" xr:uid="{12F46A80-0F27-4F05-BF49-AF24094366CF}"/>
+    <hyperlink ref="K97" r:id="rId333" xr:uid="{8E864CFD-E74B-4019-A2B2-4706CA2FD461}"/>
+    <hyperlink ref="H97" r:id="rId334" xr:uid="{31A2FFC9-8611-4C66-85B2-A520F1E268C4}"/>
+    <hyperlink ref="H96" r:id="rId335" xr:uid="{AB3A3661-592C-48A5-ACE8-7849626E100E}"/>
+    <hyperlink ref="I96" r:id="rId336" xr:uid="{DC19933C-125E-400C-9DFC-4F8D6B24C97A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25338,7 +25754,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -25350,7 +25766,7 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -25376,7 +25792,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -25402,7 +25818,7 @@
         <v>28317</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>48</v>
       </c>
@@ -25428,7 +25844,7 @@
         <v>35703</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>90</v>
       </c>
@@ -25454,7 +25870,7 @@
         <v>72593</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>122</v>
       </c>
@@ -25480,7 +25896,7 @@
         <v>417644</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>141</v>
       </c>
@@ -25506,7 +25922,7 @@
         <v>64022</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>168</v>
       </c>
@@ -25532,7 +25948,7 @@
         <v>1499734</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>194</v>
       </c>
@@ -25558,7 +25974,7 @@
         <v>91418</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>235</v>
       </c>
@@ -25584,7 +26000,7 @@
         <v>42201</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>277</v>
       </c>
@@ -25610,7 +26026,7 @@
         <v>318656</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>305</v>
       </c>
@@ -25636,7 +26052,7 @@
         <v>160548</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>336</v>
       </c>
@@ -25662,7 +26078,7 @@
         <v>89753</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>372</v>
       </c>
@@ -25688,7 +26104,7 @@
         <v>24279</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>388</v>
       </c>
@@ -25714,7 +26130,7 @@
         <v>46865</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>400</v>
       </c>
@@ -25740,7 +26156,7 @@
         <v>54352</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>426</v>
       </c>
@@ -25766,7 +26182,7 @@
         <v>74941</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>452</v>
       </c>
@@ -25792,7 +26208,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>473</v>
       </c>
@@ -25818,7 +26234,7 @@
         <v>118239</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>499</v>
       </c>
@@ -25844,7 +26260,7 @@
         <v>697910</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>535</v>
       </c>
@@ -25870,7 +26286,7 @@
         <v>115657</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>557</v>
       </c>
@@ -25896,7 +26312,7 @@
         <v>57058</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>583</v>
       </c>
@@ -25922,7 +26338,7 @@
         <v>57408</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>608</v>
       </c>
@@ -25948,7 +26364,7 @@
         <v>74571</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>632</v>
       </c>
@@ -25974,7 +26390,7 @@
         <v>82510</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>650</v>
       </c>
@@ -26000,7 +26416,7 @@
         <v>27982</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>681</v>
       </c>
@@ -26026,7 +26442,7 @@
         <v>36917</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>714</v>
       </c>
@@ -26052,7 +26468,7 @@
         <v>30090</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>732</v>
       </c>
@@ -26078,7 +26494,7 @@
         <v>85372</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>756</v>
       </c>
@@ -26104,7 +26520,7 @@
         <v>78838</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>790</v>
       </c>
@@ -26130,7 +26546,7 @@
         <v>62960</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>819</v>
       </c>
@@ -26156,7 +26572,7 @@
         <v>85145</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>844</v>
       </c>
@@ -26182,7 +26598,7 @@
         <v>27338</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>868</v>
       </c>
@@ -26208,7 +26624,7 @@
         <v>71590</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>894</v>
       </c>
@@ -26243,7 +26659,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -26253,7 +26669,7 @@
     <col min="6" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>966</v>
       </c>
@@ -26273,7 +26689,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -26293,7 +26709,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -26313,7 +26729,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -26333,7 +26749,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -26353,7 +26769,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -26373,7 +26789,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -26393,7 +26809,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -26413,7 +26829,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -26433,7 +26849,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -26453,7 +26869,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -26473,7 +26889,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -26493,7 +26909,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -26513,7 +26929,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -26533,7 +26949,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -26553,7 +26969,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -26573,7 +26989,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -26593,7 +27009,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -26613,7 +27029,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -26633,7 +27049,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -26653,7 +27069,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -26673,7 +27089,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -26693,7 +27109,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -26713,7 +27129,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -26733,7 +27149,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -26753,7 +27169,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -26773,7 +27189,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -26793,7 +27209,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -26813,7 +27229,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -26833,7 +27249,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -26853,7 +27269,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>30</v>
       </c>
@@ -26873,7 +27289,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -26893,7 +27309,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -26913,7 +27329,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -26933,7 +27349,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="14"/>
       <c r="B35" s="14" t="s">
         <v>970</v>
@@ -26946,15 +27362,15 @@
       </c>
       <c r="F35" s="14"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="26" t="s">
         <v>971</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/Colombia/Resultados electorales.xlsx
+++ b/Colombia/Resultados electorales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juansoag\Downloads\Github\Avances_tesis\Colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169E452E-3061-46AC-AA3C-F3C6C3CDBF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830F0797-5ABD-497A-9859-6E7804770518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="1245" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5026" uniqueCount="1433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5027" uniqueCount="1433">
   <si>
     <t>ID Candidato</t>
   </si>
@@ -4541,9 +4541,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4560,6 +4558,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -16151,7 +16151,7 @@
       <c r="J27" s="22" t="s">
         <v>1277</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="27" t="s">
         <v>1276</v>
       </c>
       <c r="L27" s="22" t="s">
@@ -17363,7 +17363,7 @@
       <c r="H59" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="I59" s="30" t="s">
+      <c r="I59" s="28" t="s">
         <v>1424</v>
       </c>
       <c r="J59" s="21" t="s">
@@ -18467,7 +18467,7 @@
       <c r="J88" s="22" t="s">
         <v>1425</v>
       </c>
-      <c r="K88" s="33" t="s">
+      <c r="K88" s="31" t="s">
         <v>1427</v>
       </c>
       <c r="L88" s="22" t="s">
@@ -19523,7 +19523,7 @@
       <c r="H116" s="8" t="s">
         <v>1418</v>
       </c>
-      <c r="I116" s="28" t="s">
+      <c r="I116" s="26" t="s">
         <v>1416</v>
       </c>
       <c r="J116" s="23"/>
@@ -26599,25 +26599,25 @@
     </row>
     <row r="351" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G351" s="24"/>
-      <c r="H351" s="27"/>
-      <c r="I351" s="27"/>
+      <c r="H351" s="25"/>
+      <c r="I351" s="25"/>
     </row>
     <row r="352" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="25">
-        <v>0</v>
-      </c>
-      <c r="B352" s="25"/>
-      <c r="C352" s="26"/>
-      <c r="D352" s="26"/>
-      <c r="E352" s="26"/>
-      <c r="F352" s="26"/>
-      <c r="G352" s="26"/>
-      <c r="H352" s="26"/>
-      <c r="I352" s="26"/>
-      <c r="J352" s="26"/>
-      <c r="K352" s="26"/>
-      <c r="L352" s="26"/>
-      <c r="M352" s="26"/>
+      <c r="A352" s="32">
+        <v>0</v>
+      </c>
+      <c r="B352" s="32"/>
+      <c r="C352" s="33"/>
+      <c r="D352" s="33"/>
+      <c r="E352" s="33"/>
+      <c r="F352" s="33"/>
+      <c r="G352" s="33"/>
+      <c r="H352" s="33"/>
+      <c r="I352" s="33"/>
+      <c r="J352" s="33"/>
+      <c r="K352" s="33"/>
+      <c r="L352" s="33"/>
+      <c r="M352" s="33"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M350" xr:uid="{00000000-0009-0000-0000-000001000000}">
@@ -27078,7 +27078,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35811A66-E7AF-45C7-96E0-5FFFB608A329}">
-  <dimension ref="A2:E3"/>
+  <dimension ref="A2:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="15.42578125" customWidth="1"/>
@@ -27109,13 +27109,33 @@
         <f>B3*0.012</f>
         <v>1.3440000000000001</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="30">
         <f>((60+35)/60)*B3</f>
         <v>177.33333333333331</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="29">
         <f>D3/60</f>
         <v>2.9555555555555553</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>937</v>
+      </c>
+      <c r="B4">
+        <v>123</v>
+      </c>
+      <c r="C4">
+        <f>B4*0.241</f>
+        <v>29.643000000000001</v>
+      </c>
+      <c r="D4" s="30">
+        <f>((60+5)/60)*B4</f>
+        <v>133.25</v>
+      </c>
+      <c r="E4" s="29">
+        <f>D4/60</f>
+        <v>2.2208333333333332</v>
       </c>
     </row>
   </sheetData>
@@ -28735,14 +28755,14 @@
       <c r="F35" s="14"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="32" t="s">
         <v>971</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/Colombia/Resultados electorales.xlsx
+++ b/Colombia/Resultados electorales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juansoag\Downloads\Github\Avances_tesis\Colombia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D6CA49-1466-43D3-9660-F952253FD752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8124F9B4-433B-418A-8F05-A1FADCA33D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="1245" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="1245" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidatos E-26 ALC" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Población 2023 (DANE)" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidatos E-26 ALC'!$A$1:$I$353</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidatos E-26 ALC'!$A$1:$I$351</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Población 2023 (DANE)'!$A$1:$F$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Redes Sociales'!$A$1:$M$350</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Resumen por Municipio'!$A$1:$H$34</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5027" uniqueCount="1433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5013" uniqueCount="1433">
   <si>
     <t>ID Candidato</t>
   </si>
@@ -4348,7 +4348,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4403,6 +4403,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -4477,7 +4484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4563,12 +4570,15 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4872,7 +4882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I353"/>
+  <dimension ref="A1:I351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -12571,124 +12581,124 @@
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A266" s="2" t="s">
+      <c r="A266" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="B266" s="2" t="s">
+      <c r="B266" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="C266" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="D266" s="3" t="s">
+      <c r="D266" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="E266" s="3">
+      <c r="E266" s="6">
         <v>1</v>
       </c>
-      <c r="F266" s="2" t="s">
+      <c r="F266" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="G266" s="2" t="s">
+      <c r="G266" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H266" s="4">
+      <c r="H266" s="7">
         <v>85504</v>
       </c>
-      <c r="I266" s="3" t="s">
-        <v>15</v>
+      <c r="I266" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A267" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="B267" s="5" t="s">
+      <c r="A267" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B267" s="8" t="s">
         <v>732</v>
       </c>
-      <c r="C267" s="5" t="s">
+      <c r="C267" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="D267" s="6" t="s">
+      <c r="D267" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="E267" s="6">
-        <v>1</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="G267" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H267" s="7">
-        <v>85504</v>
-      </c>
-      <c r="I267" s="6" t="s">
+      <c r="E267" s="9">
+        <v>2</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="H267" s="10">
+        <v>85372</v>
+      </c>
+      <c r="I267" s="35" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A268" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="B268" s="8" t="s">
+      <c r="A268" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="C268" s="8" t="s">
+      <c r="C268" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="D268" s="9" t="s">
+      <c r="D268" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="E268" s="9">
-        <v>2</v>
-      </c>
-      <c r="F268" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="G268" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="H268" s="10">
-        <v>85372</v>
-      </c>
-      <c r="I268" s="9" t="s">
-        <v>25</v>
+      <c r="E268" s="3">
+        <v>3</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="H268" s="4">
+        <v>16097</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A269" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="B269" s="8" t="s">
+      <c r="A269" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="B269" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="C269" s="8" t="s">
+      <c r="C269" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="D269" s="9" t="s">
+      <c r="D269" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="E269" s="9">
-        <v>2</v>
-      </c>
-      <c r="F269" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="G269" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="H269" s="10">
-        <v>85372</v>
-      </c>
-      <c r="I269" s="9" t="s">
-        <v>25</v>
+      <c r="E269" s="6">
+        <v>3</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="G269" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="H269" s="7">
+        <v>16097</v>
+      </c>
+      <c r="I269" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>732</v>
@@ -12700,16 +12710,16 @@
         <v>734</v>
       </c>
       <c r="E270" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>741</v>
+        <v>31</v>
       </c>
       <c r="H270" s="4">
-        <v>16097</v>
+        <v>5729</v>
       </c>
       <c r="I270" s="3" t="s">
         <v>15</v>
@@ -12717,7 +12727,7 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>732</v>
@@ -12729,16 +12739,16 @@
         <v>734</v>
       </c>
       <c r="E271" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>741</v>
+        <v>31</v>
       </c>
       <c r="H271" s="7">
-        <v>16097</v>
+        <v>5729</v>
       </c>
       <c r="I271" s="6" t="s">
         <v>15</v>
@@ -12746,7 +12756,7 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>732</v>
@@ -12758,16 +12768,16 @@
         <v>734</v>
       </c>
       <c r="E272" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H272" s="4">
-        <v>5729</v>
+        <v>1871</v>
       </c>
       <c r="I272" s="3" t="s">
         <v>15</v>
@@ -12775,7 +12785,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>732</v>
@@ -12787,16 +12797,16 @@
         <v>734</v>
       </c>
       <c r="E273" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G273" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H273" s="7">
-        <v>5729</v>
+        <v>1871</v>
       </c>
       <c r="I273" s="6" t="s">
         <v>15</v>
@@ -12804,7 +12814,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>732</v>
@@ -12816,16 +12826,16 @@
         <v>734</v>
       </c>
       <c r="E274" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>37</v>
+        <v>748</v>
       </c>
       <c r="H274" s="4">
-        <v>1871</v>
+        <v>1400</v>
       </c>
       <c r="I274" s="3" t="s">
         <v>15</v>
@@ -12833,7 +12843,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>732</v>
@@ -12845,16 +12855,16 @@
         <v>734</v>
       </c>
       <c r="E275" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>37</v>
+        <v>748</v>
       </c>
       <c r="H275" s="7">
-        <v>1871</v>
+        <v>1400</v>
       </c>
       <c r="I275" s="6" t="s">
         <v>15</v>
@@ -12862,7 +12872,7 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>732</v>
@@ -12874,16 +12884,16 @@
         <v>734</v>
       </c>
       <c r="E276" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>748</v>
+        <v>14</v>
       </c>
       <c r="H276" s="4">
-        <v>1400</v>
+        <v>1361</v>
       </c>
       <c r="I276" s="3" t="s">
         <v>15</v>
@@ -12891,7 +12901,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B277" s="5" t="s">
         <v>732</v>
@@ -12903,16 +12913,16 @@
         <v>734</v>
       </c>
       <c r="E277" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>748</v>
+        <v>14</v>
       </c>
       <c r="H277" s="7">
-        <v>1400</v>
+        <v>1361</v>
       </c>
       <c r="I277" s="6" t="s">
         <v>15</v>
@@ -12920,7 +12930,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>732</v>
@@ -12932,16 +12942,16 @@
         <v>734</v>
       </c>
       <c r="E278" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H278" s="4">
-        <v>1361</v>
+        <v>1192</v>
       </c>
       <c r="I278" s="3" t="s">
         <v>15</v>
@@ -12949,7 +12959,7 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B279" s="5" t="s">
         <v>732</v>
@@ -12961,16 +12971,16 @@
         <v>734</v>
       </c>
       <c r="E279" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H279" s="7">
-        <v>1361</v>
+        <v>1192</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>15</v>
@@ -12978,7 +12988,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>732</v>
@@ -12990,16 +13000,16 @@
         <v>734</v>
       </c>
       <c r="E280" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="H280" s="4">
-        <v>1192</v>
+        <v>756</v>
       </c>
       <c r="I280" s="3" t="s">
         <v>15</v>
@@ -13007,7 +13017,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>732</v>
@@ -13019,16 +13029,16 @@
         <v>734</v>
       </c>
       <c r="E281" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="H281" s="7">
-        <v>1192</v>
+        <v>756</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>15</v>
@@ -13036,28 +13046,28 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>733</v>
+        <v>757</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>734</v>
+        <v>758</v>
       </c>
       <c r="E282" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="H282" s="4">
-        <v>756</v>
+        <v>12363</v>
       </c>
       <c r="I282" s="3" t="s">
         <v>15</v>
@@ -13065,28 +13075,28 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>733</v>
+        <v>757</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>734</v>
+        <v>758</v>
       </c>
       <c r="E283" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="G283" s="5" t="s">
-        <v>126</v>
+        <v>14</v>
       </c>
       <c r="H283" s="7">
-        <v>756</v>
+        <v>618</v>
       </c>
       <c r="I283" s="6" t="s">
         <v>15</v>
@@ -13094,7 +13104,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>756</v>
@@ -13106,16 +13116,16 @@
         <v>758</v>
       </c>
       <c r="E284" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H284" s="4">
-        <v>12363</v>
+        <v>38152</v>
       </c>
       <c r="I284" s="3" t="s">
         <v>15</v>
@@ -13123,7 +13133,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>756</v>
@@ -13135,16 +13145,16 @@
         <v>758</v>
       </c>
       <c r="E285" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="G285" s="5" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="H285" s="7">
-        <v>618</v>
+        <v>1419</v>
       </c>
       <c r="I285" s="6" t="s">
         <v>15</v>
@@ -13152,7 +13162,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>756</v>
@@ -13164,16 +13174,16 @@
         <v>758</v>
       </c>
       <c r="E286" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>18</v>
+        <v>768</v>
       </c>
       <c r="H286" s="4">
-        <v>38152</v>
+        <v>1770</v>
       </c>
       <c r="I286" s="3" t="s">
         <v>15</v>
@@ -13181,7 +13191,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>756</v>
@@ -13193,16 +13203,16 @@
         <v>758</v>
       </c>
       <c r="E287" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="H287" s="7">
-        <v>1419</v>
+        <v>646</v>
       </c>
       <c r="I287" s="6" t="s">
         <v>15</v>
@@ -13210,7 +13220,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>756</v>
@@ -13222,16 +13232,16 @@
         <v>758</v>
       </c>
       <c r="E288" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="H288" s="4">
-        <v>1770</v>
+        <v>1183</v>
       </c>
       <c r="I288" s="3" t="s">
         <v>15</v>
@@ -13239,7 +13249,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>756</v>
@@ -13251,16 +13261,16 @@
         <v>758</v>
       </c>
       <c r="E289" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="H289" s="7">
-        <v>646</v>
+        <v>166</v>
       </c>
       <c r="I289" s="6" t="s">
         <v>15</v>
@@ -13268,7 +13278,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>756</v>
@@ -13280,16 +13290,16 @@
         <v>758</v>
       </c>
       <c r="E290" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>773</v>
+        <v>80</v>
       </c>
       <c r="H290" s="4">
-        <v>1183</v>
+        <v>1251</v>
       </c>
       <c r="I290" s="3" t="s">
         <v>15</v>
@@ -13297,7 +13307,7 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>756</v>
@@ -13309,16 +13319,16 @@
         <v>758</v>
       </c>
       <c r="E291" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F291" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>154</v>
+        <v>780</v>
       </c>
       <c r="H291" s="7">
-        <v>166</v>
+        <v>4374</v>
       </c>
       <c r="I291" s="6" t="s">
         <v>15</v>
@@ -13326,7 +13336,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>756</v>
@@ -13338,16 +13348,16 @@
         <v>758</v>
       </c>
       <c r="E292" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="H292" s="4">
-        <v>1251</v>
+        <v>177</v>
       </c>
       <c r="I292" s="3" t="s">
         <v>15</v>
@@ -13355,7 +13365,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>756</v>
@@ -13367,16 +13377,16 @@
         <v>758</v>
       </c>
       <c r="E293" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F293" s="5" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="G293" s="5" t="s">
-        <v>780</v>
+        <v>37</v>
       </c>
       <c r="H293" s="7">
-        <v>4374</v>
+        <v>735</v>
       </c>
       <c r="I293" s="6" t="s">
         <v>15</v>
@@ -13384,7 +13394,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>756</v>
@@ -13396,111 +13406,111 @@
         <v>758</v>
       </c>
       <c r="E294" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H294" s="4">
-        <v>177</v>
+        <v>444</v>
       </c>
       <c r="I294" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A295" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="B295" s="5" t="s">
+      <c r="A295" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="B295" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="C295" s="5" t="s">
+      <c r="C295" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="D295" s="6" t="s">
+      <c r="D295" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="E295" s="6">
-        <v>12</v>
-      </c>
-      <c r="F295" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="G295" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H295" s="7">
-        <v>735</v>
-      </c>
-      <c r="I295" s="6" t="s">
-        <v>15</v>
+      <c r="E295" s="9">
+        <v>14</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="H295" s="10">
+        <v>78838</v>
+      </c>
+      <c r="I295" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>756</v>
+        <v>790</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>757</v>
+        <v>791</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>758</v>
+        <v>792</v>
       </c>
       <c r="E296" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="H296" s="4">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="I296" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A297" s="8" t="s">
-        <v>787</v>
-      </c>
-      <c r="B297" s="8" t="s">
-        <v>756</v>
-      </c>
-      <c r="C297" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D297" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="E297" s="9">
-        <v>14</v>
-      </c>
-      <c r="F297" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="G297" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H297" s="10">
-        <v>78838</v>
-      </c>
-      <c r="I297" s="9" t="s">
-        <v>25</v>
+      <c r="A297" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="E297" s="6">
+        <v>2</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="G297" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="H297" s="7">
+        <v>1081</v>
+      </c>
+      <c r="I297" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>790</v>
@@ -13512,13 +13522,13 @@
         <v>792</v>
       </c>
       <c r="E298" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="H298" s="4">
         <v>0</v>
@@ -13529,7 +13539,7 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>790</v>
@@ -13541,16 +13551,16 @@
         <v>792</v>
       </c>
       <c r="E299" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F299" s="5" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="G299" s="5" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="H299" s="7">
-        <v>1081</v>
+        <v>0</v>
       </c>
       <c r="I299" s="6" t="s">
         <v>15</v>
@@ -13558,7 +13568,7 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>790</v>
@@ -13570,13 +13580,13 @@
         <v>792</v>
       </c>
       <c r="E300" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="H300" s="4">
         <v>0</v>
@@ -13586,37 +13596,37 @@
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A301" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="B301" s="5" t="s">
+      <c r="A301" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B301" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="C301" s="5" t="s">
+      <c r="C301" s="8" t="s">
         <v>791</v>
       </c>
-      <c r="D301" s="6" t="s">
+      <c r="D301" s="9" t="s">
         <v>792</v>
       </c>
-      <c r="E301" s="6">
-        <v>4</v>
-      </c>
-      <c r="F301" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="G301" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="H301" s="7">
-        <v>0</v>
-      </c>
-      <c r="I301" s="6" t="s">
-        <v>15</v>
+      <c r="E301" s="9">
+        <v>6</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="H301" s="10">
+        <v>62960</v>
+      </c>
+      <c r="I301" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>790</v>
@@ -13628,53 +13638,53 @@
         <v>792</v>
       </c>
       <c r="E302" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>80</v>
+        <v>809</v>
       </c>
       <c r="H302" s="4">
-        <v>0</v>
+        <v>19497</v>
       </c>
       <c r="I302" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A303" s="8" t="s">
-        <v>804</v>
-      </c>
-      <c r="B303" s="8" t="s">
+      <c r="A303" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B303" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="C303" s="8" t="s">
+      <c r="C303" s="5" t="s">
         <v>791</v>
       </c>
-      <c r="D303" s="9" t="s">
+      <c r="D303" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="E303" s="9">
-        <v>6</v>
-      </c>
-      <c r="F303" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="G303" s="8" t="s">
-        <v>806</v>
-      </c>
-      <c r="H303" s="10">
-        <v>62960</v>
-      </c>
-      <c r="I303" s="9" t="s">
-        <v>25</v>
+      <c r="E303" s="6">
+        <v>8</v>
+      </c>
+      <c r="F303" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="G303" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="H303" s="7">
+        <v>14881</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>790</v>
@@ -13686,16 +13696,16 @@
         <v>792</v>
       </c>
       <c r="E304" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="H304" s="4">
-        <v>19497</v>
+        <v>53359</v>
       </c>
       <c r="I304" s="3" t="s">
         <v>15</v>
@@ -13703,7 +13713,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="5" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>790</v>
@@ -13715,16 +13725,16 @@
         <v>792</v>
       </c>
       <c r="E305" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F305" s="5" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="G305" s="5" t="s">
-        <v>812</v>
+        <v>31</v>
       </c>
       <c r="H305" s="7">
-        <v>14881</v>
+        <v>1482</v>
       </c>
       <c r="I305" s="6" t="s">
         <v>15</v>
@@ -13732,28 +13742,28 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>790</v>
+        <v>819</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>791</v>
+        <v>123</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
       <c r="E306" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>815</v>
+        <v>129</v>
       </c>
       <c r="H306" s="4">
-        <v>53359</v>
+        <v>54221</v>
       </c>
       <c r="I306" s="3" t="s">
         <v>15</v>
@@ -13761,28 +13771,28 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="5" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>790</v>
+        <v>819</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>791</v>
+        <v>123</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
       <c r="E307" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F307" s="5" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="G307" s="5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H307" s="7">
-        <v>1482</v>
+        <v>1367</v>
       </c>
       <c r="I307" s="6" t="s">
         <v>15</v>
@@ -13790,7 +13800,7 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>819</v>
@@ -13802,16 +13812,16 @@
         <v>820</v>
       </c>
       <c r="E308" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="H308" s="4">
-        <v>54221</v>
+        <v>484</v>
       </c>
       <c r="I308" s="3" t="s">
         <v>15</v>
@@ -13819,7 +13829,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="5" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>819</v>
@@ -13831,16 +13841,16 @@
         <v>820</v>
       </c>
       <c r="E309" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F309" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="G309" s="5" t="s">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="H309" s="7">
-        <v>1367</v>
+        <v>1502</v>
       </c>
       <c r="I309" s="6" t="s">
         <v>15</v>
@@ -13848,7 +13858,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>819</v>
@@ -13860,16 +13870,16 @@
         <v>820</v>
       </c>
       <c r="E310" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H310" s="4">
-        <v>484</v>
+        <v>614</v>
       </c>
       <c r="I310" s="3" t="s">
         <v>15</v>
@@ -13877,7 +13887,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>819</v>
@@ -13889,53 +13899,53 @@
         <v>820</v>
       </c>
       <c r="E311" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F311" s="5" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="G311" s="5" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="H311" s="7">
-        <v>1502</v>
+        <v>5215</v>
       </c>
       <c r="I311" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A312" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="B312" s="2" t="s">
+      <c r="A312" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="B312" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="C312" s="2" t="s">
+      <c r="C312" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D312" s="3" t="s">
+      <c r="D312" s="9" t="s">
         <v>820</v>
       </c>
-      <c r="E312" s="3">
-        <v>5</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="G312" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H312" s="4">
-        <v>614</v>
-      </c>
-      <c r="I312" s="3" t="s">
-        <v>15</v>
+      <c r="E312" s="9">
+        <v>7</v>
+      </c>
+      <c r="F312" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="G312" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="H312" s="10">
+        <v>85145</v>
+      </c>
+      <c r="I312" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="5" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>819</v>
@@ -13947,53 +13957,53 @@
         <v>820</v>
       </c>
       <c r="E313" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F313" s="5" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="G313" s="5" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="H313" s="7">
-        <v>5215</v>
+        <v>26451</v>
       </c>
       <c r="I313" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A314" s="8" t="s">
-        <v>832</v>
-      </c>
-      <c r="B314" s="8" t="s">
+      <c r="A314" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B314" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="C314" s="8" t="s">
+      <c r="C314" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D314" s="9" t="s">
+      <c r="D314" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="E314" s="9">
-        <v>7</v>
-      </c>
-      <c r="F314" s="8" t="s">
-        <v>833</v>
-      </c>
-      <c r="G314" s="8" t="s">
-        <v>834</v>
-      </c>
-      <c r="H314" s="10">
-        <v>85145</v>
-      </c>
-      <c r="I314" s="9" t="s">
-        <v>25</v>
+      <c r="E314" s="3">
+        <v>9</v>
+      </c>
+      <c r="F314" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="G314" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H314" s="4">
+        <v>1227</v>
+      </c>
+      <c r="I314" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B315" s="5" t="s">
         <v>819</v>
@@ -14005,16 +14015,16 @@
         <v>820</v>
       </c>
       <c r="E315" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F315" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="G315" s="5" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="H315" s="7">
-        <v>26451</v>
+        <v>320</v>
       </c>
       <c r="I315" s="6" t="s">
         <v>15</v>
@@ -14022,7 +14032,7 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>819</v>
@@ -14034,16 +14044,16 @@
         <v>820</v>
       </c>
       <c r="E316" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>243</v>
+        <v>144</v>
       </c>
       <c r="H316" s="4">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="I316" s="3" t="s">
         <v>15</v>
@@ -14051,28 +14061,28 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="5" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>123</v>
+        <v>845</v>
       </c>
       <c r="D317" s="6" t="s">
-        <v>820</v>
+        <v>846</v>
       </c>
       <c r="E317" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F317" s="5" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="G317" s="5" t="s">
-        <v>252</v>
+        <v>848</v>
       </c>
       <c r="H317" s="7">
-        <v>320</v>
+        <v>11661</v>
       </c>
       <c r="I317" s="6" t="s">
         <v>15</v>
@@ -14080,28 +14090,28 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>123</v>
+        <v>845</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>820</v>
+        <v>846</v>
       </c>
       <c r="E318" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="H318" s="4">
-        <v>1221</v>
+        <v>192</v>
       </c>
       <c r="I318" s="3" t="s">
         <v>15</v>
@@ -14109,7 +14119,7 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="5" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>844</v>
@@ -14121,16 +14131,16 @@
         <v>846</v>
       </c>
       <c r="E319" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="G319" s="5" t="s">
-        <v>848</v>
+        <v>112</v>
       </c>
       <c r="H319" s="7">
-        <v>11661</v>
+        <v>0</v>
       </c>
       <c r="I319" s="6" t="s">
         <v>15</v>
@@ -14138,7 +14148,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>844</v>
@@ -14150,16 +14160,16 @@
         <v>846</v>
       </c>
       <c r="E320" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="H320" s="4">
-        <v>192</v>
+        <v>999</v>
       </c>
       <c r="I320" s="3" t="s">
         <v>15</v>
@@ -14167,7 +14177,7 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="5" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B321" s="5" t="s">
         <v>844</v>
@@ -14179,16 +14189,16 @@
         <v>846</v>
       </c>
       <c r="E321" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F321" s="5" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="G321" s="5" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="H321" s="7">
-        <v>0</v>
+        <v>6035</v>
       </c>
       <c r="I321" s="6" t="s">
         <v>15</v>
@@ -14196,7 +14206,7 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>844</v>
@@ -14208,16 +14218,16 @@
         <v>846</v>
       </c>
       <c r="E322" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>80</v>
+        <v>859</v>
       </c>
       <c r="H322" s="4">
-        <v>999</v>
+        <v>7195</v>
       </c>
       <c r="I322" s="3" t="s">
         <v>15</v>
@@ -14225,7 +14235,7 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="5" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B323" s="5" t="s">
         <v>844</v>
@@ -14237,16 +14247,16 @@
         <v>846</v>
       </c>
       <c r="E323" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F323" s="5" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="G323" s="5" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="H323" s="7">
-        <v>6035</v>
+        <v>8967</v>
       </c>
       <c r="I323" s="6" t="s">
         <v>15</v>
@@ -14254,7 +14264,7 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>844</v>
@@ -14266,111 +14276,111 @@
         <v>846</v>
       </c>
       <c r="E324" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="H324" s="4">
-        <v>7195</v>
+        <v>18782</v>
       </c>
       <c r="I324" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A325" s="5" t="s">
-        <v>860</v>
-      </c>
-      <c r="B325" s="5" t="s">
+      <c r="A325" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="B325" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="C325" s="5" t="s">
+      <c r="C325" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="D325" s="6" t="s">
+      <c r="D325" s="9" t="s">
         <v>846</v>
       </c>
-      <c r="E325" s="6">
-        <v>7</v>
-      </c>
-      <c r="F325" s="5" t="s">
-        <v>861</v>
-      </c>
-      <c r="G325" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H325" s="7">
-        <v>8967</v>
-      </c>
-      <c r="I325" s="6" t="s">
-        <v>15</v>
+      <c r="E325" s="9">
+        <v>9</v>
+      </c>
+      <c r="F325" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="G325" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H325" s="10">
+        <v>27338</v>
+      </c>
+      <c r="I325" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>845</v>
+        <v>869</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>846</v>
+        <v>870</v>
       </c>
       <c r="E326" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>864</v>
+        <v>31</v>
       </c>
       <c r="H326" s="4">
-        <v>18782</v>
+        <v>10313</v>
       </c>
       <c r="I326" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A327" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="B327" s="8" t="s">
-        <v>844</v>
-      </c>
-      <c r="C327" s="8" t="s">
-        <v>845</v>
-      </c>
-      <c r="D327" s="9" t="s">
-        <v>846</v>
-      </c>
-      <c r="E327" s="9">
-        <v>9</v>
-      </c>
-      <c r="F327" s="8" t="s">
-        <v>866</v>
-      </c>
-      <c r="G327" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H327" s="10">
-        <v>27338</v>
-      </c>
-      <c r="I327" s="9" t="s">
-        <v>25</v>
+      <c r="A327" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="E327" s="6">
+        <v>2</v>
+      </c>
+      <c r="F327" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="G327" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H327" s="7">
+        <v>11003</v>
+      </c>
+      <c r="I327" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>868</v>
@@ -14382,16 +14392,16 @@
         <v>870</v>
       </c>
       <c r="E328" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="H328" s="4">
-        <v>10313</v>
+        <v>14</v>
       </c>
       <c r="I328" s="3" t="s">
         <v>15</v>
@@ -14399,7 +14409,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B329" s="5" t="s">
         <v>868</v>
@@ -14411,16 +14421,16 @@
         <v>870</v>
       </c>
       <c r="E329" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F329" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="G329" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H329" s="7">
-        <v>11003</v>
+        <v>171</v>
       </c>
       <c r="I329" s="6" t="s">
         <v>15</v>
@@ -14428,7 +14438,7 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>868</v>
@@ -14440,16 +14450,16 @@
         <v>870</v>
       </c>
       <c r="E330" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="H330" s="4">
-        <v>14</v>
+        <v>25715</v>
       </c>
       <c r="I330" s="3" t="s">
         <v>15</v>
@@ -14457,7 +14467,7 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="B331" s="5" t="s">
         <v>868</v>
@@ -14469,53 +14479,53 @@
         <v>870</v>
       </c>
       <c r="E331" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F331" s="5" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="G331" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H331" s="7">
-        <v>171</v>
+        <v>19339</v>
       </c>
       <c r="I331" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A332" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="B332" s="2" t="s">
+      <c r="A332" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="B332" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="C332" s="2" t="s">
+      <c r="C332" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="D332" s="3" t="s">
+      <c r="D332" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="E332" s="3">
-        <v>5</v>
-      </c>
-      <c r="F332" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="G332" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H332" s="4">
-        <v>25715</v>
-      </c>
-      <c r="I332" s="3" t="s">
-        <v>15</v>
+      <c r="E332" s="9">
+        <v>7</v>
+      </c>
+      <c r="F332" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="G332" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="H332" s="10">
+        <v>71590</v>
+      </c>
+      <c r="I332" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="5" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>868</v>
@@ -14527,53 +14537,53 @@
         <v>870</v>
       </c>
       <c r="E333" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F333" s="5" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="G333" s="5" t="s">
-        <v>52</v>
+        <v>887</v>
       </c>
       <c r="H333" s="7">
-        <v>19339</v>
+        <v>21413</v>
       </c>
       <c r="I333" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A334" s="8" t="s">
-        <v>882</v>
-      </c>
-      <c r="B334" s="8" t="s">
+      <c r="A334" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B334" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="C334" s="8" t="s">
+      <c r="C334" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="D334" s="9" t="s">
+      <c r="D334" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="E334" s="9">
-        <v>7</v>
-      </c>
-      <c r="F334" s="8" t="s">
-        <v>883</v>
-      </c>
-      <c r="G334" s="8" t="s">
-        <v>884</v>
-      </c>
-      <c r="H334" s="10">
-        <v>71590</v>
-      </c>
-      <c r="I334" s="9" t="s">
-        <v>25</v>
+      <c r="E334" s="3">
+        <v>9</v>
+      </c>
+      <c r="F334" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="G334" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H334" s="4">
+        <v>2027</v>
+      </c>
+      <c r="I334" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="5" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="B335" s="5" t="s">
         <v>868</v>
@@ -14585,16 +14595,16 @@
         <v>870</v>
       </c>
       <c r="E335" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F335" s="5" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="G335" s="5" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="H335" s="7">
-        <v>21413</v>
+        <v>5799</v>
       </c>
       <c r="I335" s="6" t="s">
         <v>15</v>
@@ -14602,28 +14612,28 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>868</v>
+        <v>894</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>869</v>
+        <v>895</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>870</v>
+        <v>896</v>
       </c>
       <c r="E336" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>63</v>
+        <v>249</v>
       </c>
       <c r="H336" s="4">
-        <v>2027</v>
+        <v>6607</v>
       </c>
       <c r="I336" s="3" t="s">
         <v>15</v>
@@ -14631,28 +14641,28 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="5" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>868</v>
+        <v>894</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>869</v>
+        <v>895</v>
       </c>
       <c r="D337" s="6" t="s">
-        <v>870</v>
+        <v>896</v>
       </c>
       <c r="E337" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F337" s="5" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="G337" s="5" t="s">
-        <v>892</v>
+        <v>74</v>
       </c>
       <c r="H337" s="7">
-        <v>5799</v>
+        <v>458</v>
       </c>
       <c r="I337" s="6" t="s">
         <v>15</v>
@@ -14660,7 +14670,7 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>894</v>
@@ -14672,16 +14682,16 @@
         <v>896</v>
       </c>
       <c r="E338" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>249</v>
+        <v>902</v>
       </c>
       <c r="H338" s="4">
-        <v>6607</v>
+        <v>63046</v>
       </c>
       <c r="I338" s="3" t="s">
         <v>15</v>
@@ -14689,7 +14699,7 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="5" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="B339" s="5" t="s">
         <v>894</v>
@@ -14701,53 +14711,53 @@
         <v>896</v>
       </c>
       <c r="E339" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="G339" s="5" t="s">
-        <v>74</v>
+        <v>905</v>
       </c>
       <c r="H339" s="7">
-        <v>458</v>
+        <v>4900</v>
       </c>
       <c r="I339" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A340" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="B340" s="2" t="s">
+      <c r="A340" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="B340" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="C340" s="2" t="s">
+      <c r="C340" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="D340" s="3" t="s">
+      <c r="D340" s="9" t="s">
         <v>896</v>
       </c>
-      <c r="E340" s="3">
-        <v>3</v>
-      </c>
-      <c r="F340" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="G340" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="H340" s="4">
-        <v>63046</v>
-      </c>
-      <c r="I340" s="3" t="s">
-        <v>15</v>
+      <c r="E340" s="9">
+        <v>5</v>
+      </c>
+      <c r="F340" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="G340" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="H340" s="10">
+        <v>70987</v>
+      </c>
+      <c r="I340" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="5" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="B341" s="5" t="s">
         <v>894</v>
@@ -14759,53 +14769,53 @@
         <v>896</v>
       </c>
       <c r="E341" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F341" s="5" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="G341" s="5" t="s">
-        <v>905</v>
+        <v>126</v>
       </c>
       <c r="H341" s="7">
-        <v>4900</v>
+        <v>342</v>
       </c>
       <c r="I341" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A342" s="8" t="s">
-        <v>906</v>
-      </c>
-      <c r="B342" s="8" t="s">
+      <c r="A342" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B342" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="C342" s="8" t="s">
+      <c r="C342" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="D342" s="9" t="s">
+      <c r="D342" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="E342" s="9">
-        <v>5</v>
-      </c>
-      <c r="F342" s="8" t="s">
-        <v>907</v>
-      </c>
-      <c r="G342" s="8" t="s">
-        <v>908</v>
-      </c>
-      <c r="H342" s="10">
-        <v>70987</v>
-      </c>
-      <c r="I342" s="9" t="s">
-        <v>25</v>
+      <c r="E342" s="3">
+        <v>7</v>
+      </c>
+      <c r="F342" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="G342" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="H342" s="4">
+        <v>943</v>
+      </c>
+      <c r="I342" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="B343" s="5" t="s">
         <v>894</v>
@@ -14817,16 +14827,16 @@
         <v>896</v>
       </c>
       <c r="E343" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F343" s="5" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="G343" s="5" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="H343" s="7">
-        <v>342</v>
+        <v>15058</v>
       </c>
       <c r="I343" s="6" t="s">
         <v>15</v>
@@ -14834,7 +14844,7 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>894</v>
@@ -14846,16 +14856,16 @@
         <v>896</v>
       </c>
       <c r="E344" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>913</v>
+        <v>31</v>
       </c>
       <c r="H344" s="4">
-        <v>943</v>
+        <v>1281</v>
       </c>
       <c r="I344" s="3" t="s">
         <v>15</v>
@@ -14863,7 +14873,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B345" s="5" t="s">
         <v>894</v>
@@ -14875,16 +14885,16 @@
         <v>896</v>
       </c>
       <c r="E345" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F345" s="5" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="G345" s="5" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="H345" s="7">
-        <v>15058</v>
+        <v>230</v>
       </c>
       <c r="I345" s="6" t="s">
         <v>15</v>
@@ -14892,7 +14902,7 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>894</v>
@@ -14904,16 +14914,16 @@
         <v>896</v>
       </c>
       <c r="E346" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>31</v>
+        <v>922</v>
       </c>
       <c r="H346" s="4">
-        <v>1281</v>
+        <v>802</v>
       </c>
       <c r="I346" s="3" t="s">
         <v>15</v>
@@ -14921,7 +14931,7 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="5" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="B347" s="5" t="s">
         <v>894</v>
@@ -14933,16 +14943,16 @@
         <v>896</v>
       </c>
       <c r="E347" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F347" s="5" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="G347" s="5" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="H347" s="7">
-        <v>230</v>
+        <v>549</v>
       </c>
       <c r="I347" s="6" t="s">
         <v>15</v>
@@ -14950,7 +14960,7 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>894</v>
@@ -14962,16 +14972,16 @@
         <v>896</v>
       </c>
       <c r="E348" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>922</v>
+        <v>71</v>
       </c>
       <c r="H348" s="4">
-        <v>802</v>
+        <v>5839</v>
       </c>
       <c r="I348" s="3" t="s">
         <v>15</v>
@@ -14979,7 +14989,7 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="5" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B349" s="5" t="s">
         <v>894</v>
@@ -14991,16 +15001,16 @@
         <v>896</v>
       </c>
       <c r="E349" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F349" s="5" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="G349" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H349" s="7">
-        <v>549</v>
+        <v>658</v>
       </c>
       <c r="I349" s="6" t="s">
         <v>15</v>
@@ -15008,7 +15018,7 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>894</v>
@@ -15020,16 +15030,16 @@
         <v>896</v>
       </c>
       <c r="E350" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H350" s="4">
-        <v>5839</v>
+        <v>245</v>
       </c>
       <c r="I350" s="3" t="s">
         <v>15</v>
@@ -15037,7 +15047,7 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="5" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>894</v>
@@ -15049,81 +15059,23 @@
         <v>896</v>
       </c>
       <c r="E351" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F351" s="5" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="G351" s="5" t="s">
-        <v>28</v>
+        <v>933</v>
       </c>
       <c r="H351" s="7">
-        <v>658</v>
+        <v>40604</v>
       </c>
       <c r="I351" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A352" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="C352" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="D352" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="E352" s="3">
-        <v>15</v>
-      </c>
-      <c r="F352" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="G352" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H352" s="4">
-        <v>245</v>
-      </c>
-      <c r="I352" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A353" s="5" t="s">
-        <v>931</v>
-      </c>
-      <c r="B353" s="5" t="s">
-        <v>894</v>
-      </c>
-      <c r="C353" s="5" t="s">
-        <v>895</v>
-      </c>
-      <c r="D353" s="6" t="s">
-        <v>896</v>
-      </c>
-      <c r="E353" s="6">
-        <v>16</v>
-      </c>
-      <c r="F353" s="5" t="s">
-        <v>932</v>
-      </c>
-      <c r="G353" s="5" t="s">
-        <v>933</v>
-      </c>
-      <c r="H353" s="7">
-        <v>40604</v>
-      </c>
-      <c r="I353" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I353" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I351" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15189,7 +15141,7 @@
         <v>180</v>
       </c>
       <c r="B2" s="2">
-        <f>VLOOKUP(A2,'Candidatos E-26 ALC'!A58:I409,8,FALSE)</f>
+        <f>VLOOKUP(A2,'Candidatos E-26 ALC'!A58:I407,8,FALSE)</f>
         <v>1499734</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -15227,7 +15179,7 @@
         <v>498</v>
       </c>
       <c r="B3" s="2">
-        <f>VLOOKUP(A3,'Candidatos E-26 ALC'!A176:I527,8,FALSE)</f>
+        <f>VLOOKUP(A3,'Candidatos E-26 ALC'!A176:I525,8,FALSE)</f>
         <v>697910</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -15265,7 +15217,7 @@
         <v>188</v>
       </c>
       <c r="B4" s="2">
-        <f>VLOOKUP(A4,'Candidatos E-26 ALC'!A61:I412,8,FALSE)</f>
+        <f>VLOOKUP(A4,'Candidatos E-26 ALC'!A61:I410,8,FALSE)</f>
         <v>616902</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -15303,7 +15255,7 @@
         <v>183</v>
       </c>
       <c r="B5" s="2">
-        <f>VLOOKUP(A5,'Candidatos E-26 ALC'!A59:I410,8,FALSE)</f>
+        <f>VLOOKUP(A5,'Candidatos E-26 ALC'!A59:I408,8,FALSE)</f>
         <v>571948</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -15341,7 +15293,7 @@
         <v>127</v>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(A6,'Candidatos E-26 ALC'!A40:I391,8,FALSE)</f>
+        <f>VLOOKUP(A6,'Candidatos E-26 ALC'!A40:I389,8,FALSE)</f>
         <v>417644</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -15379,7 +15331,7 @@
         <v>280</v>
       </c>
       <c r="B7" s="2">
-        <f>VLOOKUP(A7,'Candidatos E-26 ALC'!A95:I446,8,FALSE)</f>
+        <f>VLOOKUP(A7,'Candidatos E-26 ALC'!A95:I444,8,FALSE)</f>
         <v>318656</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -15417,7 +15369,7 @@
         <v>294</v>
       </c>
       <c r="B8" s="2">
-        <f>VLOOKUP(A8,'Candidatos E-26 ALC'!A100:I451,8,FALSE)</f>
+        <f>VLOOKUP(A8,'Candidatos E-26 ALC'!A100:I449,8,FALSE)</f>
         <v>221038</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -15455,7 +15407,7 @@
         <v>332</v>
       </c>
       <c r="B9" s="2">
-        <f>VLOOKUP(A9,'Candidatos E-26 ALC'!A115:I466,8,FALSE)</f>
+        <f>VLOOKUP(A9,'Candidatos E-26 ALC'!A115:I464,8,FALSE)</f>
         <v>160548</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -15493,7 +15445,7 @@
         <v>472</v>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(A10,'Candidatos E-26 ALC'!A166:I517,8,FALSE)</f>
+        <f>VLOOKUP(A10,'Candidatos E-26 ALC'!A166:I515,8,FALSE)</f>
         <v>118239</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -15531,7 +15483,7 @@
         <v>553</v>
       </c>
       <c r="B11" s="2">
-        <f>VLOOKUP(A11,'Candidatos E-26 ALC'!A197:I548,8,FALSE)</f>
+        <f>VLOOKUP(A11,'Candidatos E-26 ALC'!A197:I546,8,FALSE)</f>
         <v>115657</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -15569,7 +15521,7 @@
         <v>528</v>
       </c>
       <c r="B12" s="2">
-        <f>VLOOKUP(A12,'Candidatos E-26 ALC'!A187:I538,8,FALSE)</f>
+        <f>VLOOKUP(A12,'Candidatos E-26 ALC'!A187:I536,8,FALSE)</f>
         <v>95883</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -15607,7 +15559,7 @@
         <v>193</v>
       </c>
       <c r="B13" s="2">
-        <f>VLOOKUP(A13,'Candidatos E-26 ALC'!A63:I414,8,FALSE)</f>
+        <f>VLOOKUP(A13,'Candidatos E-26 ALC'!A63:I412,8,FALSE)</f>
         <v>91418</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -15645,7 +15597,7 @@
         <v>360</v>
       </c>
       <c r="B14" s="2">
-        <f>VLOOKUP(A14,'Candidatos E-26 ALC'!A126:I477,8,FALSE)</f>
+        <f>VLOOKUP(A14,'Candidatos E-26 ALC'!A126:I475,8,FALSE)</f>
         <v>89753</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -15683,7 +15635,7 @@
         <v>548</v>
       </c>
       <c r="B15" s="2">
-        <f>VLOOKUP(A15,'Candidatos E-26 ALC'!A195:I546,8,FALSE)</f>
+        <f>VLOOKUP(A15,'Candidatos E-26 ALC'!A195:I544,8,FALSE)</f>
         <v>88383</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -15721,7 +15673,7 @@
         <v>366</v>
       </c>
       <c r="B16" s="2">
-        <f>VLOOKUP(A16,'Candidatos E-26 ALC'!A128:I479,8,FALSE)</f>
+        <f>VLOOKUP(A16,'Candidatos E-26 ALC'!A128:I477,8,FALSE)</f>
         <v>87424</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -15759,7 +15711,7 @@
         <v>299</v>
       </c>
       <c r="B17" s="2">
-        <f>VLOOKUP(A17,'Candidatos E-26 ALC'!A102:I453,8,FALSE)</f>
+        <f>VLOOKUP(A17,'Candidatos E-26 ALC'!A102:I451,8,FALSE)</f>
         <v>86853</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -15797,7 +15749,7 @@
         <v>731</v>
       </c>
       <c r="B18" s="2">
-        <f>VLOOKUP(A18,'Candidatos E-26 ALC'!A266:I617,8,FALSE)</f>
+        <f>VLOOKUP(A18,'Candidatos E-26 ALC'!A266:I615,8,FALSE)</f>
         <v>85504</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -15835,7 +15787,7 @@
         <v>736</v>
       </c>
       <c r="B19" s="2">
-        <f>VLOOKUP(A19,'Candidatos E-26 ALC'!A268:I619,8,FALSE)</f>
+        <f>VLOOKUP(A19,'Candidatos E-26 ALC'!A267:I617,8,FALSE)</f>
         <v>85372</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -15873,7 +15825,7 @@
         <v>832</v>
       </c>
       <c r="B20" s="2">
-        <f>VLOOKUP(A20,'Candidatos E-26 ALC'!A314:I665,8,FALSE)</f>
+        <f>VLOOKUP(A20,'Candidatos E-26 ALC'!A312:I663,8,FALSE)</f>
         <v>85145</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -15911,7 +15863,7 @@
         <v>644</v>
       </c>
       <c r="B21" s="2">
-        <f>VLOOKUP(A21,'Candidatos E-26 ALC'!A231:I582,8,FALSE)</f>
+        <f>VLOOKUP(A21,'Candidatos E-26 ALC'!A231:I580,8,FALSE)</f>
         <v>82510</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -15949,7 +15901,7 @@
         <v>787</v>
       </c>
       <c r="B22" s="2">
-        <f>VLOOKUP(A22,'Candidatos E-26 ALC'!A297:I648,8,FALSE)</f>
+        <f>VLOOKUP(A22,'Candidatos E-26 ALC'!A295:I646,8,FALSE)</f>
         <v>78838</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -15987,7 +15939,7 @@
         <v>443</v>
       </c>
       <c r="B23" s="2">
-        <f>VLOOKUP(A23,'Candidatos E-26 ALC'!A155:I506,8,FALSE)</f>
+        <f>VLOOKUP(A23,'Candidatos E-26 ALC'!A155:I504,8,FALSE)</f>
         <v>74941</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -16025,7 +15977,7 @@
         <v>622</v>
       </c>
       <c r="B24" s="2">
-        <f>VLOOKUP(A24,'Candidatos E-26 ALC'!A222:I573,8,FALSE)</f>
+        <f>VLOOKUP(A24,'Candidatos E-26 ALC'!A222:I571,8,FALSE)</f>
         <v>74571</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -16063,7 +16015,7 @@
         <v>102</v>
       </c>
       <c r="B25" s="2">
-        <f>VLOOKUP(A25,'Candidatos E-26 ALC'!A31:I382,8,FALSE)</f>
+        <f>VLOOKUP(A25,'Candidatos E-26 ALC'!A31:I380,8,FALSE)</f>
         <v>72593</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -16101,7 +16053,7 @@
         <v>882</v>
       </c>
       <c r="B26" s="2">
-        <f>VLOOKUP(A26,'Candidatos E-26 ALC'!A334:I685,8,FALSE)</f>
+        <f>VLOOKUP(A26,'Candidatos E-26 ALC'!A332:I683,8,FALSE)</f>
         <v>71590</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -16139,7 +16091,7 @@
         <v>906</v>
       </c>
       <c r="B27" s="2">
-        <f>VLOOKUP(A27,'Candidatos E-26 ALC'!A342:I693,8,FALSE)</f>
+        <f>VLOOKUP(A27,'Candidatos E-26 ALC'!A340:I691,8,FALSE)</f>
         <v>70987</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -16177,7 +16129,7 @@
         <v>425</v>
       </c>
       <c r="B28" s="2">
-        <f>VLOOKUP(A28,'Candidatos E-26 ALC'!A149:I500,8,FALSE)</f>
+        <f>VLOOKUP(A28,'Candidatos E-26 ALC'!A149:I498,8,FALSE)</f>
         <v>70364</v>
       </c>
       <c r="C28" s="5" t="s">
@@ -16215,7 +16167,7 @@
         <v>174</v>
       </c>
       <c r="B29" s="2">
-        <f>VLOOKUP(A29,'Candidatos E-26 ALC'!A56:I407,8,FALSE)</f>
+        <f>VLOOKUP(A29,'Candidatos E-26 ALC'!A56:I405,8,FALSE)</f>
         <v>69639</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -16253,7 +16205,7 @@
         <v>171</v>
       </c>
       <c r="B30" s="2">
-        <f>VLOOKUP(A30,'Candidatos E-26 ALC'!A55:I406,8,FALSE)</f>
+        <f>VLOOKUP(A30,'Candidatos E-26 ALC'!A55:I404,8,FALSE)</f>
         <v>65681</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -16291,7 +16243,7 @@
         <v>147</v>
       </c>
       <c r="B31" s="2">
-        <f>VLOOKUP(A31,'Candidatos E-26 ALC'!A47:I398,8,FALSE)</f>
+        <f>VLOOKUP(A31,'Candidatos E-26 ALC'!A47:I396,8,FALSE)</f>
         <v>64022</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -16329,7 +16281,7 @@
         <v>631</v>
       </c>
       <c r="B32" s="2">
-        <f>VLOOKUP(A32,'Candidatos E-26 ALC'!A226:I577,8,FALSE)</f>
+        <f>VLOOKUP(A32,'Candidatos E-26 ALC'!A226:I575,8,FALSE)</f>
         <v>63869</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -16367,7 +16319,7 @@
         <v>900</v>
       </c>
       <c r="B33" s="2">
-        <f>VLOOKUP(A33,'Candidatos E-26 ALC'!A340:I691,8,FALSE)</f>
+        <f>VLOOKUP(A33,'Candidatos E-26 ALC'!A338:I689,8,FALSE)</f>
         <v>63046</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -16405,7 +16357,7 @@
         <v>804</v>
       </c>
       <c r="B34" s="2">
-        <f>VLOOKUP(A34,'Candidatos E-26 ALC'!A303:I654,8,FALSE)</f>
+        <f>VLOOKUP(A34,'Candidatos E-26 ALC'!A301:I652,8,FALSE)</f>
         <v>62960</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -16443,7 +16395,7 @@
         <v>597</v>
       </c>
       <c r="B35" s="2">
-        <f>VLOOKUP(A35,'Candidatos E-26 ALC'!A213:I564,8,FALSE)</f>
+        <f>VLOOKUP(A35,'Candidatos E-26 ALC'!A213:I562,8,FALSE)</f>
         <v>57408</v>
       </c>
       <c r="C35" s="8" t="s">
@@ -16481,7 +16433,7 @@
         <v>573</v>
       </c>
       <c r="B36" s="2">
-        <f>VLOOKUP(A36,'Candidatos E-26 ALC'!A204:I555,8,FALSE)</f>
+        <f>VLOOKUP(A36,'Candidatos E-26 ALC'!A204:I553,8,FALSE)</f>
         <v>57058</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -16519,7 +16471,7 @@
         <v>327</v>
       </c>
       <c r="B37" s="2">
-        <f>VLOOKUP(A37,'Candidatos E-26 ALC'!A113:I464,8,FALSE)</f>
+        <f>VLOOKUP(A37,'Candidatos E-26 ALC'!A113:I462,8,FALSE)</f>
         <v>56893</v>
       </c>
       <c r="C37" s="5" t="s">
@@ -16557,7 +16509,7 @@
         <v>161</v>
       </c>
       <c r="B38" s="2">
-        <f>VLOOKUP(A38,'Candidatos E-26 ALC'!A52:I403,8,FALSE)</f>
+        <f>VLOOKUP(A38,'Candidatos E-26 ALC'!A52:I401,8,FALSE)</f>
         <v>56635</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -16595,7 +16547,7 @@
         <v>408</v>
       </c>
       <c r="B39" s="2">
-        <f>VLOOKUP(A39,'Candidatos E-26 ALC'!A142:I493,8,FALSE)</f>
+        <f>VLOOKUP(A39,'Candidatos E-26 ALC'!A142:I491,8,FALSE)</f>
         <v>54352</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -16633,7 +16585,7 @@
         <v>818</v>
       </c>
       <c r="B40" s="2">
-        <f>VLOOKUP(A40,'Candidatos E-26 ALC'!A308:I659,8,FALSE)</f>
+        <f>VLOOKUP(A40,'Candidatos E-26 ALC'!A306:I657,8,FALSE)</f>
         <v>54221</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -16671,7 +16623,7 @@
         <v>813</v>
       </c>
       <c r="B41" s="2">
-        <f>VLOOKUP(A41,'Candidatos E-26 ALC'!A306:I657,8,FALSE)</f>
+        <f>VLOOKUP(A41,'Candidatos E-26 ALC'!A304:I655,8,FALSE)</f>
         <v>53359</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -16709,7 +16661,7 @@
         <v>135</v>
       </c>
       <c r="B42" s="2">
-        <f>VLOOKUP(A42,'Candidatos E-26 ALC'!A43:I394,8,FALSE)</f>
+        <f>VLOOKUP(A42,'Candidatos E-26 ALC'!A43:I392,8,FALSE)</f>
         <v>53144</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -16747,7 +16699,7 @@
         <v>387</v>
       </c>
       <c r="B43" s="2">
-        <f>VLOOKUP(A43,'Candidatos E-26 ALC'!A135:I486,8,FALSE)</f>
+        <f>VLOOKUP(A43,'Candidatos E-26 ALC'!A135:I484,8,FALSE)</f>
         <v>46865</v>
       </c>
       <c r="C43" s="8" t="s">
@@ -16785,7 +16737,7 @@
         <v>458</v>
       </c>
       <c r="B44" s="2">
-        <f>VLOOKUP(A44,'Candidatos E-26 ALC'!A160:I511,8,FALSE)</f>
+        <f>VLOOKUP(A44,'Candidatos E-26 ALC'!A160:I509,8,FALSE)</f>
         <v>45874</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -16823,7 +16775,7 @@
         <v>617</v>
       </c>
       <c r="B45" s="2">
-        <f>VLOOKUP(A45,'Candidatos E-26 ALC'!A220:I571,8,FALSE)</f>
+        <f>VLOOKUP(A45,'Candidatos E-26 ALC'!A220:I569,8,FALSE)</f>
         <v>45856</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -16861,7 +16813,7 @@
         <v>357</v>
       </c>
       <c r="B46" s="2">
-        <f>VLOOKUP(A46,'Candidatos E-26 ALC'!A125:I476,8,FALSE)</f>
+        <f>VLOOKUP(A46,'Candidatos E-26 ALC'!A125:I474,8,FALSE)</f>
         <v>44292</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -16899,7 +16851,7 @@
         <v>270</v>
       </c>
       <c r="B47" s="2">
-        <f>VLOOKUP(A47,'Candidatos E-26 ALC'!A92:I443,8,FALSE)</f>
+        <f>VLOOKUP(A47,'Candidatos E-26 ALC'!A92:I441,8,FALSE)</f>
         <v>42201</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -16937,7 +16889,7 @@
         <v>931</v>
       </c>
       <c r="B48" s="2">
-        <f>VLOOKUP(A48,'Candidatos E-26 ALC'!A353:I704,8,FALSE)</f>
+        <f>VLOOKUP(A48,'Candidatos E-26 ALC'!A351:I702,8,FALSE)</f>
         <v>40604</v>
       </c>
       <c r="C48" s="5" t="s">
@@ -16975,7 +16927,7 @@
         <v>212</v>
       </c>
       <c r="B49" s="2">
-        <f>VLOOKUP(A49,'Candidatos E-26 ALC'!A70:I421,8,FALSE)</f>
+        <f>VLOOKUP(A49,'Candidatos E-26 ALC'!A70:I419,8,FALSE)</f>
         <v>39004</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -17013,7 +16965,7 @@
         <v>762</v>
       </c>
       <c r="B50" s="2">
-        <f>VLOOKUP(A50,'Candidatos E-26 ALC'!A286:I637,8,FALSE)</f>
+        <f>VLOOKUP(A50,'Candidatos E-26 ALC'!A284:I635,8,FALSE)</f>
         <v>38152</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -17047,7 +16999,7 @@
         <v>329</v>
       </c>
       <c r="B51" s="2">
-        <f>VLOOKUP(A51,'Candidatos E-26 ALC'!A114:I465,8,FALSE)</f>
+        <f>VLOOKUP(A51,'Candidatos E-26 ALC'!A114:I463,8,FALSE)</f>
         <v>38016</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -17085,7 +17037,7 @@
         <v>588</v>
       </c>
       <c r="B52" s="2">
-        <f>VLOOKUP(A52,'Candidatos E-26 ALC'!A209:I560,8,FALSE)</f>
+        <f>VLOOKUP(A52,'Candidatos E-26 ALC'!A209:I558,8,FALSE)</f>
         <v>37368</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -17123,7 +17075,7 @@
         <v>702</v>
       </c>
       <c r="B53" s="2">
-        <f>VLOOKUP(A53,'Candidatos E-26 ALC'!A255:I606,8,FALSE)</f>
+        <f>VLOOKUP(A53,'Candidatos E-26 ALC'!A255:I604,8,FALSE)</f>
         <v>36917</v>
       </c>
       <c r="C53" s="8" t="s">
@@ -17161,7 +17113,7 @@
         <v>700</v>
       </c>
       <c r="B54" s="2">
-        <f>VLOOKUP(A54,'Candidatos E-26 ALC'!A254:I605,8,FALSE)</f>
+        <f>VLOOKUP(A54,'Candidatos E-26 ALC'!A254:I603,8,FALSE)</f>
         <v>36155</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -17201,7 +17153,7 @@
         <v>309</v>
       </c>
       <c r="B55" s="2">
-        <f>VLOOKUP(A55,'Candidatos E-26 ALC'!A105:I456,8,FALSE)</f>
+        <f>VLOOKUP(A55,'Candidatos E-26 ALC'!A105:I454,8,FALSE)</f>
         <v>35885</v>
       </c>
       <c r="C55" s="5" t="s">
@@ -17239,7 +17191,7 @@
         <v>83</v>
       </c>
       <c r="B56" s="2">
-        <f>VLOOKUP(A56,'Candidatos E-26 ALC'!A25:I376,8,FALSE)</f>
+        <f>VLOOKUP(A56,'Candidatos E-26 ALC'!A25:I374,8,FALSE)</f>
         <v>35703</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -17277,7 +17229,7 @@
         <v>289</v>
       </c>
       <c r="B57" s="2">
-        <f>VLOOKUP(A57,'Candidatos E-26 ALC'!A98:I449,8,FALSE)</f>
+        <f>VLOOKUP(A57,'Candidatos E-26 ALC'!A98:I447,8,FALSE)</f>
         <v>34529</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -17315,7 +17267,7 @@
         <v>191</v>
       </c>
       <c r="B58" s="2">
-        <f>VLOOKUP(A58,'Candidatos E-26 ALC'!A62:I413,8,FALSE)</f>
+        <f>VLOOKUP(A58,'Candidatos E-26 ALC'!A62:I411,8,FALSE)</f>
         <v>34099</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -17353,7 +17305,7 @@
         <v>198</v>
       </c>
       <c r="B59" s="2">
-        <f>VLOOKUP(A59,'Candidatos E-26 ALC'!A64:I415,8,FALSE)</f>
+        <f>VLOOKUP(A59,'Candidatos E-26 ALC'!A64:I413,8,FALSE)</f>
         <v>33995</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -17391,7 +17343,7 @@
         <v>464</v>
       </c>
       <c r="B60" s="2">
-        <f>VLOOKUP(A60,'Candidatos E-26 ALC'!A162:I513,8,FALSE)</f>
+        <f>VLOOKUP(A60,'Candidatos E-26 ALC'!A162:I511,8,FALSE)</f>
         <v>33894</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -17429,7 +17381,7 @@
         <v>455</v>
       </c>
       <c r="B61" s="2">
-        <f>VLOOKUP(A61,'Candidatos E-26 ALC'!A159:I510,8,FALSE)</f>
+        <f>VLOOKUP(A61,'Candidatos E-26 ALC'!A159:I508,8,FALSE)</f>
         <v>32304</v>
       </c>
       <c r="C61" s="5" t="s">
@@ -17467,7 +17419,7 @@
         <v>422</v>
       </c>
       <c r="B62" s="2">
-        <f>VLOOKUP(A62,'Candidatos E-26 ALC'!A148:I499,8,FALSE)</f>
+        <f>VLOOKUP(A62,'Candidatos E-26 ALC'!A148:I497,8,FALSE)</f>
         <v>31777</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -17505,7 +17457,7 @@
         <v>647</v>
       </c>
       <c r="B63" s="2">
-        <f>VLOOKUP(A63,'Candidatos E-26 ALC'!A232:I583,8,FALSE)</f>
+        <f>VLOOKUP(A63,'Candidatos E-26 ALC'!A232:I581,8,FALSE)</f>
         <v>31167</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -17543,7 +17495,7 @@
         <v>167</v>
       </c>
       <c r="B64" s="2">
-        <f>VLOOKUP(A64,'Candidatos E-26 ALC'!A54:I405,8,FALSE)</f>
+        <f>VLOOKUP(A64,'Candidatos E-26 ALC'!A54:I403,8,FALSE)</f>
         <v>31153</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -17581,7 +17533,7 @@
         <v>680</v>
       </c>
       <c r="B65" s="2">
-        <f>VLOOKUP(A65,'Candidatos E-26 ALC'!A246:I597,8,FALSE)</f>
+        <f>VLOOKUP(A65,'Candidatos E-26 ALC'!A246:I595,8,FALSE)</f>
         <v>30419</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -17617,7 +17569,7 @@
         <v>720</v>
       </c>
       <c r="B66" s="2">
-        <f>VLOOKUP(A66,'Candidatos E-26 ALC'!A262:I613,8,FALSE)</f>
+        <f>VLOOKUP(A66,'Candidatos E-26 ALC'!A262:I611,8,FALSE)</f>
         <v>30090</v>
       </c>
       <c r="C66" s="8" t="s">
@@ -17655,7 +17607,7 @@
         <v>22</v>
       </c>
       <c r="B67" s="2">
-        <f>VLOOKUP(A67,'Candidatos E-26 ALC'!A5:I356,8,FALSE)</f>
+        <f>VLOOKUP(A67,'Candidatos E-26 ALC'!A5:I354,8,FALSE)</f>
         <v>28317</v>
       </c>
       <c r="C67" s="8" t="s">
@@ -17693,7 +17645,7 @@
         <v>105</v>
       </c>
       <c r="B68" s="2">
-        <f>VLOOKUP(A68,'Candidatos E-26 ALC'!A32:I383,8,FALSE)</f>
+        <f>VLOOKUP(A68,'Candidatos E-26 ALC'!A32:I381,8,FALSE)</f>
         <v>28025</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -17731,7 +17683,7 @@
         <v>670</v>
       </c>
       <c r="B69" s="2">
-        <f>VLOOKUP(A69,'Candidatos E-26 ALC'!A242:I593,8,FALSE)</f>
+        <f>VLOOKUP(A69,'Candidatos E-26 ALC'!A242:I591,8,FALSE)</f>
         <v>27982</v>
       </c>
       <c r="C69" s="8" t="s">
@@ -17765,7 +17717,7 @@
         <v>392</v>
       </c>
       <c r="B70" s="2">
-        <f>VLOOKUP(A70,'Candidatos E-26 ALC'!A136:I487,8,FALSE)</f>
+        <f>VLOOKUP(A70,'Candidatos E-26 ALC'!A136:I485,8,FALSE)</f>
         <v>27702</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -17799,7 +17751,7 @@
         <v>865</v>
       </c>
       <c r="B71" s="2">
-        <f>VLOOKUP(A71,'Candidatos E-26 ALC'!A327:I678,8,FALSE)</f>
+        <f>VLOOKUP(A71,'Candidatos E-26 ALC'!A325:I676,8,FALSE)</f>
         <v>27338</v>
       </c>
       <c r="C71" s="8" t="s">
@@ -17837,7 +17789,7 @@
         <v>522</v>
       </c>
       <c r="B72" s="2">
-        <f>VLOOKUP(A72,'Candidatos E-26 ALC'!A185:I536,8,FALSE)</f>
+        <f>VLOOKUP(A72,'Candidatos E-26 ALC'!A185:I534,8,FALSE)</f>
         <v>27261</v>
       </c>
       <c r="C72" s="5" t="s">
@@ -17875,7 +17827,7 @@
         <v>728</v>
       </c>
       <c r="B73" s="2">
-        <f>VLOOKUP(A73,'Candidatos E-26 ALC'!A265:I616,8,FALSE)</f>
+        <f>VLOOKUP(A73,'Candidatos E-26 ALC'!A265:I614,8,FALSE)</f>
         <v>26833</v>
       </c>
       <c r="C73" s="5" t="s">
@@ -17911,7 +17863,7 @@
         <v>86</v>
       </c>
       <c r="B74" s="2">
-        <f>VLOOKUP(A74,'Candidatos E-26 ALC'!A26:I377,8,FALSE)</f>
+        <f>VLOOKUP(A74,'Candidatos E-26 ALC'!A26:I375,8,FALSE)</f>
         <v>26687</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -17947,7 +17899,7 @@
         <v>835</v>
       </c>
       <c r="B75" s="2">
-        <f>VLOOKUP(A75,'Candidatos E-26 ALC'!A315:I666,8,FALSE)</f>
+        <f>VLOOKUP(A75,'Candidatos E-26 ALC'!A313:I664,8,FALSE)</f>
         <v>26451</v>
       </c>
       <c r="C75" s="5" t="s">
@@ -17985,7 +17937,7 @@
         <v>878</v>
       </c>
       <c r="B76" s="2">
-        <f>VLOOKUP(A76,'Candidatos E-26 ALC'!A332:I683,8,FALSE)</f>
+        <f>VLOOKUP(A76,'Candidatos E-26 ALC'!A330:I681,8,FALSE)</f>
         <v>25715</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -18023,7 +17975,7 @@
         <v>379</v>
       </c>
       <c r="B77" s="2">
-        <f>VLOOKUP(A77,'Candidatos E-26 ALC'!A132:I483,8,FALSE)</f>
+        <f>VLOOKUP(A77,'Candidatos E-26 ALC'!A132:I481,8,FALSE)</f>
         <v>24279</v>
       </c>
       <c r="C77" s="8" t="s">
@@ -18061,7 +18013,7 @@
         <v>677</v>
       </c>
       <c r="B78" s="2">
-        <f>VLOOKUP(A78,'Candidatos E-26 ALC'!A245:I596,8,FALSE)</f>
+        <f>VLOOKUP(A78,'Candidatos E-26 ALC'!A245:I594,8,FALSE)</f>
         <v>24205</v>
       </c>
       <c r="C78" s="5" t="s">
@@ -18099,7 +18051,7 @@
         <v>325</v>
       </c>
       <c r="B79" s="2">
-        <f>VLOOKUP(A79,'Candidatos E-26 ALC'!A112:I463,8,FALSE)</f>
+        <f>VLOOKUP(A79,'Candidatos E-26 ALC'!A112:I461,8,FALSE)</f>
         <v>23662</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -18137,7 +18089,7 @@
         <v>231</v>
       </c>
       <c r="B80" s="2">
-        <f>VLOOKUP(A80,'Candidatos E-26 ALC'!A77:I428,8,FALSE)</f>
+        <f>VLOOKUP(A80,'Candidatos E-26 ALC'!A77:I426,8,FALSE)</f>
         <v>23551</v>
       </c>
       <c r="C80" s="5" t="s">
@@ -18175,7 +18127,7 @@
         <v>385</v>
       </c>
       <c r="B81" s="2">
-        <f>VLOOKUP(A81,'Candidatos E-26 ALC'!A134:I485,8,FALSE)</f>
+        <f>VLOOKUP(A81,'Candidatos E-26 ALC'!A134:I483,8,FALSE)</f>
         <v>23129</v>
       </c>
       <c r="C81" s="2" t="s">
@@ -18213,7 +18165,7 @@
         <v>201</v>
       </c>
       <c r="B82" s="2">
-        <f>VLOOKUP(A82,'Candidatos E-26 ALC'!A65:I416,8,FALSE)</f>
+        <f>VLOOKUP(A82,'Candidatos E-26 ALC'!A65:I414,8,FALSE)</f>
         <v>22726</v>
       </c>
       <c r="C82" s="5" t="s">
@@ -18251,7 +18203,7 @@
         <v>495</v>
       </c>
       <c r="B83" s="2">
-        <f>VLOOKUP(A83,'Candidatos E-26 ALC'!A175:I526,8,FALSE)</f>
+        <f>VLOOKUP(A83,'Candidatos E-26 ALC'!A175:I524,8,FALSE)</f>
         <v>22577</v>
       </c>
       <c r="C83" s="5" t="s">
@@ -18289,7 +18241,7 @@
         <v>26</v>
       </c>
       <c r="B84" s="2">
-        <f>VLOOKUP(A84,'Candidatos E-26 ALC'!A6:I357,8,FALSE)</f>
+        <f>VLOOKUP(A84,'Candidatos E-26 ALC'!A6:I355,8,FALSE)</f>
         <v>21889</v>
       </c>
       <c r="C84" s="2" t="s">
@@ -18325,7 +18277,7 @@
         <v>885</v>
       </c>
       <c r="B85" s="2">
-        <f>VLOOKUP(A85,'Candidatos E-26 ALC'!A335:I686,8,FALSE)</f>
+        <f>VLOOKUP(A85,'Candidatos E-26 ALC'!A333:I684,8,FALSE)</f>
         <v>21413</v>
       </c>
       <c r="C85" s="5" t="s">
@@ -18363,7 +18315,7 @@
         <v>723</v>
       </c>
       <c r="B86" s="2">
-        <f>VLOOKUP(A86,'Candidatos E-26 ALC'!A263:I614,8,FALSE)</f>
+        <f>VLOOKUP(A86,'Candidatos E-26 ALC'!A263:I612,8,FALSE)</f>
         <v>21198</v>
       </c>
       <c r="C86" s="5" t="s">
@@ -18401,7 +18353,7 @@
         <v>382</v>
       </c>
       <c r="B87" s="2">
-        <f>VLOOKUP(A87,'Candidatos E-26 ALC'!A133:I484,8,FALSE)</f>
+        <f>VLOOKUP(A87,'Candidatos E-26 ALC'!A133:I482,8,FALSE)</f>
         <v>20402</v>
       </c>
       <c r="C87" s="5" t="s">
@@ -18439,7 +18391,7 @@
         <v>441</v>
       </c>
       <c r="B88" s="2">
-        <f>VLOOKUP(A88,'Candidatos E-26 ALC'!A154:I505,8,FALSE)</f>
+        <f>VLOOKUP(A88,'Candidatos E-26 ALC'!A154:I503,8,FALSE)</f>
         <v>19912</v>
       </c>
       <c r="C88" s="2" t="s">
@@ -18462,7 +18414,7 @@
       <c r="J88" s="21" t="s">
         <v>1282</v>
       </c>
-      <c r="K88" s="33" t="s">
+      <c r="K88" s="31" t="s">
         <v>1283</v>
       </c>
       <c r="L88" s="21" t="s">
@@ -18477,7 +18429,7 @@
         <v>259</v>
       </c>
       <c r="B89" s="2">
-        <f>VLOOKUP(A89,'Candidatos E-26 ALC'!A87:I438,8,FALSE)</f>
+        <f>VLOOKUP(A89,'Candidatos E-26 ALC'!A87:I436,8,FALSE)</f>
         <v>19727</v>
       </c>
       <c r="C89" s="5" t="s">
@@ -18515,7 +18467,7 @@
         <v>807</v>
       </c>
       <c r="B90" s="2">
-        <f>VLOOKUP(A90,'Candidatos E-26 ALC'!A304:I655,8,FALSE)</f>
+        <f>VLOOKUP(A90,'Candidatos E-26 ALC'!A302:I653,8,FALSE)</f>
         <v>19497</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -18553,7 +18505,7 @@
         <v>880</v>
       </c>
       <c r="B91" s="2">
-        <f>VLOOKUP(A91,'Candidatos E-26 ALC'!A333:I684,8,FALSE)</f>
+        <f>VLOOKUP(A91,'Candidatos E-26 ALC'!A331:I682,8,FALSE)</f>
         <v>19339</v>
       </c>
       <c r="C91" s="5" t="s">
@@ -18591,7 +18543,7 @@
         <v>292</v>
       </c>
       <c r="B92" s="2">
-        <f>VLOOKUP(A92,'Candidatos E-26 ALC'!A99:I450,8,FALSE)</f>
+        <f>VLOOKUP(A92,'Candidatos E-26 ALC'!A99:I448,8,FALSE)</f>
         <v>19151</v>
       </c>
       <c r="C92" s="5" t="s">
@@ -18629,7 +18581,7 @@
         <v>138</v>
       </c>
       <c r="B93" s="2">
-        <f>VLOOKUP(A93,'Candidatos E-26 ALC'!A44:I395,8,FALSE)</f>
+        <f>VLOOKUP(A93,'Candidatos E-26 ALC'!A44:I393,8,FALSE)</f>
         <v>19052</v>
       </c>
       <c r="C93" s="2" t="s">
@@ -18663,7 +18615,7 @@
         <v>862</v>
       </c>
       <c r="B94" s="2">
-        <f>VLOOKUP(A94,'Candidatos E-26 ALC'!A326:I677,8,FALSE)</f>
+        <f>VLOOKUP(A94,'Candidatos E-26 ALC'!A324:I675,8,FALSE)</f>
         <v>18782</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -18697,7 +18649,7 @@
         <v>556</v>
       </c>
       <c r="B95" s="2">
-        <f>VLOOKUP(A95,'Candidatos E-26 ALC'!A198:I549,8,FALSE)</f>
+        <f>VLOOKUP(A95,'Candidatos E-26 ALC'!A198:I547,8,FALSE)</f>
         <v>18556</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -18731,7 +18683,7 @@
         <v>273</v>
       </c>
       <c r="B96" s="2">
-        <f>VLOOKUP(A96,'Candidatos E-26 ALC'!A93:I444,8,FALSE)</f>
+        <f>VLOOKUP(A96,'Candidatos E-26 ALC'!A93:I442,8,FALSE)</f>
         <v>17708</v>
       </c>
       <c r="C96" s="5" t="s">
@@ -18761,7 +18713,7 @@
         <v>602</v>
       </c>
       <c r="B97" s="2">
-        <f>VLOOKUP(A97,'Candidatos E-26 ALC'!A215:I566,8,FALSE)</f>
+        <f>VLOOKUP(A97,'Candidatos E-26 ALC'!A215:I564,8,FALSE)</f>
         <v>17471</v>
       </c>
       <c r="C97" s="5" t="s">
@@ -18799,7 +18751,7 @@
         <v>433</v>
       </c>
       <c r="B98" s="2">
-        <f>VLOOKUP(A98,'Candidatos E-26 ALC'!A151:I502,8,FALSE)</f>
+        <f>VLOOKUP(A98,'Candidatos E-26 ALC'!A151:I500,8,FALSE)</f>
         <v>17461</v>
       </c>
       <c r="C98" s="5" t="s">
@@ -18837,7 +18789,7 @@
         <v>739</v>
       </c>
       <c r="B99" s="2">
-        <f>VLOOKUP(A99,'Candidatos E-26 ALC'!A270:I621,8,FALSE)</f>
+        <f>VLOOKUP(A99,'Candidatos E-26 ALC'!A268:I619,8,FALSE)</f>
         <v>16097</v>
       </c>
       <c r="C99" s="2" t="s">
@@ -18869,7 +18821,7 @@
         <v>351</v>
       </c>
       <c r="B100" s="2">
-        <f>VLOOKUP(A100,'Candidatos E-26 ALC'!A122:I473,8,FALSE)</f>
+        <f>VLOOKUP(A100,'Candidatos E-26 ALC'!A122:I471,8,FALSE)</f>
         <v>15856</v>
       </c>
       <c r="C100" s="2" t="s">
@@ -18907,7 +18859,7 @@
         <v>97</v>
       </c>
       <c r="B101" s="2">
-        <f>VLOOKUP(A101,'Candidatos E-26 ALC'!A29:I380,8,FALSE)</f>
+        <f>VLOOKUP(A101,'Candidatos E-26 ALC'!A29:I378,8,FALSE)</f>
         <v>15779</v>
       </c>
       <c r="C101" s="5" t="s">
@@ -18945,7 +18897,7 @@
         <v>448</v>
       </c>
       <c r="B102" s="2">
-        <f>VLOOKUP(A102,'Candidatos E-26 ALC'!A157:I508,8,FALSE)</f>
+        <f>VLOOKUP(A102,'Candidatos E-26 ALC'!A157:I506,8,FALSE)</f>
         <v>15314</v>
       </c>
       <c r="C102" s="5" t="s">
@@ -18983,7 +18935,7 @@
         <v>394</v>
       </c>
       <c r="B103" s="2">
-        <f>VLOOKUP(A103,'Candidatos E-26 ALC'!A137:I488,8,FALSE)</f>
+        <f>VLOOKUP(A103,'Candidatos E-26 ALC'!A137:I486,8,FALSE)</f>
         <v>15288</v>
       </c>
       <c r="C103" s="5" t="s">
@@ -19017,7 +18969,7 @@
         <v>914</v>
       </c>
       <c r="B104" s="2">
-        <f>VLOOKUP(A104,'Candidatos E-26 ALC'!A345:I696,8,FALSE)</f>
+        <f>VLOOKUP(A104,'Candidatos E-26 ALC'!A343:I694,8,FALSE)</f>
         <v>15058</v>
       </c>
       <c r="C104" s="5" t="s">
@@ -19055,7 +19007,7 @@
         <v>614</v>
       </c>
       <c r="B105" s="2">
-        <f>VLOOKUP(A105,'Candidatos E-26 ALC'!A219:I570,8,FALSE)</f>
+        <f>VLOOKUP(A105,'Candidatos E-26 ALC'!A219:I568,8,FALSE)</f>
         <v>14890</v>
       </c>
       <c r="C105" s="5" t="s">
@@ -19093,7 +19045,7 @@
         <v>810</v>
       </c>
       <c r="B106" s="2">
-        <f>VLOOKUP(A106,'Candidatos E-26 ALC'!A305:I656,8,FALSE)</f>
+        <f>VLOOKUP(A106,'Candidatos E-26 ALC'!A303:I654,8,FALSE)</f>
         <v>14881</v>
       </c>
       <c r="C106" s="5" t="s">
@@ -19131,7 +19083,7 @@
         <v>177</v>
       </c>
       <c r="B107" s="2">
-        <f>VLOOKUP(A107,'Candidatos E-26 ALC'!A57:I408,8,FALSE)</f>
+        <f>VLOOKUP(A107,'Candidatos E-26 ALC'!A57:I406,8,FALSE)</f>
         <v>14855</v>
       </c>
       <c r="C107" s="5" t="s">
@@ -19167,7 +19119,7 @@
         <v>576</v>
       </c>
       <c r="B108" s="2">
-        <f>VLOOKUP(A108,'Candidatos E-26 ALC'!A205:I556,8,FALSE)</f>
+        <f>VLOOKUP(A108,'Candidatos E-26 ALC'!A205:I554,8,FALSE)</f>
         <v>14453</v>
       </c>
       <c r="C108" s="5" t="s">
@@ -19201,7 +19153,7 @@
         <v>638</v>
       </c>
       <c r="B109" s="2">
-        <f>VLOOKUP(A109,'Candidatos E-26 ALC'!A228:I579,8,FALSE)</f>
+        <f>VLOOKUP(A109,'Candidatos E-26 ALC'!A228:I577,8,FALSE)</f>
         <v>13177</v>
       </c>
       <c r="C109" s="2" t="s">
@@ -19239,7 +19191,7 @@
         <v>570</v>
       </c>
       <c r="B110" s="2">
-        <f>VLOOKUP(A110,'Candidatos E-26 ALC'!A203:I554,8,FALSE)</f>
+        <f>VLOOKUP(A110,'Candidatos E-26 ALC'!A203:I552,8,FALSE)</f>
         <v>13176</v>
       </c>
       <c r="C110" s="5" t="s">
@@ -19277,7 +19229,7 @@
         <v>415</v>
       </c>
       <c r="B111" s="2">
-        <f>VLOOKUP(A111,'Candidatos E-26 ALC'!A145:I496,8,FALSE)</f>
+        <f>VLOOKUP(A111,'Candidatos E-26 ALC'!A145:I494,8,FALSE)</f>
         <v>13127</v>
       </c>
       <c r="C111" s="5" t="s">
@@ -19315,7 +19267,7 @@
         <v>525</v>
       </c>
       <c r="B112" s="2">
-        <f>VLOOKUP(A112,'Candidatos E-26 ALC'!A186:I537,8,FALSE)</f>
+        <f>VLOOKUP(A112,'Candidatos E-26 ALC'!A186:I535,8,FALSE)</f>
         <v>12836</v>
       </c>
       <c r="C112" s="2" t="s">
@@ -19353,7 +19305,7 @@
         <v>369</v>
       </c>
       <c r="B113" s="2">
-        <f>VLOOKUP(A113,'Candidatos E-26 ALC'!A129:I480,8,FALSE)</f>
+        <f>VLOOKUP(A113,'Candidatos E-26 ALC'!A129:I478,8,FALSE)</f>
         <v>12796</v>
       </c>
       <c r="C113" s="5" t="s">
@@ -19391,7 +19343,7 @@
         <v>565</v>
       </c>
       <c r="B114" s="2">
-        <f>VLOOKUP(A114,'Candidatos E-26 ALC'!A201:I552,8,FALSE)</f>
+        <f>VLOOKUP(A114,'Candidatos E-26 ALC'!A201:I550,8,FALSE)</f>
         <v>12722</v>
       </c>
       <c r="C114" s="5" t="s">
@@ -19427,7 +19379,7 @@
         <v>755</v>
       </c>
       <c r="B115" s="2">
-        <f>VLOOKUP(A115,'Candidatos E-26 ALC'!A284:I635,8,FALSE)</f>
+        <f>VLOOKUP(A115,'Candidatos E-26 ALC'!A282:I633,8,FALSE)</f>
         <v>12363</v>
       </c>
       <c r="C115" s="2" t="s">
@@ -19461,7 +19413,7 @@
         <v>561</v>
       </c>
       <c r="B116" s="2">
-        <f>VLOOKUP(A116,'Candidatos E-26 ALC'!A199:I550,8,FALSE)</f>
+        <f>VLOOKUP(A116,'Candidatos E-26 ALC'!A199:I548,8,FALSE)</f>
         <v>12111</v>
       </c>
       <c r="C116" s="5" t="s">
@@ -19499,7 +19451,7 @@
         <v>579</v>
       </c>
       <c r="B117" s="2">
-        <f>VLOOKUP(A117,'Candidatos E-26 ALC'!A206:I557,8,FALSE)</f>
+        <f>VLOOKUP(A117,'Candidatos E-26 ALC'!A206:I555,8,FALSE)</f>
         <v>12081</v>
       </c>
       <c r="C117" s="2" t="s">
@@ -19529,7 +19481,7 @@
         <v>396</v>
       </c>
       <c r="B118" s="2">
-        <f>VLOOKUP(A118,'Candidatos E-26 ALC'!A138:I489,8,FALSE)</f>
+        <f>VLOOKUP(A118,'Candidatos E-26 ALC'!A138:I487,8,FALSE)</f>
         <v>11943</v>
       </c>
       <c r="C118" s="2" t="s">
@@ -19559,7 +19511,7 @@
         <v>363</v>
       </c>
       <c r="B119" s="2">
-        <f>VLOOKUP(A119,'Candidatos E-26 ALC'!A127:I478,8,FALSE)</f>
+        <f>VLOOKUP(A119,'Candidatos E-26 ALC'!A127:I476,8,FALSE)</f>
         <v>11926</v>
       </c>
       <c r="C119" s="5" t="s">
@@ -19597,7 +19549,7 @@
         <v>532</v>
       </c>
       <c r="B120" s="2">
-        <f>VLOOKUP(A120,'Candidatos E-26 ALC'!A189:I540,8,FALSE)</f>
+        <f>VLOOKUP(A120,'Candidatos E-26 ALC'!A189:I538,8,FALSE)</f>
         <v>11776</v>
       </c>
       <c r="C120" s="5" t="s">
@@ -19635,7 +19587,7 @@
         <v>55</v>
       </c>
       <c r="B121" s="2">
-        <f>VLOOKUP(A121,'Candidatos E-26 ALC'!A15:I366,8,FALSE)</f>
+        <f>VLOOKUP(A121,'Candidatos E-26 ALC'!A15:I364,8,FALSE)</f>
         <v>11674</v>
       </c>
       <c r="C121" s="5" t="s">
@@ -19673,7 +19625,7 @@
         <v>843</v>
       </c>
       <c r="B122" s="2">
-        <f>VLOOKUP(A122,'Candidatos E-26 ALC'!A319:I670,8,FALSE)</f>
+        <f>VLOOKUP(A122,'Candidatos E-26 ALC'!A317:I668,8,FALSE)</f>
         <v>11661</v>
       </c>
       <c r="C122" s="5" t="s">
@@ -19711,7 +19663,7 @@
         <v>140</v>
       </c>
       <c r="B123" s="2">
-        <f>VLOOKUP(A123,'Candidatos E-26 ALC'!A45:I396,8,FALSE)</f>
+        <f>VLOOKUP(A123,'Candidatos E-26 ALC'!A45:I394,8,FALSE)</f>
         <v>11226</v>
       </c>
       <c r="C123" s="5" t="s">
@@ -19743,7 +19695,7 @@
         <v>302</v>
       </c>
       <c r="B124" s="2">
-        <f>VLOOKUP(A124,'Candidatos E-26 ALC'!A103:I454,8,FALSE)</f>
+        <f>VLOOKUP(A124,'Candidatos E-26 ALC'!A103:I452,8,FALSE)</f>
         <v>11067</v>
       </c>
       <c r="C124" s="5" t="s">
@@ -19781,7 +19733,7 @@
         <v>438</v>
       </c>
       <c r="B125" s="2">
-        <f>VLOOKUP(A125,'Candidatos E-26 ALC'!A153:I504,8,FALSE)</f>
+        <f>VLOOKUP(A125,'Candidatos E-26 ALC'!A153:I502,8,FALSE)</f>
         <v>11051</v>
       </c>
       <c r="C125" s="5" t="s">
@@ -19813,14 +19765,14 @@
       <c r="M125" s="22" t="s">
         <v>1396</v>
       </c>
-      <c r="P125" s="34"/>
+      <c r="P125" s="32"/>
     </row>
     <row r="126" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>872</v>
       </c>
       <c r="B126" s="2">
-        <f>VLOOKUP(A126,'Candidatos E-26 ALC'!A329:I680,8,FALSE)</f>
+        <f>VLOOKUP(A126,'Candidatos E-26 ALC'!A327:I678,8,FALSE)</f>
         <v>11003</v>
       </c>
       <c r="C126" s="5" t="s">
@@ -19858,7 +19810,7 @@
         <v>75</v>
       </c>
       <c r="B127" s="2">
-        <f>VLOOKUP(A127,'Candidatos E-26 ALC'!A22:I373,8,FALSE)</f>
+        <f>VLOOKUP(A127,'Candidatos E-26 ALC'!A22:I371,8,FALSE)</f>
         <v>10996</v>
       </c>
       <c r="C127" s="2" t="s">
@@ -19888,7 +19840,7 @@
         <v>654</v>
       </c>
       <c r="B128" s="2">
-        <f>VLOOKUP(A128,'Candidatos E-26 ALC'!A234:I585,8,FALSE)</f>
+        <f>VLOOKUP(A128,'Candidatos E-26 ALC'!A234:I583,8,FALSE)</f>
         <v>10915</v>
       </c>
       <c r="C128" s="2" t="s">
@@ -19926,7 +19878,7 @@
         <v>508</v>
       </c>
       <c r="B129" s="2">
-        <f>VLOOKUP(A129,'Candidatos E-26 ALC'!A179:I530,8,FALSE)</f>
+        <f>VLOOKUP(A129,'Candidatos E-26 ALC'!A179:I528,8,FALSE)</f>
         <v>10707</v>
       </c>
       <c r="C129" s="5" t="s">
@@ -19964,7 +19916,7 @@
         <v>225</v>
       </c>
       <c r="B130" s="2">
-        <f>VLOOKUP(A130,'Candidatos E-26 ALC'!A75:I426,8,FALSE)</f>
+        <f>VLOOKUP(A130,'Candidatos E-26 ALC'!A75:I424,8,FALSE)</f>
         <v>10693</v>
       </c>
       <c r="C130" s="5" t="s">
@@ -20002,7 +19954,7 @@
         <v>222</v>
       </c>
       <c r="B131" s="2">
-        <f>VLOOKUP(A131,'Candidatos E-26 ALC'!A74:I425,8,FALSE)</f>
+        <f>VLOOKUP(A131,'Candidatos E-26 ALC'!A74:I423,8,FALSE)</f>
         <v>10326</v>
       </c>
       <c r="C131" s="2" t="s">
@@ -20036,7 +19988,7 @@
         <v>867</v>
       </c>
       <c r="B132" s="2">
-        <f>VLOOKUP(A132,'Candidatos E-26 ALC'!A328:I679,8,FALSE)</f>
+        <f>VLOOKUP(A132,'Candidatos E-26 ALC'!A326:I677,8,FALSE)</f>
         <v>10313</v>
       </c>
       <c r="C132" s="2" t="s">
@@ -20066,7 +20018,7 @@
         <v>58</v>
       </c>
       <c r="B133" s="2">
-        <f>VLOOKUP(A133,'Candidatos E-26 ALC'!A16:I367,8,FALSE)</f>
+        <f>VLOOKUP(A133,'Candidatos E-26 ALC'!A16:I365,8,FALSE)</f>
         <v>9436</v>
       </c>
       <c r="C133" s="2" t="s">
@@ -20096,7 +20048,7 @@
         <v>349</v>
       </c>
       <c r="B134" s="2">
-        <f>VLOOKUP(A134,'Candidatos E-26 ALC'!A121:I472,8,FALSE)</f>
+        <f>VLOOKUP(A134,'Candidatos E-26 ALC'!A121:I470,8,FALSE)</f>
         <v>9301</v>
       </c>
       <c r="C134" s="5" t="s">
@@ -20126,7 +20078,7 @@
         <v>860</v>
       </c>
       <c r="B135" s="2">
-        <f>VLOOKUP(A135,'Candidatos E-26 ALC'!A325:I676,8,FALSE)</f>
+        <f>VLOOKUP(A135,'Candidatos E-26 ALC'!A323:I674,8,FALSE)</f>
         <v>8967</v>
       </c>
       <c r="C135" s="5" t="s">
@@ -20156,7 +20108,7 @@
         <v>484</v>
       </c>
       <c r="B136" s="2">
-        <f>VLOOKUP(A136,'Candidatos E-26 ALC'!A170:I521,8,FALSE)</f>
+        <f>VLOOKUP(A136,'Candidatos E-26 ALC'!A170:I519,8,FALSE)</f>
         <v>8323</v>
       </c>
       <c r="C136" s="2" t="s">
@@ -20186,7 +20138,7 @@
         <v>219</v>
       </c>
       <c r="B137" s="2">
-        <f>VLOOKUP(A137,'Candidatos E-26 ALC'!A73:I424,8,FALSE)</f>
+        <f>VLOOKUP(A137,'Candidatos E-26 ALC'!A73:I422,8,FALSE)</f>
         <v>8212</v>
       </c>
       <c r="C137" s="5" t="s">
@@ -20216,7 +20168,7 @@
         <v>709</v>
       </c>
       <c r="B138" s="2">
-        <f>VLOOKUP(A138,'Candidatos E-26 ALC'!A258:I609,8,FALSE)</f>
+        <f>VLOOKUP(A138,'Candidatos E-26 ALC'!A258:I607,8,FALSE)</f>
         <v>8052</v>
       </c>
       <c r="C138" s="2" t="s">
@@ -20246,7 +20198,7 @@
         <v>121</v>
       </c>
       <c r="B139" s="2">
-        <f>VLOOKUP(A139,'Candidatos E-26 ALC'!A39:I390,8,FALSE)</f>
+        <f>VLOOKUP(A139,'Candidatos E-26 ALC'!A39:I388,8,FALSE)</f>
         <v>7790</v>
       </c>
       <c r="C139" s="5" t="s">
@@ -20276,7 +20228,7 @@
         <v>627</v>
       </c>
       <c r="B140" s="2">
-        <f>VLOOKUP(A140,'Candidatos E-26 ALC'!A224:I575,8,FALSE)</f>
+        <f>VLOOKUP(A140,'Candidatos E-26 ALC'!A224:I573,8,FALSE)</f>
         <v>7733</v>
       </c>
       <c r="C140" s="2" t="s">
@@ -20306,7 +20258,7 @@
         <v>130</v>
       </c>
       <c r="B141" s="2">
-        <f>VLOOKUP(A141,'Candidatos E-26 ALC'!A41:I392,8,FALSE)</f>
+        <f>VLOOKUP(A141,'Candidatos E-26 ALC'!A41:I390,8,FALSE)</f>
         <v>7659</v>
       </c>
       <c r="C141" s="5" t="s">
@@ -20336,7 +20288,7 @@
         <v>371</v>
       </c>
       <c r="B142" s="2">
-        <f>VLOOKUP(A142,'Candidatos E-26 ALC'!A130:I481,8,FALSE)</f>
+        <f>VLOOKUP(A142,'Candidatos E-26 ALC'!A130:I479,8,FALSE)</f>
         <v>7585</v>
       </c>
       <c r="C142" s="2" t="s">
@@ -20366,7 +20318,7 @@
         <v>67</v>
       </c>
       <c r="B143" s="2">
-        <f>VLOOKUP(A143,'Candidatos E-26 ALC'!A19:I370,8,FALSE)</f>
+        <f>VLOOKUP(A143,'Candidatos E-26 ALC'!A19:I368,8,FALSE)</f>
         <v>7569</v>
       </c>
       <c r="C143" s="5" t="s">
@@ -20396,7 +20348,7 @@
         <v>152</v>
       </c>
       <c r="B144" s="2">
-        <f>VLOOKUP(A144,'Candidatos E-26 ALC'!A49:I400,8,FALSE)</f>
+        <f>VLOOKUP(A144,'Candidatos E-26 ALC'!A49:I398,8,FALSE)</f>
         <v>7457</v>
       </c>
       <c r="C144" s="5" t="s">
@@ -20426,7 +20378,7 @@
         <v>446</v>
       </c>
       <c r="B145" s="2">
-        <f>VLOOKUP(A145,'Candidatos E-26 ALC'!A156:I507,8,FALSE)</f>
+        <f>VLOOKUP(A145,'Candidatos E-26 ALC'!A156:I505,8,FALSE)</f>
         <v>7299</v>
       </c>
       <c r="C145" s="2" t="s">
@@ -20456,7 +20408,7 @@
         <v>857</v>
       </c>
       <c r="B146" s="2">
-        <f>VLOOKUP(A146,'Candidatos E-26 ALC'!A324:I675,8,FALSE)</f>
+        <f>VLOOKUP(A146,'Candidatos E-26 ALC'!A322:I673,8,FALSE)</f>
         <v>7195</v>
       </c>
       <c r="C146" s="2" t="s">
@@ -20486,7 +20438,7 @@
         <v>250</v>
       </c>
       <c r="B147" s="2">
-        <f>VLOOKUP(A147,'Candidatos E-26 ALC'!A83:I434,8,FALSE)</f>
+        <f>VLOOKUP(A147,'Candidatos E-26 ALC'!A83:I432,8,FALSE)</f>
         <v>7080</v>
       </c>
       <c r="C147" s="5" t="s">
@@ -20516,7 +20468,7 @@
         <v>893</v>
       </c>
       <c r="B148" s="2">
-        <f>VLOOKUP(A148,'Candidatos E-26 ALC'!A338:I689,8,FALSE)</f>
+        <f>VLOOKUP(A148,'Candidatos E-26 ALC'!A336:I687,8,FALSE)</f>
         <v>6607</v>
       </c>
       <c r="C148" s="2" t="s">
@@ -20546,7 +20498,7 @@
         <v>420</v>
       </c>
       <c r="B149" s="2">
-        <f>VLOOKUP(A149,'Candidatos E-26 ALC'!A147:I498,8,FALSE)</f>
+        <f>VLOOKUP(A149,'Candidatos E-26 ALC'!A147:I496,8,FALSE)</f>
         <v>6458</v>
       </c>
       <c r="C149" s="5" t="s">
@@ -20576,7 +20528,7 @@
         <v>510</v>
       </c>
       <c r="B150" s="2">
-        <f>VLOOKUP(A150,'Candidatos E-26 ALC'!A180:I531,8,FALSE)</f>
+        <f>VLOOKUP(A150,'Candidatos E-26 ALC'!A180:I529,8,FALSE)</f>
         <v>6370</v>
       </c>
       <c r="C150" s="2" t="s">
@@ -20606,7 +20558,7 @@
         <v>403</v>
       </c>
       <c r="B151" s="2">
-        <f>VLOOKUP(A151,'Candidatos E-26 ALC'!A140:I491,8,FALSE)</f>
+        <f>VLOOKUP(A151,'Candidatos E-26 ALC'!A140:I489,8,FALSE)</f>
         <v>6165</v>
       </c>
       <c r="C151" s="2" t="s">
@@ -20636,7 +20588,7 @@
         <v>355</v>
       </c>
       <c r="B152" s="2">
-        <f>VLOOKUP(A152,'Candidatos E-26 ALC'!A124:I475,8,FALSE)</f>
+        <f>VLOOKUP(A152,'Candidatos E-26 ALC'!A124:I473,8,FALSE)</f>
         <v>6144</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -20666,7 +20618,7 @@
         <v>855</v>
       </c>
       <c r="B153" s="2">
-        <f>VLOOKUP(A153,'Candidatos E-26 ALC'!A323:I674,8,FALSE)</f>
+        <f>VLOOKUP(A153,'Candidatos E-26 ALC'!A321:I672,8,FALSE)</f>
         <v>6035</v>
       </c>
       <c r="C153" s="5" t="s">
@@ -20696,7 +20648,7 @@
         <v>673</v>
       </c>
       <c r="B154" s="2">
-        <f>VLOOKUP(A154,'Candidatos E-26 ALC'!A243:I594,8,FALSE)</f>
+        <f>VLOOKUP(A154,'Candidatos E-26 ALC'!A243:I592,8,FALSE)</f>
         <v>5953</v>
       </c>
       <c r="C154" s="5" t="s">
@@ -20726,7 +20678,7 @@
         <v>430</v>
       </c>
       <c r="B155" s="2">
-        <f>VLOOKUP(A155,'Candidatos E-26 ALC'!A150:I501,8,FALSE)</f>
+        <f>VLOOKUP(A155,'Candidatos E-26 ALC'!A150:I499,8,FALSE)</f>
         <v>5936</v>
       </c>
       <c r="C155" s="2" t="s">
@@ -20756,7 +20708,7 @@
         <v>642</v>
       </c>
       <c r="B156" s="2">
-        <f>VLOOKUP(A156,'Candidatos E-26 ALC'!A230:I581,8,FALSE)</f>
+        <f>VLOOKUP(A156,'Candidatos E-26 ALC'!A230:I579,8,FALSE)</f>
         <v>5851</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -20786,7 +20738,7 @@
         <v>925</v>
       </c>
       <c r="B157" s="2">
-        <f>VLOOKUP(A157,'Candidatos E-26 ALC'!A350:I701,8,FALSE)</f>
+        <f>VLOOKUP(A157,'Candidatos E-26 ALC'!A348:I699,8,FALSE)</f>
         <v>5839</v>
       </c>
       <c r="C157" s="2" t="s">
@@ -20816,7 +20768,7 @@
         <v>890</v>
       </c>
       <c r="B158" s="2">
-        <f>VLOOKUP(A158,'Candidatos E-26 ALC'!A337:I688,8,FALSE)</f>
+        <f>VLOOKUP(A158,'Candidatos E-26 ALC'!A335:I686,8,FALSE)</f>
         <v>5799</v>
       </c>
       <c r="C158" s="5" t="s">
@@ -20846,7 +20798,7 @@
         <v>346</v>
       </c>
       <c r="B159" s="2">
-        <f>VLOOKUP(A159,'Candidatos E-26 ALC'!A120:I471,8,FALSE)</f>
+        <f>VLOOKUP(A159,'Candidatos E-26 ALC'!A120:I469,8,FALSE)</f>
         <v>5790</v>
       </c>
       <c r="C159" s="2" t="s">
@@ -20876,7 +20828,7 @@
         <v>312</v>
       </c>
       <c r="B160" s="2">
-        <f>VLOOKUP(A160,'Candidatos E-26 ALC'!A106:I457,8,FALSE)</f>
+        <f>VLOOKUP(A160,'Candidatos E-26 ALC'!A106:I455,8,FALSE)</f>
         <v>5786</v>
       </c>
       <c r="C160" s="2" t="s">
@@ -20906,7 +20858,7 @@
         <v>742</v>
       </c>
       <c r="B161" s="2">
-        <f>VLOOKUP(A161,'Candidatos E-26 ALC'!A272:I623,8,FALSE)</f>
+        <f>VLOOKUP(A161,'Candidatos E-26 ALC'!A270:I621,8,FALSE)</f>
         <v>5729</v>
       </c>
       <c r="C161" s="2" t="s">
@@ -20936,7 +20888,7 @@
         <v>742</v>
       </c>
       <c r="B162" s="2">
-        <f>VLOOKUP(A162,'Candidatos E-26 ALC'!A273:I624,8,FALSE)</f>
+        <f>VLOOKUP(A162,'Candidatos E-26 ALC'!A271:I622,8,FALSE)</f>
         <v>5729</v>
       </c>
       <c r="C162" s="5" t="s">
@@ -20966,7 +20918,7 @@
         <v>478</v>
       </c>
       <c r="B163" s="2">
-        <f>VLOOKUP(A163,'Candidatos E-26 ALC'!A167:I518,8,FALSE)</f>
+        <f>VLOOKUP(A163,'Candidatos E-26 ALC'!A167:I516,8,FALSE)</f>
         <v>5697</v>
       </c>
       <c r="C163" s="5" t="s">
@@ -20996,7 +20948,7 @@
         <v>541</v>
       </c>
       <c r="B164" s="2">
-        <f>VLOOKUP(A164,'Candidatos E-26 ALC'!A192:I543,8,FALSE)</f>
+        <f>VLOOKUP(A164,'Candidatos E-26 ALC'!A192:I541,8,FALSE)</f>
         <v>5637</v>
       </c>
       <c r="C164" s="2" t="s">
@@ -21026,7 +20978,7 @@
         <v>340</v>
       </c>
       <c r="B165" s="2">
-        <f>VLOOKUP(A165,'Candidatos E-26 ALC'!A117:I468,8,FALSE)</f>
+        <f>VLOOKUP(A165,'Candidatos E-26 ALC'!A117:I466,8,FALSE)</f>
         <v>5387</v>
       </c>
       <c r="C165" s="5" t="s">
@@ -21056,7 +21008,7 @@
         <v>286</v>
       </c>
       <c r="B166" s="2">
-        <f>VLOOKUP(A166,'Candidatos E-26 ALC'!A97:I448,8,FALSE)</f>
+        <f>VLOOKUP(A166,'Candidatos E-26 ALC'!A97:I446,8,FALSE)</f>
         <v>5380</v>
       </c>
       <c r="C166" s="5" t="s">
@@ -21086,7 +21038,7 @@
         <v>625</v>
       </c>
       <c r="B167" s="2">
-        <f>VLOOKUP(A167,'Candidatos E-26 ALC'!A223:I574,8,FALSE)</f>
+        <f>VLOOKUP(A167,'Candidatos E-26 ALC'!A223:I572,8,FALSE)</f>
         <v>5346</v>
       </c>
       <c r="C167" s="5" t="s">
@@ -21116,7 +21068,7 @@
         <v>636</v>
       </c>
       <c r="B168" s="2">
-        <f>VLOOKUP(A168,'Candidatos E-26 ALC'!A227:I578,8,FALSE)</f>
+        <f>VLOOKUP(A168,'Candidatos E-26 ALC'!A227:I576,8,FALSE)</f>
         <v>5270</v>
       </c>
       <c r="C168" s="5" t="s">
@@ -21146,7 +21098,7 @@
         <v>830</v>
       </c>
       <c r="B169" s="2">
-        <f>VLOOKUP(A169,'Candidatos E-26 ALC'!A313:I664,8,FALSE)</f>
+        <f>VLOOKUP(A169,'Candidatos E-26 ALC'!A311:I662,8,FALSE)</f>
         <v>5215</v>
       </c>
       <c r="C169" s="5" t="s">
@@ -21176,7 +21128,7 @@
         <v>64</v>
       </c>
       <c r="B170" s="2">
-        <f>VLOOKUP(A170,'Candidatos E-26 ALC'!A18:I369,8,FALSE)</f>
+        <f>VLOOKUP(A170,'Candidatos E-26 ALC'!A18:I367,8,FALSE)</f>
         <v>5135</v>
       </c>
       <c r="C170" s="2" t="s">
@@ -21206,7 +21158,7 @@
         <v>593</v>
       </c>
       <c r="B171" s="2">
-        <f>VLOOKUP(A171,'Candidatos E-26 ALC'!A211:I562,8,FALSE)</f>
+        <f>VLOOKUP(A171,'Candidatos E-26 ALC'!A211:I560,8,FALSE)</f>
         <v>5044</v>
       </c>
       <c r="C171" s="5" t="s">
@@ -21236,7 +21188,7 @@
         <v>903</v>
       </c>
       <c r="B172" s="2">
-        <f>VLOOKUP(A172,'Candidatos E-26 ALC'!A341:I692,8,FALSE)</f>
+        <f>VLOOKUP(A172,'Candidatos E-26 ALC'!A339:I690,8,FALSE)</f>
         <v>4900</v>
       </c>
       <c r="C172" s="5" t="s">
@@ -21266,7 +21218,7 @@
         <v>133</v>
       </c>
       <c r="B173" s="2">
-        <f>VLOOKUP(A173,'Candidatos E-26 ALC'!A42:I393,8,FALSE)</f>
+        <f>VLOOKUP(A173,'Candidatos E-26 ALC'!A42:I391,8,FALSE)</f>
         <v>4874</v>
       </c>
       <c r="C173" s="2" t="s">
@@ -21296,7 +21248,7 @@
         <v>461</v>
       </c>
       <c r="B174" s="2">
-        <f>VLOOKUP(A174,'Candidatos E-26 ALC'!A161:I512,8,FALSE)</f>
+        <f>VLOOKUP(A174,'Candidatos E-26 ALC'!A161:I510,8,FALSE)</f>
         <v>4758</v>
       </c>
       <c r="C174" s="5" t="s">
@@ -21326,7 +21278,7 @@
         <v>321</v>
       </c>
       <c r="B175" s="2">
-        <f>VLOOKUP(A175,'Candidatos E-26 ALC'!A110:I461,8,FALSE)</f>
+        <f>VLOOKUP(A175,'Candidatos E-26 ALC'!A110:I459,8,FALSE)</f>
         <v>4676</v>
       </c>
       <c r="C175" s="2" t="s">
@@ -21356,7 +21308,7 @@
         <v>612</v>
       </c>
       <c r="B176" s="2">
-        <f>VLOOKUP(A176,'Candidatos E-26 ALC'!A218:I569,8,FALSE)</f>
+        <f>VLOOKUP(A176,'Candidatos E-26 ALC'!A218:I567,8,FALSE)</f>
         <v>4648</v>
       </c>
       <c r="C176" s="2" t="s">
@@ -21386,7 +21338,7 @@
         <v>145</v>
       </c>
       <c r="B177" s="2">
-        <f>VLOOKUP(A177,'Candidatos E-26 ALC'!A46:I397,8,FALSE)</f>
+        <f>VLOOKUP(A177,'Candidatos E-26 ALC'!A46:I395,8,FALSE)</f>
         <v>4439</v>
       </c>
       <c r="C177" s="2" t="s">
@@ -21416,7 +21368,7 @@
         <v>707</v>
       </c>
       <c r="B178" s="2">
-        <f>VLOOKUP(A178,'Candidatos E-26 ALC'!A257:I608,8,FALSE)</f>
+        <f>VLOOKUP(A178,'Candidatos E-26 ALC'!A257:I606,8,FALSE)</f>
         <v>4396</v>
       </c>
       <c r="C178" s="5" t="s">
@@ -21446,7 +21398,7 @@
         <v>551</v>
       </c>
       <c r="B179" s="2">
-        <f>VLOOKUP(A179,'Candidatos E-26 ALC'!A196:I547,8,FALSE)</f>
+        <f>VLOOKUP(A179,'Candidatos E-26 ALC'!A196:I545,8,FALSE)</f>
         <v>4376</v>
       </c>
       <c r="C179" s="2" t="s">
@@ -21476,7 +21428,7 @@
         <v>778</v>
       </c>
       <c r="B180" s="2">
-        <f>VLOOKUP(A180,'Candidatos E-26 ALC'!A293:I644,8,FALSE)</f>
+        <f>VLOOKUP(A180,'Candidatos E-26 ALC'!A291:I642,8,FALSE)</f>
         <v>4374</v>
       </c>
       <c r="C180" s="5" t="s">
@@ -21506,7 +21458,7 @@
         <v>418</v>
       </c>
       <c r="B181" s="2">
-        <f>VLOOKUP(A181,'Candidatos E-26 ALC'!A146:I497,8,FALSE)</f>
+        <f>VLOOKUP(A181,'Candidatos E-26 ALC'!A146:I495,8,FALSE)</f>
         <v>4321</v>
       </c>
       <c r="C181" s="2" t="s">
@@ -21536,7 +21488,7 @@
         <v>515</v>
       </c>
       <c r="B182" s="2">
-        <f>VLOOKUP(A182,'Candidatos E-26 ALC'!A182:I533,8,FALSE)</f>
+        <f>VLOOKUP(A182,'Candidatos E-26 ALC'!A182:I531,8,FALSE)</f>
         <v>4172</v>
       </c>
       <c r="C182" s="2" t="s">
@@ -21566,7 +21518,7 @@
         <v>297</v>
       </c>
       <c r="B183" s="2">
-        <f>VLOOKUP(A183,'Candidatos E-26 ALC'!A101:I452,8,FALSE)</f>
+        <f>VLOOKUP(A183,'Candidatos E-26 ALC'!A101:I450,8,FALSE)</f>
         <v>4109</v>
       </c>
       <c r="C183" s="5" t="s">
@@ -21596,7 +21548,7 @@
         <v>586</v>
       </c>
       <c r="B184" s="2">
-        <f>VLOOKUP(A184,'Candidatos E-26 ALC'!A208:I559,8,FALSE)</f>
+        <f>VLOOKUP(A184,'Candidatos E-26 ALC'!A208:I557,8,FALSE)</f>
         <v>4018</v>
       </c>
       <c r="C184" s="2" t="s">
@@ -21626,7 +21578,7 @@
         <v>705</v>
       </c>
       <c r="B185" s="2">
-        <f>VLOOKUP(A185,'Candidatos E-26 ALC'!A256:I607,8,FALSE)</f>
+        <f>VLOOKUP(A185,'Candidatos E-26 ALC'!A256:I605,8,FALSE)</f>
         <v>3988</v>
       </c>
       <c r="C185" s="2" t="s">
@@ -21656,7 +21608,7 @@
         <v>513</v>
       </c>
       <c r="B186" s="2">
-        <f>VLOOKUP(A186,'Candidatos E-26 ALC'!A181:I532,8,FALSE)</f>
+        <f>VLOOKUP(A186,'Candidatos E-26 ALC'!A181:I530,8,FALSE)</f>
         <v>3944</v>
       </c>
       <c r="C186" s="5" t="s">
@@ -21686,7 +21638,7 @@
         <v>486</v>
       </c>
       <c r="B187" s="2">
-        <f>VLOOKUP(A187,'Candidatos E-26 ALC'!A171:I522,8,FALSE)</f>
+        <f>VLOOKUP(A187,'Candidatos E-26 ALC'!A171:I520,8,FALSE)</f>
         <v>3835</v>
       </c>
       <c r="C187" s="5" t="s">
@@ -21716,7 +21668,7 @@
         <v>695</v>
       </c>
       <c r="B188" s="2">
-        <f>VLOOKUP(A188,'Candidatos E-26 ALC'!A252:I603,8,FALSE)</f>
+        <f>VLOOKUP(A188,'Candidatos E-26 ALC'!A252:I601,8,FALSE)</f>
         <v>3761</v>
       </c>
       <c r="C188" s="2" t="s">
@@ -21746,7 +21698,7 @@
         <v>344</v>
       </c>
       <c r="B189" s="2">
-        <f>VLOOKUP(A189,'Candidatos E-26 ALC'!A119:I470,8,FALSE)</f>
+        <f>VLOOKUP(A189,'Candidatos E-26 ALC'!A119:I468,8,FALSE)</f>
         <v>3388</v>
       </c>
       <c r="C189" s="5" t="s">
@@ -21776,7 +21728,7 @@
         <v>413</v>
       </c>
       <c r="B190" s="2">
-        <f>VLOOKUP(A190,'Candidatos E-26 ALC'!A144:I495,8,FALSE)</f>
+        <f>VLOOKUP(A190,'Candidatos E-26 ALC'!A144:I493,8,FALSE)</f>
         <v>3322</v>
       </c>
       <c r="C190" s="2" t="s">
@@ -21806,7 +21758,7 @@
         <v>502</v>
       </c>
       <c r="B191" s="2">
-        <f>VLOOKUP(A191,'Candidatos E-26 ALC'!A177:I528,8,FALSE)</f>
+        <f>VLOOKUP(A191,'Candidatos E-26 ALC'!A177:I526,8,FALSE)</f>
         <v>3214</v>
       </c>
       <c r="C191" s="5" t="s">
@@ -21836,7 +21788,7 @@
         <v>316</v>
       </c>
       <c r="B192" s="2">
-        <f>VLOOKUP(A192,'Candidatos E-26 ALC'!A108:I459,8,FALSE)</f>
+        <f>VLOOKUP(A192,'Candidatos E-26 ALC'!A108:I457,8,FALSE)</f>
         <v>3188</v>
       </c>
       <c r="C192" s="2" t="s">
@@ -21866,7 +21818,7 @@
         <v>649</v>
       </c>
       <c r="B193" s="2">
-        <f>VLOOKUP(A193,'Candidatos E-26 ALC'!A233:I584,8,FALSE)</f>
+        <f>VLOOKUP(A193,'Candidatos E-26 ALC'!A233:I582,8,FALSE)</f>
         <v>3145</v>
       </c>
       <c r="C193" s="5" t="s">
@@ -21896,7 +21848,7 @@
         <v>493</v>
       </c>
       <c r="B194" s="2">
-        <f>VLOOKUP(A194,'Candidatos E-26 ALC'!A174:I525,8,FALSE)</f>
+        <f>VLOOKUP(A194,'Candidatos E-26 ALC'!A174:I523,8,FALSE)</f>
         <v>3119</v>
       </c>
       <c r="C194" s="2" t="s">
@@ -21926,7 +21878,7 @@
         <v>468</v>
       </c>
       <c r="B195" s="2">
-        <f>VLOOKUP(A195,'Candidatos E-26 ALC'!A164:I515,8,FALSE)</f>
+        <f>VLOOKUP(A195,'Candidatos E-26 ALC'!A164:I513,8,FALSE)</f>
         <v>3030</v>
       </c>
       <c r="C195" s="2" t="s">
@@ -21956,7 +21908,7 @@
         <v>261</v>
       </c>
       <c r="B196" s="2">
-        <f>VLOOKUP(A196,'Candidatos E-26 ALC'!A88:I439,8,FALSE)</f>
+        <f>VLOOKUP(A196,'Candidatos E-26 ALC'!A88:I437,8,FALSE)</f>
         <v>2973</v>
       </c>
       <c r="C196" s="2" t="s">
@@ -21986,7 +21938,7 @@
         <v>488</v>
       </c>
       <c r="B197" s="2">
-        <f>VLOOKUP(A197,'Candidatos E-26 ALC'!A172:I523,8,FALSE)</f>
+        <f>VLOOKUP(A197,'Candidatos E-26 ALC'!A172:I521,8,FALSE)</f>
         <v>2792</v>
       </c>
       <c r="C197" s="2" t="s">
@@ -22016,7 +21968,7 @@
         <v>314</v>
       </c>
       <c r="B198" s="2">
-        <f>VLOOKUP(A198,'Candidatos E-26 ALC'!A107:I458,8,FALSE)</f>
+        <f>VLOOKUP(A198,'Candidatos E-26 ALC'!A107:I456,8,FALSE)</f>
         <v>2753</v>
       </c>
       <c r="C198" s="5" t="s">
@@ -22046,7 +21998,7 @@
         <v>519</v>
       </c>
       <c r="B199" s="2">
-        <f>VLOOKUP(A199,'Candidatos E-26 ALC'!A184:I535,8,FALSE)</f>
+        <f>VLOOKUP(A199,'Candidatos E-26 ALC'!A184:I533,8,FALSE)</f>
         <v>2749</v>
       </c>
       <c r="C199" s="2" t="s">
@@ -22076,7 +22028,7 @@
         <v>115</v>
       </c>
       <c r="B200" s="2">
-        <f>VLOOKUP(A200,'Candidatos E-26 ALC'!A36:I387,8,FALSE)</f>
+        <f>VLOOKUP(A200,'Candidatos E-26 ALC'!A36:I385,8,FALSE)</f>
         <v>2740</v>
       </c>
       <c r="C200" s="2" t="s">
@@ -22106,7 +22058,7 @@
         <v>186</v>
       </c>
       <c r="B201" s="2">
-        <f>VLOOKUP(A201,'Candidatos E-26 ALC'!A60:I411,8,FALSE)</f>
+        <f>VLOOKUP(A201,'Candidatos E-26 ALC'!A60:I409,8,FALSE)</f>
         <v>2730</v>
       </c>
       <c r="C201" s="2" t="s">
@@ -22144,7 +22096,7 @@
         <v>530</v>
       </c>
       <c r="B202" s="2">
-        <f>VLOOKUP(A202,'Candidatos E-26 ALC'!A188:I539,8,FALSE)</f>
+        <f>VLOOKUP(A202,'Candidatos E-26 ALC'!A188:I537,8,FALSE)</f>
         <v>2676</v>
       </c>
       <c r="C202" s="2" t="s">
@@ -22174,7 +22126,7 @@
         <v>480</v>
       </c>
       <c r="B203" s="2">
-        <f>VLOOKUP(A203,'Candidatos E-26 ALC'!A168:I519,8,FALSE)</f>
+        <f>VLOOKUP(A203,'Candidatos E-26 ALC'!A168:I517,8,FALSE)</f>
         <v>2647</v>
       </c>
       <c r="C203" s="2" t="s">
@@ -22204,7 +22156,7 @@
         <v>582</v>
       </c>
       <c r="B204" s="2">
-        <f>VLOOKUP(A204,'Candidatos E-26 ALC'!A207:I558,8,FALSE)</f>
+        <f>VLOOKUP(A204,'Candidatos E-26 ALC'!A207:I556,8,FALSE)</f>
         <v>2601</v>
       </c>
       <c r="C204" s="5" t="s">
@@ -22234,7 +22186,7 @@
         <v>215</v>
       </c>
       <c r="B205" s="2">
-        <f>VLOOKUP(A205,'Candidatos E-26 ALC'!A71:I422,8,FALSE)</f>
+        <f>VLOOKUP(A205,'Candidatos E-26 ALC'!A71:I420,8,FALSE)</f>
         <v>2544</v>
       </c>
       <c r="C205" s="5" t="s">
@@ -22264,7 +22216,7 @@
         <v>72</v>
       </c>
       <c r="B206" s="2">
-        <f>VLOOKUP(A206,'Candidatos E-26 ALC'!A21:I372,8,FALSE)</f>
+        <f>VLOOKUP(A206,'Candidatos E-26 ALC'!A21:I370,8,FALSE)</f>
         <v>2516</v>
       </c>
       <c r="C206" s="5" t="s">
@@ -22294,7 +22246,7 @@
         <v>718</v>
       </c>
       <c r="B207" s="2">
-        <f>VLOOKUP(A207,'Candidatos E-26 ALC'!A261:I612,8,FALSE)</f>
+        <f>VLOOKUP(A207,'Candidatos E-26 ALC'!A261:I610,8,FALSE)</f>
         <v>2447</v>
       </c>
       <c r="C207" s="5" t="s">
@@ -22324,7 +22276,7 @@
         <v>629</v>
       </c>
       <c r="B208" s="2">
-        <f>VLOOKUP(A208,'Candidatos E-26 ALC'!A225:I576,8,FALSE)</f>
+        <f>VLOOKUP(A208,'Candidatos E-26 ALC'!A225:I574,8,FALSE)</f>
         <v>2397</v>
       </c>
       <c r="C208" s="5" t="s">
@@ -22354,7 +22306,7 @@
         <v>353</v>
       </c>
       <c r="B209" s="2">
-        <f>VLOOKUP(A209,'Candidatos E-26 ALC'!A123:I474,8,FALSE)</f>
+        <f>VLOOKUP(A209,'Candidatos E-26 ALC'!A123:I472,8,FALSE)</f>
         <v>2382</v>
       </c>
       <c r="C209" s="5" t="s">
@@ -22384,7 +22336,7 @@
         <v>595</v>
       </c>
       <c r="B210" s="2">
-        <f>VLOOKUP(A210,'Candidatos E-26 ALC'!A212:I563,8,FALSE)</f>
+        <f>VLOOKUP(A210,'Candidatos E-26 ALC'!A212:I561,8,FALSE)</f>
         <v>2369</v>
       </c>
       <c r="C210" s="2" t="s">
@@ -22414,7 +22366,7 @@
         <v>253</v>
       </c>
       <c r="B211" s="2">
-        <f>VLOOKUP(A211,'Candidatos E-26 ALC'!A84:I435,8,FALSE)</f>
+        <f>VLOOKUP(A211,'Candidatos E-26 ALC'!A84:I433,8,FALSE)</f>
         <v>2127</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -22444,7 +22396,7 @@
         <v>691</v>
       </c>
       <c r="B212" s="2">
-        <f>VLOOKUP(A212,'Candidatos E-26 ALC'!A250:I601,8,FALSE)</f>
+        <f>VLOOKUP(A212,'Candidatos E-26 ALC'!A250:I599,8,FALSE)</f>
         <v>2053</v>
       </c>
       <c r="C212" s="2" t="s">
@@ -22474,7 +22426,7 @@
         <v>158</v>
       </c>
       <c r="B213" s="2">
-        <f>VLOOKUP(A213,'Candidatos E-26 ALC'!A51:I402,8,FALSE)</f>
+        <f>VLOOKUP(A213,'Candidatos E-26 ALC'!A51:I400,8,FALSE)</f>
         <v>2035</v>
       </c>
       <c r="C213" s="5" t="s">
@@ -22504,7 +22456,7 @@
         <v>888</v>
       </c>
       <c r="B214" s="2">
-        <f>VLOOKUP(A214,'Candidatos E-26 ALC'!A336:I687,8,FALSE)</f>
+        <f>VLOOKUP(A214,'Candidatos E-26 ALC'!A334:I685,8,FALSE)</f>
         <v>2027</v>
       </c>
       <c r="C214" s="2" t="s">
@@ -22534,7 +22486,7 @@
         <v>283</v>
       </c>
       <c r="B215" s="2">
-        <f>VLOOKUP(A215,'Candidatos E-26 ALC'!A96:I447,8,FALSE)</f>
+        <f>VLOOKUP(A215,'Candidatos E-26 ALC'!A96:I445,8,FALSE)</f>
         <v>1947</v>
       </c>
       <c r="C215" s="2" t="s">
@@ -22564,7 +22516,7 @@
         <v>61</v>
       </c>
       <c r="B216" s="2">
-        <f>VLOOKUP(A216,'Candidatos E-26 ALC'!A17:I368,8,FALSE)</f>
+        <f>VLOOKUP(A216,'Candidatos E-26 ALC'!A17:I366,8,FALSE)</f>
         <v>1928</v>
       </c>
       <c r="C216" s="5" t="s">
@@ -22594,7 +22546,7 @@
         <v>78</v>
       </c>
       <c r="B217" s="2">
-        <f>VLOOKUP(A217,'Candidatos E-26 ALC'!A23:I374,8,FALSE)</f>
+        <f>VLOOKUP(A217,'Candidatos E-26 ALC'!A23:I372,8,FALSE)</f>
         <v>1914</v>
       </c>
       <c r="C217" s="5" t="s">
@@ -22624,7 +22576,7 @@
         <v>323</v>
       </c>
       <c r="B218" s="2">
-        <f>VLOOKUP(A218,'Candidatos E-26 ALC'!A111:I462,8,FALSE)</f>
+        <f>VLOOKUP(A218,'Candidatos E-26 ALC'!A111:I460,8,FALSE)</f>
         <v>1879</v>
       </c>
       <c r="C218" s="5" t="s">
@@ -22654,7 +22606,7 @@
         <v>744</v>
       </c>
       <c r="B219" s="2">
-        <f>VLOOKUP(A219,'Candidatos E-26 ALC'!A274:I625,8,FALSE)</f>
+        <f>VLOOKUP(A219,'Candidatos E-26 ALC'!A272:I623,8,FALSE)</f>
         <v>1871</v>
       </c>
       <c r="C219" s="2" t="s">
@@ -22684,7 +22636,7 @@
         <v>744</v>
       </c>
       <c r="B220" s="2">
-        <f>VLOOKUP(A220,'Candidatos E-26 ALC'!A275:I626,8,FALSE)</f>
+        <f>VLOOKUP(A220,'Candidatos E-26 ALC'!A273:I624,8,FALSE)</f>
         <v>1871</v>
       </c>
       <c r="C220" s="5" t="s">
@@ -22714,7 +22666,7 @@
         <v>228</v>
       </c>
       <c r="B221" s="2">
-        <f>VLOOKUP(A221,'Candidatos E-26 ALC'!A76:I427,8,FALSE)</f>
+        <f>VLOOKUP(A221,'Candidatos E-26 ALC'!A76:I425,8,FALSE)</f>
         <v>1779</v>
       </c>
       <c r="C221" s="2" t="s">
@@ -22744,7 +22696,7 @@
         <v>766</v>
       </c>
       <c r="B222" s="2">
-        <f>VLOOKUP(A222,'Candidatos E-26 ALC'!A288:I639,8,FALSE)</f>
+        <f>VLOOKUP(A222,'Candidatos E-26 ALC'!A286:I637,8,FALSE)</f>
         <v>1770</v>
       </c>
       <c r="C222" s="2" t="s">
@@ -22774,7 +22726,7 @@
         <v>244</v>
       </c>
       <c r="B223" s="2">
-        <f>VLOOKUP(A223,'Candidatos E-26 ALC'!A81:I432,8,FALSE)</f>
+        <f>VLOOKUP(A223,'Candidatos E-26 ALC'!A81:I430,8,FALSE)</f>
         <v>1734</v>
       </c>
       <c r="C223" s="5" t="s">
@@ -22804,7 +22756,7 @@
         <v>517</v>
       </c>
       <c r="B224" s="2">
-        <f>VLOOKUP(A224,'Candidatos E-26 ALC'!A183:I534,8,FALSE)</f>
+        <f>VLOOKUP(A224,'Candidatos E-26 ALC'!A183:I532,8,FALSE)</f>
         <v>1714</v>
       </c>
       <c r="C224" s="5" t="s">
@@ -22834,7 +22786,7 @@
         <v>470</v>
       </c>
       <c r="B225" s="2">
-        <f>VLOOKUP(A225,'Candidatos E-26 ALC'!A165:I516,8,FALSE)</f>
+        <f>VLOOKUP(A225,'Candidatos E-26 ALC'!A165:I514,8,FALSE)</f>
         <v>1669</v>
       </c>
       <c r="C225" s="5" t="s">
@@ -22864,7 +22816,7 @@
         <v>263</v>
       </c>
       <c r="B226" s="2">
-        <f>VLOOKUP(A226,'Candidatos E-26 ALC'!A89:I440,8,FALSE)</f>
+        <f>VLOOKUP(A226,'Candidatos E-26 ALC'!A89:I438,8,FALSE)</f>
         <v>1608</v>
       </c>
       <c r="C226" s="5" t="s">
@@ -22894,7 +22846,7 @@
         <v>662</v>
       </c>
       <c r="B227" s="2">
-        <f>VLOOKUP(A227,'Candidatos E-26 ALC'!A238:I589,8,FALSE)</f>
+        <f>VLOOKUP(A227,'Candidatos E-26 ALC'!A238:I587,8,FALSE)</f>
         <v>1585</v>
       </c>
       <c r="C227" s="2" t="s">
@@ -22924,7 +22876,7 @@
         <v>318</v>
       </c>
       <c r="B228" s="2">
-        <f>VLOOKUP(A228,'Candidatos E-26 ALC'!A109:I460,8,FALSE)</f>
+        <f>VLOOKUP(A228,'Candidatos E-26 ALC'!A109:I458,8,FALSE)</f>
         <v>1579</v>
       </c>
       <c r="C228" s="5" t="s">
@@ -22954,7 +22906,7 @@
         <v>150</v>
       </c>
       <c r="B229" s="2">
-        <f>VLOOKUP(A229,'Candidatos E-26 ALC'!A48:I399,8,FALSE)</f>
+        <f>VLOOKUP(A229,'Candidatos E-26 ALC'!A48:I397,8,FALSE)</f>
         <v>1562</v>
       </c>
       <c r="C229" s="2" t="s">
@@ -22984,7 +22936,7 @@
         <v>335</v>
       </c>
       <c r="B230" s="2">
-        <f>VLOOKUP(A230,'Candidatos E-26 ALC'!A116:I467,8,FALSE)</f>
+        <f>VLOOKUP(A230,'Candidatos E-26 ALC'!A116:I465,8,FALSE)</f>
         <v>1521</v>
       </c>
       <c r="C230" s="2" t="s">
@@ -23014,7 +22966,7 @@
         <v>53</v>
       </c>
       <c r="B231" s="2">
-        <f>VLOOKUP(A231,'Candidatos E-26 ALC'!A14:I365,8,FALSE)</f>
+        <f>VLOOKUP(A231,'Candidatos E-26 ALC'!A14:I363,8,FALSE)</f>
         <v>1503</v>
       </c>
       <c r="C231" s="2" t="s">
@@ -23044,7 +22996,7 @@
         <v>826</v>
       </c>
       <c r="B232" s="2">
-        <f>VLOOKUP(A232,'Candidatos E-26 ALC'!A311:I662,8,FALSE)</f>
+        <f>VLOOKUP(A232,'Candidatos E-26 ALC'!A309:I660,8,FALSE)</f>
         <v>1502</v>
       </c>
       <c r="C232" s="5" t="s">
@@ -23074,7 +23026,7 @@
         <v>816</v>
       </c>
       <c r="B233" s="2">
-        <f>VLOOKUP(A233,'Candidatos E-26 ALC'!A307:I658,8,FALSE)</f>
+        <f>VLOOKUP(A233,'Candidatos E-26 ALC'!A305:I656,8,FALSE)</f>
         <v>1482</v>
       </c>
       <c r="C233" s="5" t="s">
@@ -23104,7 +23056,7 @@
         <v>435</v>
       </c>
       <c r="B234" s="2">
-        <f>VLOOKUP(A234,'Candidatos E-26 ALC'!A152:I503,8,FALSE)</f>
+        <f>VLOOKUP(A234,'Candidatos E-26 ALC'!A152:I501,8,FALSE)</f>
         <v>1458</v>
       </c>
       <c r="C234" s="2" t="s">
@@ -23134,7 +23086,7 @@
         <v>764</v>
       </c>
       <c r="B235" s="2">
-        <f>VLOOKUP(A235,'Candidatos E-26 ALC'!A287:I638,8,FALSE)</f>
+        <f>VLOOKUP(A235,'Candidatos E-26 ALC'!A285:I636,8,FALSE)</f>
         <v>1419</v>
       </c>
       <c r="C235" s="5" t="s">
@@ -23164,7 +23116,7 @@
         <v>746</v>
       </c>
       <c r="B236" s="2">
-        <f>VLOOKUP(A236,'Candidatos E-26 ALC'!A276:I627,8,FALSE)</f>
+        <f>VLOOKUP(A236,'Candidatos E-26 ALC'!A274:I625,8,FALSE)</f>
         <v>1400</v>
       </c>
       <c r="C236" s="2" t="s">
@@ -23194,7 +23146,7 @@
         <v>746</v>
       </c>
       <c r="B237" s="2">
-        <f>VLOOKUP(A237,'Candidatos E-26 ALC'!A277:I628,8,FALSE)</f>
+        <f>VLOOKUP(A237,'Candidatos E-26 ALC'!A275:I626,8,FALSE)</f>
         <v>1400</v>
       </c>
       <c r="C237" s="5" t="s">
@@ -23224,7 +23176,7 @@
         <v>822</v>
       </c>
       <c r="B238" s="2">
-        <f>VLOOKUP(A238,'Candidatos E-26 ALC'!A309:I660,8,FALSE)</f>
+        <f>VLOOKUP(A238,'Candidatos E-26 ALC'!A307:I658,8,FALSE)</f>
         <v>1367</v>
       </c>
       <c r="C238" s="5" t="s">
@@ -23254,7 +23206,7 @@
         <v>342</v>
       </c>
       <c r="B239" s="2">
-        <f>VLOOKUP(A239,'Candidatos E-26 ALC'!A118:I469,8,FALSE)</f>
+        <f>VLOOKUP(A239,'Candidatos E-26 ALC'!A118:I467,8,FALSE)</f>
         <v>1365</v>
       </c>
       <c r="C239" s="2" t="s">
@@ -23284,7 +23236,7 @@
         <v>749</v>
       </c>
       <c r="B240" s="2">
-        <f>VLOOKUP(A240,'Candidatos E-26 ALC'!A278:I629,8,FALSE)</f>
+        <f>VLOOKUP(A240,'Candidatos E-26 ALC'!A276:I627,8,FALSE)</f>
         <v>1361</v>
       </c>
       <c r="C240" s="2" t="s">
@@ -23314,7 +23266,7 @@
         <v>749</v>
       </c>
       <c r="B241" s="2">
-        <f>VLOOKUP(A241,'Candidatos E-26 ALC'!A279:I630,8,FALSE)</f>
+        <f>VLOOKUP(A241,'Candidatos E-26 ALC'!A277:I628,8,FALSE)</f>
         <v>1361</v>
       </c>
       <c r="C241" s="5" t="s">
@@ -23344,7 +23296,7 @@
         <v>916</v>
       </c>
       <c r="B242" s="2">
-        <f>VLOOKUP(A242,'Candidatos E-26 ALC'!A346:I697,8,FALSE)</f>
+        <f>VLOOKUP(A242,'Candidatos E-26 ALC'!A344:I695,8,FALSE)</f>
         <v>1281</v>
       </c>
       <c r="C242" s="2" t="s">
@@ -23374,7 +23326,7 @@
         <v>776</v>
       </c>
       <c r="B243" s="2">
-        <f>VLOOKUP(A243,'Candidatos E-26 ALC'!A292:I643,8,FALSE)</f>
+        <f>VLOOKUP(A243,'Candidatos E-26 ALC'!A290:I641,8,FALSE)</f>
         <v>1251</v>
       </c>
       <c r="C243" s="2" t="s">
@@ -23404,7 +23356,7 @@
         <v>276</v>
       </c>
       <c r="B244" s="2">
-        <f>VLOOKUP(A244,'Candidatos E-26 ALC'!A94:I445,8,FALSE)</f>
+        <f>VLOOKUP(A244,'Candidatos E-26 ALC'!A94:I443,8,FALSE)</f>
         <v>1245</v>
       </c>
       <c r="C244" s="2" t="s">
@@ -23434,7 +23386,7 @@
         <v>9</v>
       </c>
       <c r="B245" s="2">
-        <f>VLOOKUP(A245,'Candidatos E-26 ALC'!A2:I353,8,FALSE)</f>
+        <f>VLOOKUP(A245,'Candidatos E-26 ALC'!A2:I351,8,FALSE)</f>
         <v>1238</v>
       </c>
       <c r="C245" s="2" t="s">
@@ -23464,7 +23416,7 @@
         <v>605</v>
       </c>
       <c r="B246" s="2">
-        <f>VLOOKUP(A246,'Candidatos E-26 ALC'!A216:I567,8,FALSE)</f>
+        <f>VLOOKUP(A246,'Candidatos E-26 ALC'!A216:I565,8,FALSE)</f>
         <v>1234</v>
       </c>
       <c r="C246" s="2" t="s">
@@ -23494,7 +23446,7 @@
         <v>837</v>
       </c>
       <c r="B247" s="2">
-        <f>VLOOKUP(A247,'Candidatos E-26 ALC'!A316:I667,8,FALSE)</f>
+        <f>VLOOKUP(A247,'Candidatos E-26 ALC'!A314:I665,8,FALSE)</f>
         <v>1227</v>
       </c>
       <c r="C247" s="2" t="s">
@@ -23524,7 +23476,7 @@
         <v>841</v>
       </c>
       <c r="B248" s="2">
-        <f>VLOOKUP(A248,'Candidatos E-26 ALC'!A318:I669,8,FALSE)</f>
+        <f>VLOOKUP(A248,'Candidatos E-26 ALC'!A316:I667,8,FALSE)</f>
         <v>1221</v>
       </c>
       <c r="C248" s="2" t="s">
@@ -23554,7 +23506,7 @@
         <v>546</v>
       </c>
       <c r="B249" s="2">
-        <f>VLOOKUP(A249,'Candidatos E-26 ALC'!A194:I545,8,FALSE)</f>
+        <f>VLOOKUP(A249,'Candidatos E-26 ALC'!A194:I543,8,FALSE)</f>
         <v>1200</v>
       </c>
       <c r="C249" s="2" t="s">
@@ -23584,7 +23536,7 @@
         <v>482</v>
       </c>
       <c r="B250" s="2">
-        <f>VLOOKUP(A250,'Candidatos E-26 ALC'!A169:I520,8,FALSE)</f>
+        <f>VLOOKUP(A250,'Candidatos E-26 ALC'!A169:I518,8,FALSE)</f>
         <v>1193</v>
       </c>
       <c r="C250" s="5" t="s">
@@ -23614,7 +23566,7 @@
         <v>751</v>
       </c>
       <c r="B251" s="2">
-        <f>VLOOKUP(A251,'Candidatos E-26 ALC'!A280:I631,8,FALSE)</f>
+        <f>VLOOKUP(A251,'Candidatos E-26 ALC'!A278:I629,8,FALSE)</f>
         <v>1192</v>
       </c>
       <c r="C251" s="2" t="s">
@@ -23644,7 +23596,7 @@
         <v>751</v>
       </c>
       <c r="B252" s="2">
-        <f>VLOOKUP(A252,'Candidatos E-26 ALC'!A281:I632,8,FALSE)</f>
+        <f>VLOOKUP(A252,'Candidatos E-26 ALC'!A279:I630,8,FALSE)</f>
         <v>1192</v>
       </c>
       <c r="C252" s="5" t="s">
@@ -23674,7 +23626,7 @@
         <v>656</v>
       </c>
       <c r="B253" s="2">
-        <f>VLOOKUP(A253,'Candidatos E-26 ALC'!A235:I586,8,FALSE)</f>
+        <f>VLOOKUP(A253,'Candidatos E-26 ALC'!A235:I584,8,FALSE)</f>
         <v>1189</v>
       </c>
       <c r="C253" s="5" t="s">
@@ -23704,7 +23656,7 @@
         <v>771</v>
       </c>
       <c r="B254" s="2">
-        <f>VLOOKUP(A254,'Candidatos E-26 ALC'!A290:I641,8,FALSE)</f>
+        <f>VLOOKUP(A254,'Candidatos E-26 ALC'!A288:I639,8,FALSE)</f>
         <v>1183</v>
       </c>
       <c r="C254" s="2" t="s">
@@ -23734,7 +23686,7 @@
         <v>304</v>
       </c>
       <c r="B255" s="2">
-        <f>VLOOKUP(A255,'Candidatos E-26 ALC'!A104:I455,8,FALSE)</f>
+        <f>VLOOKUP(A255,'Candidatos E-26 ALC'!A104:I453,8,FALSE)</f>
         <v>1173</v>
       </c>
       <c r="C255" s="2" t="s">
@@ -23764,7 +23716,7 @@
         <v>666</v>
       </c>
       <c r="B256" s="2">
-        <f>VLOOKUP(A256,'Candidatos E-26 ALC'!A240:I591,8,FALSE)</f>
+        <f>VLOOKUP(A256,'Candidatos E-26 ALC'!A240:I589,8,FALSE)</f>
         <v>1150</v>
       </c>
       <c r="C256" s="2" t="s">
@@ -23794,7 +23746,7 @@
         <v>505</v>
       </c>
       <c r="B257" s="2">
-        <f>VLOOKUP(A257,'Candidatos E-26 ALC'!A178:I529,8,FALSE)</f>
+        <f>VLOOKUP(A257,'Candidatos E-26 ALC'!A178:I527,8,FALSE)</f>
         <v>1107</v>
       </c>
       <c r="C257" s="2" t="s">
@@ -23824,7 +23776,7 @@
         <v>794</v>
       </c>
       <c r="B258" s="2">
-        <f>VLOOKUP(A258,'Candidatos E-26 ALC'!A299:I650,8,FALSE)</f>
+        <f>VLOOKUP(A258,'Candidatos E-26 ALC'!A297:I648,8,FALSE)</f>
         <v>1081</v>
       </c>
       <c r="C258" s="5" t="s">
@@ -23854,7 +23806,7 @@
         <v>204</v>
       </c>
       <c r="B259" s="2">
-        <f>VLOOKUP(A259,'Candidatos E-26 ALC'!A66:I417,8,FALSE)</f>
+        <f>VLOOKUP(A259,'Candidatos E-26 ALC'!A66:I415,8,FALSE)</f>
         <v>1050</v>
       </c>
       <c r="C259" s="2" t="s">
@@ -23884,7 +23836,7 @@
         <v>239</v>
       </c>
       <c r="B260" s="2">
-        <f>VLOOKUP(A260,'Candidatos E-26 ALC'!A79:I430,8,FALSE)</f>
+        <f>VLOOKUP(A260,'Candidatos E-26 ALC'!A79:I428,8,FALSE)</f>
         <v>1022</v>
       </c>
       <c r="C260" s="5" t="s">
@@ -23914,7 +23866,7 @@
         <v>100</v>
       </c>
       <c r="B261" s="2">
-        <f>VLOOKUP(A261,'Candidatos E-26 ALC'!A30:I381,8,FALSE)</f>
+        <f>VLOOKUP(A261,'Candidatos E-26 ALC'!A30:I379,8,FALSE)</f>
         <v>1020</v>
       </c>
       <c r="C261" s="2" t="s">
@@ -23944,7 +23896,7 @@
         <v>208</v>
       </c>
       <c r="B262" s="2">
-        <f>VLOOKUP(A262,'Candidatos E-26 ALC'!A68:I419,8,FALSE)</f>
+        <f>VLOOKUP(A262,'Candidatos E-26 ALC'!A68:I417,8,FALSE)</f>
         <v>1001</v>
       </c>
       <c r="C262" s="2" t="s">
@@ -23974,7 +23926,7 @@
         <v>94</v>
       </c>
       <c r="B263" s="2">
-        <f>VLOOKUP(A263,'Candidatos E-26 ALC'!A28:I379,8,FALSE)</f>
+        <f>VLOOKUP(A263,'Candidatos E-26 ALC'!A28:I377,8,FALSE)</f>
         <v>1000</v>
       </c>
       <c r="C263" s="2" t="s">
@@ -24004,7 +23956,7 @@
         <v>853</v>
       </c>
       <c r="B264" s="2">
-        <f>VLOOKUP(A264,'Candidatos E-26 ALC'!A322:I673,8,FALSE)</f>
+        <f>VLOOKUP(A264,'Candidatos E-26 ALC'!A320:I671,8,FALSE)</f>
         <v>999</v>
       </c>
       <c r="C264" s="2" t="s">
@@ -24034,7 +23986,7 @@
         <v>69</v>
       </c>
       <c r="B265" s="2">
-        <f>VLOOKUP(A265,'Candidatos E-26 ALC'!A20:I371,8,FALSE)</f>
+        <f>VLOOKUP(A265,'Candidatos E-26 ALC'!A20:I369,8,FALSE)</f>
         <v>983</v>
       </c>
       <c r="C265" s="2" t="s">
@@ -24064,7 +24016,7 @@
         <v>689</v>
       </c>
       <c r="B266" s="2">
-        <f>VLOOKUP(A266,'Candidatos E-26 ALC'!A249:I600,8,FALSE)</f>
+        <f>VLOOKUP(A266,'Candidatos E-26 ALC'!A249:I598,8,FALSE)</f>
         <v>980</v>
       </c>
       <c r="C266" s="5" t="s">
@@ -24094,7 +24046,7 @@
         <v>491</v>
       </c>
       <c r="B267" s="2">
-        <f>VLOOKUP(A267,'Candidatos E-26 ALC'!A173:I524,8,FALSE)</f>
+        <f>VLOOKUP(A267,'Candidatos E-26 ALC'!A173:I522,8,FALSE)</f>
         <v>969</v>
       </c>
       <c r="C267" s="5" t="s">
@@ -24124,7 +24076,7 @@
         <v>451</v>
       </c>
       <c r="B268" s="2">
-        <f>VLOOKUP(A268,'Candidatos E-26 ALC'!A158:I509,8,FALSE)</f>
+        <f>VLOOKUP(A268,'Candidatos E-26 ALC'!A158:I507,8,FALSE)</f>
         <v>953</v>
       </c>
       <c r="C268" s="2" t="s">
@@ -24154,7 +24106,7 @@
         <v>911</v>
       </c>
       <c r="B269" s="2">
-        <f>VLOOKUP(A269,'Candidatos E-26 ALC'!A344:I695,8,FALSE)</f>
+        <f>VLOOKUP(A269,'Candidatos E-26 ALC'!A342:I693,8,FALSE)</f>
         <v>943</v>
       </c>
       <c r="C269" s="2" t="s">
@@ -24184,7 +24136,7 @@
         <v>563</v>
       </c>
       <c r="B270" s="2">
-        <f>VLOOKUP(A270,'Candidatos E-26 ALC'!A200:I551,8,FALSE)</f>
+        <f>VLOOKUP(A270,'Candidatos E-26 ALC'!A200:I549,8,FALSE)</f>
         <v>889</v>
       </c>
       <c r="C270" s="2" t="s">
@@ -24214,7 +24166,7 @@
         <v>591</v>
       </c>
       <c r="B271" s="2">
-        <f>VLOOKUP(A271,'Candidatos E-26 ALC'!A210:I561,8,FALSE)</f>
+        <f>VLOOKUP(A271,'Candidatos E-26 ALC'!A210:I559,8,FALSE)</f>
         <v>872</v>
       </c>
       <c r="C271" s="2" t="s">
@@ -24244,7 +24196,7 @@
         <v>675</v>
       </c>
       <c r="B272" s="2">
-        <f>VLOOKUP(A272,'Candidatos E-26 ALC'!A244:I595,8,FALSE)</f>
+        <f>VLOOKUP(A272,'Candidatos E-26 ALC'!A244:I593,8,FALSE)</f>
         <v>867</v>
       </c>
       <c r="C272" s="2" t="s">
@@ -24274,7 +24226,7 @@
         <v>660</v>
       </c>
       <c r="B273" s="2">
-        <f>VLOOKUP(A273,'Candidatos E-26 ALC'!A237:I588,8,FALSE)</f>
+        <f>VLOOKUP(A273,'Candidatos E-26 ALC'!A237:I586,8,FALSE)</f>
         <v>853</v>
       </c>
       <c r="C273" s="5" t="s">
@@ -24304,7 +24256,7 @@
         <v>377</v>
       </c>
       <c r="B274" s="2">
-        <f>VLOOKUP(A274,'Candidatos E-26 ALC'!A131:I482,8,FALSE)</f>
+        <f>VLOOKUP(A274,'Candidatos E-26 ALC'!A131:I480,8,FALSE)</f>
         <v>824</v>
       </c>
       <c r="C274" s="5" t="s">
@@ -24334,7 +24286,7 @@
         <v>920</v>
       </c>
       <c r="B275" s="2">
-        <f>VLOOKUP(A275,'Candidatos E-26 ALC'!A348:I699,8,FALSE)</f>
+        <f>VLOOKUP(A275,'Candidatos E-26 ALC'!A346:I697,8,FALSE)</f>
         <v>802</v>
       </c>
       <c r="C275" s="2" t="s">
@@ -24364,7 +24316,7 @@
         <v>620</v>
       </c>
       <c r="B276" s="2">
-        <f>VLOOKUP(A276,'Candidatos E-26 ALC'!A221:I572,8,FALSE)</f>
+        <f>VLOOKUP(A276,'Candidatos E-26 ALC'!A221:I570,8,FALSE)</f>
         <v>781</v>
       </c>
       <c r="C276" s="5" t="s">
@@ -24394,7 +24346,7 @@
         <v>29</v>
       </c>
       <c r="B277" s="2">
-        <f>VLOOKUP(A277,'Candidatos E-26 ALC'!A7:I358,8,FALSE)</f>
+        <f>VLOOKUP(A277,'Candidatos E-26 ALC'!A7:I356,8,FALSE)</f>
         <v>774</v>
       </c>
       <c r="C277" s="5" t="s">
@@ -24424,7 +24376,7 @@
         <v>539</v>
       </c>
       <c r="B278" s="2">
-        <f>VLOOKUP(A278,'Candidatos E-26 ALC'!A191:I542,8,FALSE)</f>
+        <f>VLOOKUP(A278,'Candidatos E-26 ALC'!A191:I540,8,FALSE)</f>
         <v>771</v>
       </c>
       <c r="C278" s="5" t="s">
@@ -24454,7 +24406,7 @@
         <v>607</v>
       </c>
       <c r="B279" s="2">
-        <f>VLOOKUP(A279,'Candidatos E-26 ALC'!A217:I568,8,FALSE)</f>
+        <f>VLOOKUP(A279,'Candidatos E-26 ALC'!A217:I566,8,FALSE)</f>
         <v>764</v>
       </c>
       <c r="C279" s="5" t="s">
@@ -24484,7 +24436,7 @@
         <v>753</v>
       </c>
       <c r="B280" s="2">
-        <f>VLOOKUP(A280,'Candidatos E-26 ALC'!A282:I633,8,FALSE)</f>
+        <f>VLOOKUP(A280,'Candidatos E-26 ALC'!A280:I631,8,FALSE)</f>
         <v>756</v>
       </c>
       <c r="C280" s="2" t="s">
@@ -24514,7 +24466,7 @@
         <v>753</v>
       </c>
       <c r="B281" s="2">
-        <f>VLOOKUP(A281,'Candidatos E-26 ALC'!A283:I634,8,FALSE)</f>
+        <f>VLOOKUP(A281,'Candidatos E-26 ALC'!A281:I632,8,FALSE)</f>
         <v>756</v>
       </c>
       <c r="C281" s="5" t="s">
@@ -24544,7 +24496,7 @@
         <v>783</v>
       </c>
       <c r="B282" s="2">
-        <f>VLOOKUP(A282,'Candidatos E-26 ALC'!A295:I646,8,FALSE)</f>
+        <f>VLOOKUP(A282,'Candidatos E-26 ALC'!A293:I644,8,FALSE)</f>
         <v>735</v>
       </c>
       <c r="C282" s="5" t="s">
@@ -24574,7 +24526,7 @@
         <v>81</v>
       </c>
       <c r="B283" s="2">
-        <f>VLOOKUP(A283,'Candidatos E-26 ALC'!A24:I375,8,FALSE)</f>
+        <f>VLOOKUP(A283,'Candidatos E-26 ALC'!A24:I373,8,FALSE)</f>
         <v>698</v>
       </c>
       <c r="C283" s="2" t="s">
@@ -24604,7 +24556,7 @@
         <v>155</v>
       </c>
       <c r="B284" s="2">
-        <f>VLOOKUP(A284,'Candidatos E-26 ALC'!A50:I401,8,FALSE)</f>
+        <f>VLOOKUP(A284,'Candidatos E-26 ALC'!A50:I399,8,FALSE)</f>
         <v>684</v>
       </c>
       <c r="C284" s="2" t="s">
@@ -24634,7 +24586,7 @@
         <v>927</v>
       </c>
       <c r="B285" s="2">
-        <f>VLOOKUP(A285,'Candidatos E-26 ALC'!A351:I702,8,FALSE)</f>
+        <f>VLOOKUP(A285,'Candidatos E-26 ALC'!A349:I700,8,FALSE)</f>
         <v>658</v>
       </c>
       <c r="C285" s="5" t="s">
@@ -24664,7 +24616,7 @@
         <v>769</v>
       </c>
       <c r="B286" s="2">
-        <f>VLOOKUP(A286,'Candidatos E-26 ALC'!A289:I640,8,FALSE)</f>
+        <f>VLOOKUP(A286,'Candidatos E-26 ALC'!A287:I638,8,FALSE)</f>
         <v>646</v>
       </c>
       <c r="C286" s="5" t="s">
@@ -24694,7 +24646,7 @@
         <v>206</v>
       </c>
       <c r="B287" s="2">
-        <f>VLOOKUP(A287,'Candidatos E-26 ALC'!A67:I418,8,FALSE)</f>
+        <f>VLOOKUP(A287,'Candidatos E-26 ALC'!A67:I416,8,FALSE)</f>
         <v>642</v>
       </c>
       <c r="C287" s="5" t="s">
@@ -24724,7 +24676,7 @@
         <v>568</v>
       </c>
       <c r="B288" s="2">
-        <f>VLOOKUP(A288,'Candidatos E-26 ALC'!A202:I553,8,FALSE)</f>
+        <f>VLOOKUP(A288,'Candidatos E-26 ALC'!A202:I551,8,FALSE)</f>
         <v>642</v>
       </c>
       <c r="C288" s="2" t="s">
@@ -24754,7 +24706,7 @@
         <v>600</v>
       </c>
       <c r="B289" s="2">
-        <f>VLOOKUP(A289,'Candidatos E-26 ALC'!A214:I565,8,FALSE)</f>
+        <f>VLOOKUP(A289,'Candidatos E-26 ALC'!A214:I563,8,FALSE)</f>
         <v>640</v>
       </c>
       <c r="C289" s="2" t="s">
@@ -24784,7 +24736,7 @@
         <v>108</v>
       </c>
       <c r="B290" s="2">
-        <f>VLOOKUP(A290,'Candidatos E-26 ALC'!A33:I384,8,FALSE)</f>
+        <f>VLOOKUP(A290,'Candidatos E-26 ALC'!A33:I382,8,FALSE)</f>
         <v>639</v>
       </c>
       <c r="C290" s="5" t="s">
@@ -24814,7 +24766,7 @@
         <v>257</v>
       </c>
       <c r="B291" s="2">
-        <f>VLOOKUP(A291,'Candidatos E-26 ALC'!A86:I437,8,FALSE)</f>
+        <f>VLOOKUP(A291,'Candidatos E-26 ALC'!A86:I435,8,FALSE)</f>
         <v>637</v>
       </c>
       <c r="C291" s="2" t="s">
@@ -24844,7 +24796,7 @@
         <v>760</v>
       </c>
       <c r="B292" s="2">
-        <f>VLOOKUP(A292,'Candidatos E-26 ALC'!A285:I636,8,FALSE)</f>
+        <f>VLOOKUP(A292,'Candidatos E-26 ALC'!A283:I634,8,FALSE)</f>
         <v>618</v>
       </c>
       <c r="C292" s="5" t="s">
@@ -24874,7 +24826,7 @@
         <v>113</v>
       </c>
       <c r="B293" s="2">
-        <f>VLOOKUP(A293,'Candidatos E-26 ALC'!A35:I386,8,FALSE)</f>
+        <f>VLOOKUP(A293,'Candidatos E-26 ALC'!A35:I384,8,FALSE)</f>
         <v>614</v>
       </c>
       <c r="C293" s="5" t="s">
@@ -24904,7 +24856,7 @@
         <v>828</v>
       </c>
       <c r="B294" s="2">
-        <f>VLOOKUP(A294,'Candidatos E-26 ALC'!A312:I663,8,FALSE)</f>
+        <f>VLOOKUP(A294,'Candidatos E-26 ALC'!A310:I661,8,FALSE)</f>
         <v>614</v>
       </c>
       <c r="C294" s="2" t="s">
@@ -24934,7 +24886,7 @@
         <v>685</v>
       </c>
       <c r="B295" s="2">
-        <f>VLOOKUP(A295,'Candidatos E-26 ALC'!A247:I598,8,FALSE)</f>
+        <f>VLOOKUP(A295,'Candidatos E-26 ALC'!A247:I596,8,FALSE)</f>
         <v>585</v>
       </c>
       <c r="C295" s="5" t="s">
@@ -24964,7 +24916,7 @@
         <v>41</v>
       </c>
       <c r="B296" s="2">
-        <f>VLOOKUP(A296,'Candidatos E-26 ALC'!A11:I362,8,FALSE)</f>
+        <f>VLOOKUP(A296,'Candidatos E-26 ALC'!A11:I360,8,FALSE)</f>
         <v>579</v>
       </c>
       <c r="C296" s="5" t="s">
@@ -24994,7 +24946,7 @@
         <v>923</v>
       </c>
       <c r="B297" s="2">
-        <f>VLOOKUP(A297,'Candidatos E-26 ALC'!A349:I700,8,FALSE)</f>
+        <f>VLOOKUP(A297,'Candidatos E-26 ALC'!A347:I698,8,FALSE)</f>
         <v>549</v>
       </c>
       <c r="C297" s="5" t="s">
@@ -25024,7 +24976,7 @@
         <v>658</v>
       </c>
       <c r="B298" s="2">
-        <f>VLOOKUP(A298,'Candidatos E-26 ALC'!A236:I587,8,FALSE)</f>
+        <f>VLOOKUP(A298,'Candidatos E-26 ALC'!A236:I585,8,FALSE)</f>
         <v>546</v>
       </c>
       <c r="C298" s="2" t="s">
@@ -25054,7 +25006,7 @@
         <v>19</v>
       </c>
       <c r="B299" s="2">
-        <f>VLOOKUP(A299,'Candidatos E-26 ALC'!A4:I355,8,FALSE)</f>
+        <f>VLOOKUP(A299,'Candidatos E-26 ALC'!A4:I353,8,FALSE)</f>
         <v>541</v>
       </c>
       <c r="C299" s="2" t="s">
@@ -25084,7 +25036,7 @@
         <v>255</v>
       </c>
       <c r="B300" s="2">
-        <f>VLOOKUP(A300,'Candidatos E-26 ALC'!A85:I436,8,FALSE)</f>
+        <f>VLOOKUP(A300,'Candidatos E-26 ALC'!A85:I434,8,FALSE)</f>
         <v>537</v>
       </c>
       <c r="C300" s="5" t="s">
@@ -25114,7 +25066,7 @@
         <v>698</v>
       </c>
       <c r="B301" s="2">
-        <f>VLOOKUP(A301,'Candidatos E-26 ALC'!A253:I604,8,FALSE)</f>
+        <f>VLOOKUP(A301,'Candidatos E-26 ALC'!A253:I602,8,FALSE)</f>
         <v>536</v>
       </c>
       <c r="C301" s="5" t="s">
@@ -25144,7 +25096,7 @@
         <v>543</v>
       </c>
       <c r="B302" s="2">
-        <f>VLOOKUP(A302,'Candidatos E-26 ALC'!A193:I544,8,FALSE)</f>
+        <f>VLOOKUP(A302,'Candidatos E-26 ALC'!A193:I542,8,FALSE)</f>
         <v>503</v>
       </c>
       <c r="C302" s="5" t="s">
@@ -25174,7 +25126,7 @@
         <v>824</v>
       </c>
       <c r="B303" s="2">
-        <f>VLOOKUP(A303,'Candidatos E-26 ALC'!A310:I661,8,FALSE)</f>
+        <f>VLOOKUP(A303,'Candidatos E-26 ALC'!A308:I659,8,FALSE)</f>
         <v>484</v>
       </c>
       <c r="C303" s="2" t="s">
@@ -25204,7 +25156,7 @@
         <v>268</v>
       </c>
       <c r="B304" s="2">
-        <f>VLOOKUP(A304,'Candidatos E-26 ALC'!A91:I442,8,FALSE)</f>
+        <f>VLOOKUP(A304,'Candidatos E-26 ALC'!A91:I440,8,FALSE)</f>
         <v>482</v>
       </c>
       <c r="C304" s="5" t="s">
@@ -25234,7 +25186,7 @@
         <v>898</v>
       </c>
       <c r="B305" s="2">
-        <f>VLOOKUP(A305,'Candidatos E-26 ALC'!A339:I690,8,FALSE)</f>
+        <f>VLOOKUP(A305,'Candidatos E-26 ALC'!A337:I688,8,FALSE)</f>
         <v>458</v>
       </c>
       <c r="C305" s="5" t="s">
@@ -25264,7 +25216,7 @@
         <v>693</v>
       </c>
       <c r="B306" s="2">
-        <f>VLOOKUP(A306,'Candidatos E-26 ALC'!A251:I602,8,FALSE)</f>
+        <f>VLOOKUP(A306,'Candidatos E-26 ALC'!A251:I600,8,FALSE)</f>
         <v>451</v>
       </c>
       <c r="C306" s="5" t="s">
@@ -25294,7 +25246,7 @@
         <v>785</v>
       </c>
       <c r="B307" s="2">
-        <f>VLOOKUP(A307,'Candidatos E-26 ALC'!A296:I647,8,FALSE)</f>
+        <f>VLOOKUP(A307,'Candidatos E-26 ALC'!A294:I645,8,FALSE)</f>
         <v>444</v>
       </c>
       <c r="C307" s="2" t="s">
@@ -25324,7 +25276,7 @@
         <v>466</v>
       </c>
       <c r="B308" s="2">
-        <f>VLOOKUP(A308,'Candidatos E-26 ALC'!A163:I514,8,FALSE)</f>
+        <f>VLOOKUP(A308,'Candidatos E-26 ALC'!A163:I512,8,FALSE)</f>
         <v>412</v>
       </c>
       <c r="C308" s="5" t="s">
@@ -25354,7 +25306,7 @@
         <v>89</v>
       </c>
       <c r="B309" s="2">
-        <f>VLOOKUP(A309,'Candidatos E-26 ALC'!A27:I378,8,FALSE)</f>
+        <f>VLOOKUP(A309,'Candidatos E-26 ALC'!A27:I376,8,FALSE)</f>
         <v>411</v>
       </c>
       <c r="C309" s="5" t="s">
@@ -25384,7 +25336,7 @@
         <v>640</v>
       </c>
       <c r="B310" s="2">
-        <f>VLOOKUP(A310,'Candidatos E-26 ALC'!A229:I580,8,FALSE)</f>
+        <f>VLOOKUP(A310,'Candidatos E-26 ALC'!A229:I578,8,FALSE)</f>
         <v>400</v>
       </c>
       <c r="C310" s="5" t="s">
@@ -25414,7 +25366,7 @@
         <v>47</v>
       </c>
       <c r="B311" s="2">
-        <f>VLOOKUP(A311,'Candidatos E-26 ALC'!A13:I364,8,FALSE)</f>
+        <f>VLOOKUP(A311,'Candidatos E-26 ALC'!A13:I362,8,FALSE)</f>
         <v>388</v>
       </c>
       <c r="C311" s="5" t="s">
@@ -25444,7 +25396,7 @@
         <v>110</v>
       </c>
       <c r="B312" s="2">
-        <f>VLOOKUP(A312,'Candidatos E-26 ALC'!A34:I385,8,FALSE)</f>
+        <f>VLOOKUP(A312,'Candidatos E-26 ALC'!A34:I383,8,FALSE)</f>
         <v>361</v>
       </c>
       <c r="C312" s="2" t="s">
@@ -25474,7 +25426,7 @@
         <v>210</v>
       </c>
       <c r="B313" s="2">
-        <f>VLOOKUP(A313,'Candidatos E-26 ALC'!A69:I420,8,FALSE)</f>
+        <f>VLOOKUP(A313,'Candidatos E-26 ALC'!A69:I418,8,FALSE)</f>
         <v>361</v>
       </c>
       <c r="C313" s="5" t="s">
@@ -25504,7 +25456,7 @@
         <v>32</v>
       </c>
       <c r="B314" s="2">
-        <f>VLOOKUP(A314,'Candidatos E-26 ALC'!A8:I359,8,FALSE)</f>
+        <f>VLOOKUP(A314,'Candidatos E-26 ALC'!A8:I357,8,FALSE)</f>
         <v>352</v>
       </c>
       <c r="C314" s="2" t="s">
@@ -25532,7 +25484,7 @@
         <v>164</v>
       </c>
       <c r="B315" s="2">
-        <f>VLOOKUP(A315,'Candidatos E-26 ALC'!A53:I404,8,FALSE)</f>
+        <f>VLOOKUP(A315,'Candidatos E-26 ALC'!A53:I402,8,FALSE)</f>
         <v>348</v>
       </c>
       <c r="C315" s="5" t="s">
@@ -25562,7 +25514,7 @@
         <v>713</v>
       </c>
       <c r="B316" s="2">
-        <f>VLOOKUP(A316,'Candidatos E-26 ALC'!A260:I611,8,FALSE)</f>
+        <f>VLOOKUP(A316,'Candidatos E-26 ALC'!A260:I609,8,FALSE)</f>
         <v>346</v>
       </c>
       <c r="C316" s="2" t="s">
@@ -25592,7 +25544,7 @@
         <v>241</v>
       </c>
       <c r="B317" s="2">
-        <f>VLOOKUP(A317,'Candidatos E-26 ALC'!A80:I431,8,FALSE)</f>
+        <f>VLOOKUP(A317,'Candidatos E-26 ALC'!A80:I429,8,FALSE)</f>
         <v>345</v>
       </c>
       <c r="C317" s="2" t="s">
@@ -25622,7 +25574,7 @@
         <v>909</v>
       </c>
       <c r="B318" s="2">
-        <f>VLOOKUP(A318,'Candidatos E-26 ALC'!A343:I694,8,FALSE)</f>
+        <f>VLOOKUP(A318,'Candidatos E-26 ALC'!A341:I692,8,FALSE)</f>
         <v>342</v>
       </c>
       <c r="C318" s="5" t="s">
@@ -25652,7 +25604,7 @@
         <v>217</v>
       </c>
       <c r="B319" s="2">
-        <f>VLOOKUP(A319,'Candidatos E-26 ALC'!A72:I423,8,FALSE)</f>
+        <f>VLOOKUP(A319,'Candidatos E-26 ALC'!A72:I421,8,FALSE)</f>
         <v>328</v>
       </c>
       <c r="C319" s="2" t="s">
@@ -25682,7 +25634,7 @@
         <v>839</v>
       </c>
       <c r="B320" s="2">
-        <f>VLOOKUP(A320,'Candidatos E-26 ALC'!A317:I668,8,FALSE)</f>
+        <f>VLOOKUP(A320,'Candidatos E-26 ALC'!A315:I666,8,FALSE)</f>
         <v>320</v>
       </c>
       <c r="C320" s="5" t="s">
@@ -25712,7 +25664,7 @@
         <v>664</v>
       </c>
       <c r="B321" s="2">
-        <f>VLOOKUP(A321,'Candidatos E-26 ALC'!A239:I590,8,FALSE)</f>
+        <f>VLOOKUP(A321,'Candidatos E-26 ALC'!A239:I588,8,FALSE)</f>
         <v>305</v>
       </c>
       <c r="C321" s="5" t="s">
@@ -25742,7 +25694,7 @@
         <v>265</v>
       </c>
       <c r="B322" s="2">
-        <f>VLOOKUP(A322,'Candidatos E-26 ALC'!A90:I441,8,FALSE)</f>
+        <f>VLOOKUP(A322,'Candidatos E-26 ALC'!A90:I439,8,FALSE)</f>
         <v>300</v>
       </c>
       <c r="C322" s="2" t="s">
@@ -25772,7 +25724,7 @@
         <v>534</v>
       </c>
       <c r="B323" s="2">
-        <f>VLOOKUP(A323,'Candidatos E-26 ALC'!A190:I541,8,FALSE)</f>
+        <f>VLOOKUP(A323,'Candidatos E-26 ALC'!A190:I539,8,FALSE)</f>
         <v>293</v>
       </c>
       <c r="C323" s="2" t="s">
@@ -25802,7 +25754,7 @@
         <v>711</v>
       </c>
       <c r="B324" s="2">
-        <f>VLOOKUP(A324,'Candidatos E-26 ALC'!A259:I610,8,FALSE)</f>
+        <f>VLOOKUP(A324,'Candidatos E-26 ALC'!A259:I608,8,FALSE)</f>
         <v>290</v>
       </c>
       <c r="C324" s="5" t="s">
@@ -25832,7 +25784,7 @@
         <v>929</v>
       </c>
       <c r="B325" s="2">
-        <f>VLOOKUP(A325,'Candidatos E-26 ALC'!A352:I703,8,FALSE)</f>
+        <f>VLOOKUP(A325,'Candidatos E-26 ALC'!A350:I701,8,FALSE)</f>
         <v>245</v>
       </c>
       <c r="C325" s="2" t="s">
@@ -25862,7 +25814,7 @@
         <v>918</v>
       </c>
       <c r="B326" s="2">
-        <f>VLOOKUP(A326,'Candidatos E-26 ALC'!A347:I698,8,FALSE)</f>
+        <f>VLOOKUP(A326,'Candidatos E-26 ALC'!A345:I696,8,FALSE)</f>
         <v>230</v>
       </c>
       <c r="C326" s="5" t="s">
@@ -25892,7 +25844,7 @@
         <v>726</v>
       </c>
       <c r="B327" s="2">
-        <f>VLOOKUP(A327,'Candidatos E-26 ALC'!A264:I615,8,FALSE)</f>
+        <f>VLOOKUP(A327,'Candidatos E-26 ALC'!A264:I613,8,FALSE)</f>
         <v>218</v>
       </c>
       <c r="C327" s="2" t="s">
@@ -25922,7 +25874,7 @@
         <v>849</v>
       </c>
       <c r="B328" s="2">
-        <f>VLOOKUP(A328,'Candidatos E-26 ALC'!A320:I671,8,FALSE)</f>
+        <f>VLOOKUP(A328,'Candidatos E-26 ALC'!A318:I669,8,FALSE)</f>
         <v>192</v>
       </c>
       <c r="C328" s="2" t="s">
@@ -25952,7 +25904,7 @@
         <v>234</v>
       </c>
       <c r="B329" s="2">
-        <f>VLOOKUP(A329,'Candidatos E-26 ALC'!A78:I429,8,FALSE)</f>
+        <f>VLOOKUP(A329,'Candidatos E-26 ALC'!A78:I427,8,FALSE)</f>
         <v>179</v>
       </c>
       <c r="C329" s="2" t="s">
@@ -25982,7 +25934,7 @@
         <v>781</v>
       </c>
       <c r="B330" s="2">
-        <f>VLOOKUP(A330,'Candidatos E-26 ALC'!A294:I645,8,FALSE)</f>
+        <f>VLOOKUP(A330,'Candidatos E-26 ALC'!A292:I643,8,FALSE)</f>
         <v>177</v>
       </c>
       <c r="C330" s="2" t="s">
@@ -26012,7 +25964,7 @@
         <v>668</v>
       </c>
       <c r="B331" s="2">
-        <f>VLOOKUP(A331,'Candidatos E-26 ALC'!A241:I592,8,FALSE)</f>
+        <f>VLOOKUP(A331,'Candidatos E-26 ALC'!A241:I590,8,FALSE)</f>
         <v>173</v>
       </c>
       <c r="C331" s="5" t="s">
@@ -26042,7 +25994,7 @@
         <v>876</v>
       </c>
       <c r="B332" s="2">
-        <f>VLOOKUP(A332,'Candidatos E-26 ALC'!A331:I682,8,FALSE)</f>
+        <f>VLOOKUP(A332,'Candidatos E-26 ALC'!A329:I680,8,FALSE)</f>
         <v>171</v>
       </c>
       <c r="C332" s="5" t="s">
@@ -26072,7 +26024,7 @@
         <v>774</v>
       </c>
       <c r="B333" s="2">
-        <f>VLOOKUP(A333,'Candidatos E-26 ALC'!A291:I642,8,FALSE)</f>
+        <f>VLOOKUP(A333,'Candidatos E-26 ALC'!A289:I640,8,FALSE)</f>
         <v>166</v>
       </c>
       <c r="C333" s="5" t="s">
@@ -26102,7 +26054,7 @@
         <v>687</v>
       </c>
       <c r="B334" s="2">
-        <f>VLOOKUP(A334,'Candidatos E-26 ALC'!A248:I599,8,FALSE)</f>
+        <f>VLOOKUP(A334,'Candidatos E-26 ALC'!A248:I597,8,FALSE)</f>
         <v>159</v>
       </c>
       <c r="C334" s="2" t="s">
@@ -26132,7 +26084,7 @@
         <v>16</v>
       </c>
       <c r="B335" s="2">
-        <f>VLOOKUP(A335,'Candidatos E-26 ALC'!A3:I354,8,FALSE)</f>
+        <f>VLOOKUP(A335,'Candidatos E-26 ALC'!A3:I352,8,FALSE)</f>
         <v>146</v>
       </c>
       <c r="C335" s="5" t="s">
@@ -26162,7 +26114,7 @@
         <v>119</v>
       </c>
       <c r="B336" s="2">
-        <f>VLOOKUP(A336,'Candidatos E-26 ALC'!A38:I389,8,FALSE)</f>
+        <f>VLOOKUP(A336,'Candidatos E-26 ALC'!A38:I387,8,FALSE)</f>
         <v>133</v>
       </c>
       <c r="C336" s="2" t="s">
@@ -26192,7 +26144,7 @@
         <v>247</v>
       </c>
       <c r="B337" s="2">
-        <f>VLOOKUP(A337,'Candidatos E-26 ALC'!A82:I433,8,FALSE)</f>
+        <f>VLOOKUP(A337,'Candidatos E-26 ALC'!A82:I431,8,FALSE)</f>
         <v>93</v>
       </c>
       <c r="C337" s="2" t="s">
@@ -26222,7 +26174,7 @@
         <v>117</v>
       </c>
       <c r="B338" s="2">
-        <f>VLOOKUP(A338,'Candidatos E-26 ALC'!A37:I388,8,FALSE)</f>
+        <f>VLOOKUP(A338,'Candidatos E-26 ALC'!A37:I386,8,FALSE)</f>
         <v>68</v>
       </c>
       <c r="C338" s="5" t="s">
@@ -26252,7 +26204,7 @@
         <v>874</v>
       </c>
       <c r="B339" s="2">
-        <f>VLOOKUP(A339,'Candidatos E-26 ALC'!A330:I681,8,FALSE)</f>
+        <f>VLOOKUP(A339,'Candidatos E-26 ALC'!A328:I679,8,FALSE)</f>
         <v>14</v>
       </c>
       <c r="C339" s="2" t="s">
@@ -26282,7 +26234,7 @@
         <v>411</v>
       </c>
       <c r="B340" s="2">
-        <f>VLOOKUP(A340,'Candidatos E-26 ALC'!A143:I494,8,FALSE)</f>
+        <f>VLOOKUP(A340,'Candidatos E-26 ALC'!A143:I492,8,FALSE)</f>
         <v>5</v>
       </c>
       <c r="C340" s="5" t="s">
@@ -26312,7 +26264,7 @@
         <v>399</v>
       </c>
       <c r="B341" s="2">
-        <f>VLOOKUP(A341,'Candidatos E-26 ALC'!A139:I490,8,FALSE)</f>
+        <f>VLOOKUP(A341,'Candidatos E-26 ALC'!A139:I488,8,FALSE)</f>
         <v>3</v>
       </c>
       <c r="C341" s="5" t="s">
@@ -26342,7 +26294,7 @@
         <v>406</v>
       </c>
       <c r="B342" s="2">
-        <f>VLOOKUP(A342,'Candidatos E-26 ALC'!A141:I492,8,FALSE)</f>
+        <f>VLOOKUP(A342,'Candidatos E-26 ALC'!A141:I490,8,FALSE)</f>
         <v>3</v>
       </c>
       <c r="C342" s="5" t="s">
@@ -26372,7 +26324,7 @@
         <v>35</v>
       </c>
       <c r="B343" s="2">
-        <f>VLOOKUP(A343,'Candidatos E-26 ALC'!A9:I360,8,FALSE)</f>
+        <f>VLOOKUP(A343,'Candidatos E-26 ALC'!A9:I358,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C343" s="5" t="s">
@@ -26402,7 +26354,7 @@
         <v>38</v>
       </c>
       <c r="B344" s="2">
-        <f>VLOOKUP(A344,'Candidatos E-26 ALC'!A10:I361,8,FALSE)</f>
+        <f>VLOOKUP(A344,'Candidatos E-26 ALC'!A10:I359,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C344" s="2" t="s">
@@ -26432,7 +26384,7 @@
         <v>44</v>
       </c>
       <c r="B345" s="2">
-        <f>VLOOKUP(A345,'Candidatos E-26 ALC'!A12:I363,8,FALSE)</f>
+        <f>VLOOKUP(A345,'Candidatos E-26 ALC'!A12:I361,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C345" s="2" t="s">
@@ -26462,7 +26414,7 @@
         <v>789</v>
       </c>
       <c r="B346" s="2">
-        <f>VLOOKUP(A346,'Candidatos E-26 ALC'!A298:I649,8,FALSE)</f>
+        <f>VLOOKUP(A346,'Candidatos E-26 ALC'!A296:I647,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C346" s="2" t="s">
@@ -26492,7 +26444,7 @@
         <v>797</v>
       </c>
       <c r="B347" s="2">
-        <f>VLOOKUP(A347,'Candidatos E-26 ALC'!A300:I651,8,FALSE)</f>
+        <f>VLOOKUP(A347,'Candidatos E-26 ALC'!A298:I649,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C347" s="2" t="s">
@@ -26522,7 +26474,7 @@
         <v>799</v>
       </c>
       <c r="B348" s="2">
-        <f>VLOOKUP(A348,'Candidatos E-26 ALC'!A301:I652,8,FALSE)</f>
+        <f>VLOOKUP(A348,'Candidatos E-26 ALC'!A299:I650,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C348" s="5" t="s">
@@ -26552,7 +26504,7 @@
         <v>802</v>
       </c>
       <c r="B349" s="2">
-        <f>VLOOKUP(A349,'Candidatos E-26 ALC'!A302:I653,8,FALSE)</f>
+        <f>VLOOKUP(A349,'Candidatos E-26 ALC'!A300:I651,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C349" s="2" t="s">
@@ -26582,7 +26534,7 @@
         <v>851</v>
       </c>
       <c r="B350" s="2">
-        <f>VLOOKUP(A350,'Candidatos E-26 ALC'!A321:I672,8,FALSE)</f>
+        <f>VLOOKUP(A350,'Candidatos E-26 ALC'!A319:I670,8,FALSE)</f>
         <v>0</v>
       </c>
       <c r="C350" s="5" t="s">
@@ -26613,21 +26565,21 @@
       <c r="I351" s="25"/>
     </row>
     <row r="352" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="31">
-        <v>0</v>
-      </c>
-      <c r="B352" s="31"/>
-      <c r="C352" s="32"/>
-      <c r="D352" s="32"/>
-      <c r="E352" s="32"/>
-      <c r="F352" s="32"/>
-      <c r="G352" s="32"/>
-      <c r="H352" s="32"/>
-      <c r="I352" s="32"/>
-      <c r="J352" s="32"/>
-      <c r="K352" s="32"/>
-      <c r="L352" s="32"/>
-      <c r="M352" s="32"/>
+      <c r="A352" s="33">
+        <v>0</v>
+      </c>
+      <c r="B352" s="33"/>
+      <c r="C352" s="34"/>
+      <c r="D352" s="34"/>
+      <c r="E352" s="34"/>
+      <c r="F352" s="34"/>
+      <c r="G352" s="34"/>
+      <c r="H352" s="34"/>
+      <c r="I352" s="34"/>
+      <c r="J352" s="34"/>
+      <c r="K352" s="34"/>
+      <c r="L352" s="34"/>
+      <c r="M352" s="34"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M350" xr:uid="{00000000-0009-0000-0000-000001000000}">
@@ -28765,14 +28717,14 @@
       <c r="F35" s="14"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="33" t="s">
         <v>971</v>
       </c>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F34" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
